--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA695EAC-5A63-4C0B-96FB-0055045A4253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0254651-D311-441C-96B7-FD82302C2EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="1755" windowWidth="16305" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="432">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,132 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>03/19/2026 2:37:03 PM</t>
+  </si>
+  <si>
+    <t>Truck 6</t>
+  </si>
+  <si>
+    <t>Robert Bailey</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Forward Collision Warning</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Melissa H Mericle</t>
+  </si>
+  <si>
+    <t>7101 US 79, River Hill, TX, 75639</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450799-f498-5512-add6-e9823215d7df</t>
+  </si>
+  <si>
+    <t>03/17/2026 3:43:53 PM</t>
+  </si>
+  <si>
+    <t>Truck 22</t>
+  </si>
+  <si>
+    <t>Josh Gregory</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Pedestrians, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>5221 Jewella Avenue, Shreveport, LA, 71109</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd8a-6c12-52ce-baf3-303addf7bdf3</t>
+  </si>
+  <si>
+    <t>03/17/2026 12:44:39 PM</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>I 20, Webster Parish, LA, 71067</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fce6-554c-5558-a57e-9e8a5b08a13c</t>
+  </si>
+  <si>
+    <t>03/17/2026 8:28:46 AM</t>
+  </si>
+  <si>
+    <t>Truck 3</t>
+  </si>
+  <si>
+    <t>Mark Gwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t>Congested</t>
+  </si>
+  <si>
+    <t>Inner Loop Expressway, Shreveport, LA, 71118</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbfc-1056-531a-8556-dc31dc98a53f</t>
+  </si>
+  <si>
+    <t>03/17/2026 8:14:03 AM</t>
+  </si>
+  <si>
+    <t>Truck 12</t>
+  </si>
+  <si>
+    <t>Kendall Mckerley</t>
+  </si>
+  <si>
+    <t>I 20;US 71, Bossier City, LA, 71171</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbee-9601-5000-bd9a-cc9c81f9757b</t>
+  </si>
+  <si>
     <t>03/14/2026 12:08:45 PM</t>
   </si>
   <si>
@@ -74,39 +200,18 @@
     <t>Full fleet , Heavy Duty</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Rolling Stop</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Melissa H Mericle</t>
-  </si>
-  <si>
     <t>1999 Venus Drive, Bossier City, LA, 71112</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ed52-6229-5cf8-b84a-6b5c83872cd3</t>
   </si>
   <si>
     <t>03/13/2026 12:28:19 PM</t>
   </si>
   <si>
-    <t>Truck 3</t>
-  </si>
-  <si>
     <t>Will Ordoyne</t>
   </si>
   <si>
@@ -146,9 +251,6 @@
     <t>Truck 23</t>
   </si>
   <si>
-    <t>Josh Gregory</t>
-  </si>
-  <si>
     <t>No Seat Belt</t>
   </si>
   <si>
@@ -194,9 +296,6 @@
     <t>Josh Caldwell</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
     <t>4801 McGee Road, Greenwood, LA, 71119</t>
   </si>
   <si>
@@ -206,12 +305,6 @@
     <t>03/10/2026 10:37:33 PM</t>
   </si>
   <si>
-    <t>Truck 6</t>
-  </si>
-  <si>
-    <t>Robert Bailey</t>
-  </si>
-  <si>
     <t>8400 East Kings Highway, Shreveport, LA, 71115</t>
   </si>
   <si>
@@ -251,9 +344,6 @@
     <t>03/08/2026 5:02:11 PM</t>
   </si>
   <si>
-    <t>Truck 22</t>
-  </si>
-  <si>
     <t>Construction, Parking Lot, Light Traffic</t>
   </si>
   <si>
@@ -290,9 +380,6 @@
     <t>143 Lakewood Point Drive, Bossier Parish, LA, 71111</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -302,12 +389,6 @@
     <t>03/05/2026 2:26:58 AM</t>
   </si>
   <si>
-    <t>Truck 12</t>
-  </si>
-  <si>
-    <t>Kendall Mckerley</t>
-  </si>
-  <si>
     <t>Drowsiness</t>
   </si>
   <si>
@@ -353,9 +434,6 @@
     <t>03/02/2026 7:20:02 PM</t>
   </si>
   <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
     <t>746 East Flournoy Lucas Road, Shreveport, LA, 71115</t>
   </si>
   <si>
@@ -374,9 +452,6 @@
     <t>6391 LA 1;LA 6, Natchitoches, LA, 71457</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b06f-f8d0-57b8-bab8-41729cacf1db</t>
   </si>
   <si>
@@ -398,12 +473,6 @@
     <t>Peyton Birchfield</t>
   </si>
   <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>3564 Hollywood Avenue, Shreveport, LA, 71109</t>
   </si>
   <si>
@@ -419,9 +488,6 @@
     <t>I 20;US 371, Minden, LA, 71055</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a069-fc2c-5020-a12e-3af0b806a496</t>
   </si>
   <si>
@@ -470,9 +536,6 @@
     <t>02/19/2026 3:42:11 PM</t>
   </si>
   <si>
-    <t>Mark Gwin</t>
-  </si>
-  <si>
     <t>256 Lake Street, Shreveport, LA, 71101</t>
   </si>
   <si>
@@ -722,9 +785,6 @@
     <t>02/02/2026 4:29:47 PM</t>
   </si>
   <si>
-    <t>Congested</t>
-  </si>
-  <si>
     <t>2125 Hollywood Avenue, Shreveport, LA, 71108</t>
   </si>
   <si>
@@ -1103,9 +1163,6 @@
     <t>US 71;LA 1, Shreveport, LA, 71137</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459dec-7061-5fe2-9fcf-ddda463e90ec</t>
   </si>
   <si>
@@ -1254,15 +1311,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454330-f5e4-51fb-b9c5-fb0ac3c927ad</t>
-  </si>
-  <si>
-    <t>12/18/2025 3:45:40 PM</t>
-  </si>
-  <si>
-    <t>921 Rickey Place, Bossier City, LA, 71112</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445336d-0375-567b-a0a9-a251f9529b3c</t>
   </si>
 </sst>
 </file>
@@ -1639,10 +1687,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O100"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1689,7 +1737,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1736,7 +1784,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1747,204 +1795,204 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" t="s">
-        <v>26</v>
-      </c>
       <c r="O6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1953,45 +2001,45 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
         <v>60</v>
       </c>
-      <c r="K7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -2000,10 +2048,10 @@
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -2015,30 +2063,30 @@
         <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -2047,10 +2095,10 @@
         <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -2062,42 +2110,42 @@
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -2109,30 +2157,30 @@
         <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>78</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -2141,10 +2189,10 @@
         <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
         <v>26</v>
@@ -2156,30 +2204,30 @@
         <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -2188,139 +2236,139 @@
         <v>23</v>
       </c>
       <c r="J12" t="s">
+        <v>93</v>
+      </c>
+      <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s">
         <v>84</v>
       </c>
-      <c r="K12" t="s">
+      <c r="C15" t="s">
         <v>85</v>
       </c>
-      <c r="L12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" t="s">
-        <v>86</v>
-      </c>
-      <c r="O12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" t="s">
-        <v>90</v>
-      </c>
-      <c r="K13" t="s">
-        <v>91</v>
-      </c>
-      <c r="L13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" t="s">
-        <v>92</v>
-      </c>
-      <c r="N13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" t="s">
-        <v>100</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2329,57 +2377,57 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -2391,30 +2439,30 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -2423,10 +2471,10 @@
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -2435,233 +2483,233 @@
         <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
+        <v>121</v>
+      </c>
+      <c r="N18" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" t="s">
         <v>21</v>
       </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
         <v>23</v>
       </c>
-      <c r="J18" t="s">
-        <v>118</v>
-      </c>
-      <c r="K18" t="s">
-        <v>119</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" t="s">
-        <v>92</v>
-      </c>
-      <c r="N18" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="J20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" t="s">
         <v>121</v>
       </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" t="s">
-        <v>122</v>
-      </c>
-      <c r="K19" t="s">
-        <v>123</v>
-      </c>
-      <c r="L19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" t="s">
-        <v>129</v>
-      </c>
-      <c r="K20" t="s">
-        <v>66</v>
-      </c>
-      <c r="L20" t="s">
-        <v>26</v>
-      </c>
-      <c r="M20" t="s">
-        <v>26</v>
-      </c>
       <c r="N20" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="G22" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K22" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -2673,27 +2721,27 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="G23" t="s">
         <v>21</v>
@@ -2705,57 +2753,57 @@
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N23" t="s">
         <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K24" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2767,42 +2815,42 @@
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K25" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -2811,30 +2859,30 @@
         <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="O25" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G26" t="s">
         <v>21</v>
@@ -2843,92 +2891,92 @@
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K26" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N26" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K27" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s">
         <v>21</v>
@@ -2940,10 +2988,10 @@
         <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K28" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
@@ -2955,42 +3003,42 @@
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K29" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -3002,27 +3050,27 @@
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s">
         <v>21</v>
@@ -3034,10 +3082,10 @@
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K30" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s">
         <v>26</v>
@@ -3049,30 +3097,30 @@
         <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
@@ -3081,45 +3129,45 @@
         <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
+        <v>174</v>
+      </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>175</v>
+      </c>
+      <c r="O31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
         <v>85</v>
       </c>
-      <c r="L31" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>173</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>51</v>
-      </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G32" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
@@ -3128,92 +3176,92 @@
         <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L32" t="s">
         <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
+        <v>181</v>
+      </c>
+      <c r="K33" t="s">
+        <v>182</v>
+      </c>
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
         <v>151</v>
       </c>
-      <c r="D33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" t="s">
-        <v>137</v>
-      </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" t="s">
-        <v>177</v>
-      </c>
-      <c r="K33" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>179</v>
-      </c>
-      <c r="B34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" t="s">
-        <v>96</v>
-      </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -3222,10 +3270,10 @@
         <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s">
         <v>26</v>
@@ -3237,18 +3285,18 @@
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -3257,7 +3305,7 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s">
         <v>21</v>
@@ -3269,198 +3317,198 @@
         <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K35" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="L35" t="s">
         <v>26</v>
       </c>
       <c r="M35" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N35" t="s">
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
       <c r="F36" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" t="s">
+        <v>192</v>
+      </c>
+      <c r="K36" t="s">
+        <v>115</v>
+      </c>
+      <c r="L36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>26</v>
+      </c>
+      <c r="O36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" t="s">
+        <v>195</v>
+      </c>
+      <c r="K37" t="s">
+        <v>67</v>
+      </c>
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>26</v>
+      </c>
+      <c r="O37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s">
         <v>44</v>
       </c>
-      <c r="G36" t="s">
+      <c r="D38" t="s">
         <v>45</v>
       </c>
-      <c r="H36" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" t="s">
-        <v>187</v>
-      </c>
-      <c r="K36" t="s">
-        <v>188</v>
-      </c>
-      <c r="L36" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>190</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G37" t="s">
-        <v>191</v>
-      </c>
-      <c r="H37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" t="s">
-        <v>192</v>
-      </c>
-      <c r="K37" t="s">
-        <v>165</v>
-      </c>
-      <c r="L37" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>194</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
-        <v>195</v>
-      </c>
-      <c r="D38" t="s">
-        <v>26</v>
-      </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="G38" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" t="s">
+        <v>198</v>
+      </c>
+      <c r="K38" t="s">
+        <v>40</v>
+      </c>
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s">
         <v>21</v>
       </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" t="s">
-        <v>26</v>
-      </c>
-      <c r="J38" t="s">
-        <v>196</v>
-      </c>
-      <c r="K38" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>198</v>
-      </c>
-      <c r="B39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" t="s">
-        <v>199</v>
-      </c>
-      <c r="D39" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" t="s">
-        <v>191</v>
-      </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K39" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -3472,30 +3520,30 @@
         <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="G40" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
@@ -3504,92 +3552,92 @@
         <v>23</v>
       </c>
       <c r="J40" t="s">
+        <v>204</v>
+      </c>
+      <c r="K40" t="s">
+        <v>205</v>
+      </c>
+      <c r="L40" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" t="s">
+        <v>121</v>
+      </c>
+      <c r="N40" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" t="s">
         <v>206</v>
       </c>
-      <c r="K40" t="s">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A41" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" t="s">
         <v>91</v>
       </c>
-      <c r="L40" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" t="s">
-        <v>26</v>
-      </c>
-      <c r="O40" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" t="s">
         <v>208</v>
       </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" t="s">
-        <v>89</v>
-      </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" t="s">
-        <v>26</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>209</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" t="s">
         <v>210</v>
       </c>
-      <c r="L41" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" t="s">
-        <v>92</v>
-      </c>
-      <c r="N41" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" t="s">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A42" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>38</v>
+      </c>
+      <c r="G42" t="s">
         <v>212</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" t="s">
-        <v>83</v>
-      </c>
-      <c r="G42" t="s">
-        <v>21</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -3601,31 +3649,31 @@
         <v>213</v>
       </c>
       <c r="K42" t="s">
+        <v>186</v>
+      </c>
+      <c r="L42" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>26</v>
+      </c>
+      <c r="O42" t="s">
         <v>214</v>
       </c>
-      <c r="L42" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" t="s">
-        <v>130</v>
-      </c>
-      <c r="O42" t="s">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A43" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
         <v>216</v>
       </c>
-      <c r="B43" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" t="s">
-        <v>96</v>
-      </c>
       <c r="D43" t="s">
         <v>26</v>
       </c>
@@ -3633,10 +3681,10 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G43" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -3648,7 +3696,7 @@
         <v>217</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L43" t="s">
         <v>26</v>
@@ -3663,15 +3711,15 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>219</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>220</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -3680,10 +3728,10 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
@@ -3692,10 +3740,10 @@
         <v>23</v>
       </c>
       <c r="J44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K44" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s">
         <v>26</v>
@@ -3707,18 +3755,18 @@
         <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -3727,10 +3775,10 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="G45" t="s">
-        <v>52</v>
+        <v>226</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
@@ -3739,10 +3787,10 @@
         <v>23</v>
       </c>
       <c r="J45" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K45" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L45" t="s">
         <v>26</v>
@@ -3754,74 +3802,74 @@
         <v>26</v>
       </c>
       <c r="O45" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s">
+        <v>26</v>
+      </c>
+      <c r="J46" t="s">
+        <v>230</v>
+      </c>
+      <c r="K46" t="s">
+        <v>231</v>
+      </c>
+      <c r="L46" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" t="s">
+        <v>121</v>
+      </c>
+      <c r="N46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A47" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
         <v>151</v>
       </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
-        <v>227</v>
-      </c>
-      <c r="G46" t="s">
-        <v>52</v>
-      </c>
-      <c r="H46" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" t="s">
-        <v>26</v>
-      </c>
-      <c r="J46" t="s">
-        <v>69</v>
-      </c>
-      <c r="K46" t="s">
-        <v>228</v>
-      </c>
-      <c r="L46" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>230</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="s">
-        <v>195</v>
-      </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="G47" t="s">
         <v>21</v>
@@ -3833,10 +3881,10 @@
         <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K47" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s">
         <v>26</v>
@@ -3845,45 +3893,45 @@
         <v>26</v>
       </c>
       <c r="N47" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="O47" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="G48" t="s">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K48" t="s">
-        <v>237</v>
+        <v>67</v>
       </c>
       <c r="L48" t="s">
         <v>26</v>
@@ -3892,316 +3940,316 @@
         <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>238</v>
+        <v>26</v>
       </c>
       <c r="O48" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>240</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
         <v>241</v>
       </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
+        <v>97</v>
+      </c>
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49" t="s">
         <v>242</v>
       </c>
-      <c r="K49" t="s">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A50" t="s">
         <v>243</v>
       </c>
-      <c r="L49" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" t="s">
+      <c r="B50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="K50" t="s">
+        <v>48</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>26</v>
+      </c>
+      <c r="O50" t="s">
         <v>245</v>
       </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
-        <v>97</v>
-      </c>
-      <c r="G50" t="s">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A51" t="s">
         <v>246</v>
       </c>
-      <c r="H50" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" t="s">
-        <v>26</v>
-      </c>
-      <c r="J50" t="s">
-        <v>69</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="B51" t="s">
         <v>247</v>
       </c>
-      <c r="L50" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" t="s">
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="G51" t="s">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" t="s">
+        <v>100</v>
+      </c>
+      <c r="K51" t="s">
         <v>249</v>
       </c>
-      <c r="B51" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" t="s">
-        <v>35</v>
-      </c>
-      <c r="F51" t="s">
-        <v>89</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>26</v>
+      </c>
+      <c r="O51" t="s">
         <v>250</v>
       </c>
-      <c r="H51" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" t="s">
-        <v>26</v>
-      </c>
-      <c r="J51" t="s">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A52" t="s">
         <v>251</v>
       </c>
-      <c r="K51" t="s">
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>216</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J52" t="s">
         <v>252</v>
       </c>
-      <c r="L51" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" t="s">
-        <v>92</v>
-      </c>
-      <c r="N51" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" t="s">
+      <c r="K52" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" t="s">
+        <v>26</v>
+      </c>
+      <c r="O52" t="s">
         <v>254</v>
       </c>
-      <c r="B52" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" t="s">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A53" t="s">
+        <v>255</v>
+      </c>
+      <c r="B53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" t="s">
+        <v>220</v>
+      </c>
+      <c r="D53" t="s">
         <v>18</v>
       </c>
-      <c r="E52" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" t="s">
-        <v>44</v>
-      </c>
-      <c r="G52" t="s">
-        <v>255</v>
-      </c>
-      <c r="H52" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" t="s">
+        <v>46</v>
+      </c>
+      <c r="H53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
         <v>23</v>
       </c>
-      <c r="J52" t="s">
-        <v>69</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="J53" t="s">
         <v>256</v>
       </c>
-      <c r="L52" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" t="s">
+      <c r="K53" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" t="s">
         <v>258</v>
       </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" t="s">
-        <v>127</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="O53" t="s">
         <v>259</v>
       </c>
-      <c r="H53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" t="s">
-        <v>26</v>
-      </c>
-      <c r="J53" t="s">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A54" t="s">
         <v>260</v>
       </c>
-      <c r="K53" t="s">
-        <v>100</v>
-      </c>
-      <c r="L53" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>262</v>
-      </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
         <v>151</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G54" t="s">
+        <v>261</v>
+      </c>
+      <c r="H54" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" t="s">
+        <v>262</v>
+      </c>
+      <c r="K54" t="s">
         <v>263</v>
       </c>
-      <c r="H54" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="L54" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O54" t="s">
         <v>264</v>
       </c>
-      <c r="K54" t="s">
-        <v>232</v>
-      </c>
-      <c r="L54" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" t="s">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A55" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
+        <v>151</v>
+      </c>
+      <c r="D55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>124</v>
+      </c>
+      <c r="G55" t="s">
         <v>266</v>
       </c>
-      <c r="B55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C55" t="s">
-        <v>43</v>
-      </c>
-      <c r="D55" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" t="s">
-        <v>44</v>
-      </c>
-      <c r="G55" t="s">
-        <v>52</v>
-      </c>
       <c r="H55" t="s">
         <v>22</v>
       </c>
@@ -4209,10 +4257,10 @@
         <v>26</v>
       </c>
       <c r="J55" t="s">
+        <v>100</v>
+      </c>
+      <c r="K55" t="s">
         <v>267</v>
-      </c>
-      <c r="K55" t="s">
-        <v>32</v>
       </c>
       <c r="L55" t="s">
         <v>26</v>
@@ -4227,27 +4275,27 @@
         <v>268</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>269</v>
       </c>
       <c r="B56" t="s">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G56" t="s">
-        <v>45</v>
+        <v>270</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
@@ -4256,45 +4304,45 @@
         <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K56" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
       </c>
       <c r="M56" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N56" t="s">
         <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s">
-        <v>45</v>
+        <v>275</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
@@ -4303,57 +4351,57 @@
         <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c r="K57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L57" t="s">
         <v>26</v>
       </c>
       <c r="M57" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N57" t="s">
         <v>26</v>
       </c>
       <c r="O57" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="D58" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="G58" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K58" t="s">
-        <v>188</v>
+        <v>127</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -4365,42 +4413,42 @@
         <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>282</v>
+        <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G59" t="s">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K59" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -4412,18 +4460,18 @@
         <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
@@ -4432,10 +4480,10 @@
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
@@ -4447,136 +4495,136 @@
         <v>287</v>
       </c>
       <c r="K60" t="s">
+        <v>67</v>
+      </c>
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>26</v>
+      </c>
+      <c r="O60" t="s">
         <v>288</v>
       </c>
-      <c r="L60" t="s">
-        <v>26</v>
-      </c>
-      <c r="M60" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" t="s">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A61" t="s">
         <v>289</v>
       </c>
-      <c r="O60" t="s">
+      <c r="B61" t="s">
+        <v>247</v>
+      </c>
+      <c r="C61" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" t="s">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="K61" t="s">
         <v>291</v>
       </c>
-      <c r="B61" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" t="s">
-        <v>151</v>
-      </c>
-      <c r="D61" t="s">
-        <v>127</v>
-      </c>
-      <c r="E61" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="L61" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" t="s">
+        <v>26</v>
+      </c>
+      <c r="O61" t="s">
         <v>292</v>
       </c>
-      <c r="H61" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" t="s">
-        <v>26</v>
-      </c>
-      <c r="J61" t="s">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A62" t="s">
         <v>293</v>
       </c>
-      <c r="K61" t="s">
-        <v>66</v>
-      </c>
-      <c r="L61" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" t="s">
-        <v>26</v>
-      </c>
-      <c r="O61" t="s">
+      <c r="B62" t="s">
+        <v>91</v>
+      </c>
+      <c r="C62" t="s">
+        <v>92</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" t="s">
+        <v>119</v>
+      </c>
+      <c r="G62" t="s">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="K62" t="s">
         <v>295</v>
       </c>
-      <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" t="s">
-        <v>19</v>
-      </c>
-      <c r="F62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" t="s">
-        <v>246</v>
-      </c>
-      <c r="H62" t="s">
-        <v>22</v>
-      </c>
-      <c r="I62" t="s">
-        <v>26</v>
-      </c>
-      <c r="J62" t="s">
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" t="s">
+        <v>121</v>
+      </c>
+      <c r="N62" t="s">
+        <v>26</v>
+      </c>
+      <c r="O62" t="s">
         <v>296</v>
       </c>
-      <c r="K62" t="s">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A63" t="s">
         <v>297</v>
       </c>
-      <c r="L62" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>299</v>
-      </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G63" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="H63" t="s">
         <v>22</v>
@@ -4585,140 +4633,140 @@
         <v>23</v>
       </c>
       <c r="J63" t="s">
+        <v>298</v>
+      </c>
+      <c r="K63" t="s">
+        <v>209</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" t="s">
+        <v>26</v>
+      </c>
+      <c r="O63" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A64" t="s">
+        <v>300</v>
+      </c>
+      <c r="B64" t="s">
         <v>301</v>
       </c>
-      <c r="K63" t="s">
+      <c r="C64" t="s">
         <v>302</v>
       </c>
-      <c r="L63" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" t="s">
-        <v>26</v>
-      </c>
-      <c r="O63" t="s">
+      <c r="D64" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" t="s">
+        <v>61</v>
+      </c>
+      <c r="G64" t="s">
+        <v>86</v>
+      </c>
+      <c r="H64" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="K64" t="s">
+        <v>182</v>
+      </c>
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" t="s">
+        <v>26</v>
+      </c>
+      <c r="O64" t="s">
         <v>304</v>
       </c>
-      <c r="B64" t="s">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A65" t="s">
         <v>305</v>
       </c>
-      <c r="C64" t="s">
-        <v>26</v>
-      </c>
-      <c r="D64" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" t="s">
-        <v>127</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="B65" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>306</v>
+      </c>
+      <c r="G65" t="s">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" t="s">
+        <v>307</v>
+      </c>
+      <c r="K65" t="s">
+        <v>308</v>
+      </c>
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>309</v>
+      </c>
+      <c r="O65" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A66" t="s">
+        <v>311</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
         <v>44</v>
       </c>
-      <c r="G64" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64" t="s">
-        <v>22</v>
-      </c>
-      <c r="I64" t="s">
-        <v>26</v>
-      </c>
-      <c r="J64" t="s">
-        <v>306</v>
-      </c>
-      <c r="K64" t="s">
-        <v>214</v>
-      </c>
-      <c r="L64" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" t="s">
-        <v>26</v>
-      </c>
-      <c r="O64" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>308</v>
-      </c>
-      <c r="B65" t="s">
-        <v>305</v>
-      </c>
-      <c r="C65" t="s">
-        <v>26</v>
-      </c>
-      <c r="D65" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" t="s">
-        <v>127</v>
-      </c>
-      <c r="F65" t="s">
-        <v>44</v>
-      </c>
-      <c r="G65" t="s">
-        <v>21</v>
-      </c>
-      <c r="H65" t="s">
-        <v>22</v>
-      </c>
-      <c r="I65" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" t="s">
-        <v>309</v>
-      </c>
-      <c r="K65" t="s">
-        <v>310</v>
-      </c>
-      <c r="L65" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="D66" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" t="s">
         <v>312</v>
       </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66" t="s">
-        <v>127</v>
-      </c>
-      <c r="E66" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" t="s">
-        <v>112</v>
-      </c>
-      <c r="G66" t="s">
-        <v>241</v>
-      </c>
       <c r="H66" t="s">
         <v>22</v>
       </c>
@@ -4726,10 +4774,10 @@
         <v>26</v>
       </c>
       <c r="J66" t="s">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="K66" t="s">
-        <v>313</v>
+        <v>97</v>
       </c>
       <c r="L66" t="s">
         <v>26</v>
@@ -4744,15 +4792,15 @@
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>315</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -4761,10 +4809,10 @@
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="G67" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
@@ -4776,7 +4824,7 @@
         <v>316</v>
       </c>
       <c r="K67" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -4788,30 +4836,30 @@
         <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="G68" t="s">
-        <v>52</v>
+        <v>320</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
@@ -4820,10 +4868,10 @@
         <v>23</v>
       </c>
       <c r="J68" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K68" t="s">
-        <v>123</v>
+        <v>322</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -4835,42 +4883,42 @@
         <v>26</v>
       </c>
       <c r="O68" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="C69" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F69" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="H69" t="s">
         <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="K69" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L69" t="s">
         <v>26</v>
@@ -4882,27 +4930,27 @@
         <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
+        <v>26</v>
       </c>
       <c r="D70" t="s">
         <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s">
         <v>21</v>
@@ -4914,10 +4962,10 @@
         <v>26</v>
       </c>
       <c r="J70" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="K70" t="s">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="L70" t="s">
         <v>26</v>
@@ -4929,124 +4977,124 @@
         <v>26</v>
       </c>
       <c r="O70" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" t="s">
+        <v>45</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>38</v>
+      </c>
+      <c r="G71" t="s">
+        <v>261</v>
+      </c>
+      <c r="H71" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71" t="s">
+        <v>213</v>
+      </c>
+      <c r="K71" t="s">
+        <v>333</v>
+      </c>
+      <c r="L71" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" t="s">
+        <v>26</v>
+      </c>
+      <c r="O71" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A72" t="s">
+        <v>335</v>
+      </c>
+      <c r="B72" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72" t="s">
+        <v>53</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>124</v>
+      </c>
+      <c r="G72" t="s">
+        <v>279</v>
+      </c>
+      <c r="H72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" t="s">
+        <v>336</v>
+      </c>
+      <c r="K72" t="s">
+        <v>308</v>
+      </c>
+      <c r="L72" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A73" t="s">
+        <v>338</v>
+      </c>
+      <c r="B73" t="s">
         <v>16</v>
       </c>
-      <c r="C71" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" t="s">
-        <v>26</v>
-      </c>
-      <c r="J71" t="s">
-        <v>31</v>
-      </c>
-      <c r="K71" t="s">
-        <v>328</v>
-      </c>
-      <c r="L71" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O71" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>330</v>
-      </c>
-      <c r="B72" t="s">
-        <v>50</v>
-      </c>
-      <c r="C72" t="s">
-        <v>51</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
         <v>18</v>
       </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>44</v>
-      </c>
-      <c r="G72" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" t="s">
-        <v>22</v>
-      </c>
-      <c r="I72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J72" t="s">
-        <v>331</v>
-      </c>
-      <c r="K72" t="s">
-        <v>161</v>
-      </c>
-      <c r="L72" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>333</v>
-      </c>
-      <c r="B73" t="s">
-        <v>57</v>
-      </c>
-      <c r="C73" t="s">
-        <v>58</v>
-      </c>
-      <c r="D73" t="s">
-        <v>59</v>
-      </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="G73" t="s">
-        <v>334</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
@@ -5055,10 +5103,10 @@
         <v>23</v>
       </c>
       <c r="J73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K73" t="s">
-        <v>256</v>
+        <v>148</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
@@ -5070,42 +5118,42 @@
         <v>26</v>
       </c>
       <c r="O73" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="G74" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="H74" t="s">
         <v>22</v>
       </c>
       <c r="I74" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J74" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K74" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -5117,27 +5165,27 @@
         <v>26</v>
       </c>
       <c r="O74" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G75" t="s">
         <v>21</v>
@@ -5146,48 +5194,48 @@
         <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J75" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K75" t="s">
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
       </c>
       <c r="M75" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N75" t="s">
         <v>26</v>
       </c>
       <c r="O75" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C76" t="s">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D76" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="G76" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="H76" t="s">
         <v>22</v>
@@ -5196,10 +5244,10 @@
         <v>26</v>
       </c>
       <c r="J76" t="s">
-        <v>316</v>
+        <v>66</v>
       </c>
       <c r="K76" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="L76" t="s">
         <v>26</v>
@@ -5211,30 +5259,30 @@
         <v>26</v>
       </c>
       <c r="O76" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B77" t="s">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>348</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E77" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="H77" t="s">
         <v>22</v>
@@ -5243,10 +5291,10 @@
         <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K77" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -5258,42 +5306,42 @@
         <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B78" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="G78" t="s">
-        <v>191</v>
+        <v>354</v>
       </c>
       <c r="H78" t="s">
         <v>22</v>
       </c>
       <c r="I78" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K78" t="s">
-        <v>92</v>
+        <v>276</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -5305,74 +5353,74 @@
         <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="G79" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H79" t="s">
         <v>22</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J79" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K79" t="s">
+        <v>263</v>
+      </c>
+      <c r="L79" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" t="s">
+        <v>26</v>
+      </c>
+      <c r="O79" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A80" t="s">
+        <v>360</v>
+      </c>
+      <c r="B80" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D80" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
         <v>119</v>
-      </c>
-      <c r="L79" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" t="s">
-        <v>92</v>
-      </c>
-      <c r="N79" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>357</v>
-      </c>
-      <c r="B80" t="s">
-        <v>50</v>
-      </c>
-      <c r="C80" t="s">
-        <v>51</v>
-      </c>
-      <c r="D80" t="s">
-        <v>18</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
-        <v>89</v>
       </c>
       <c r="G80" t="s">
         <v>21</v>
@@ -5384,45 +5432,45 @@
         <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>157</v>
+        <v>361</v>
       </c>
       <c r="K80" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="L80" t="s">
         <v>26</v>
       </c>
       <c r="M80" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="N80" t="s">
         <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B81" t="s">
-        <v>360</v>
+        <v>43</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="H81" t="s">
         <v>22</v>
@@ -5431,7 +5479,7 @@
         <v>26</v>
       </c>
       <c r="J81" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="K81" t="s">
         <v>362</v>
@@ -5440,48 +5488,48 @@
         <v>26</v>
       </c>
       <c r="M81" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N81" t="s">
         <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>367</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>368</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="H82" t="s">
         <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K82" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
@@ -5493,121 +5541,121 @@
         <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B83" t="s">
-        <v>63</v>
+        <v>224</v>
       </c>
       <c r="C83" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="H83" t="s">
         <v>22</v>
       </c>
       <c r="I83" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" t="s">
+        <v>372</v>
+      </c>
+      <c r="K83" t="s">
+        <v>121</v>
+      </c>
+      <c r="L83" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" t="s">
+        <v>26</v>
+      </c>
+      <c r="O83" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A84" t="s">
+        <v>374</v>
+      </c>
+      <c r="B84" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" t="s">
+        <v>85</v>
+      </c>
+      <c r="D84" t="s">
+        <v>60</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>119</v>
+      </c>
+      <c r="G84" t="s">
+        <v>86</v>
+      </c>
+      <c r="H84" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" t="s">
         <v>23</v>
       </c>
-      <c r="J83" t="s">
-        <v>368</v>
-      </c>
-      <c r="K83" t="s">
-        <v>123</v>
-      </c>
-      <c r="L83" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>370</v>
-      </c>
-      <c r="B84" t="s">
-        <v>203</v>
-      </c>
-      <c r="C84" t="s">
-        <v>26</v>
-      </c>
-      <c r="D84" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" t="s">
-        <v>19</v>
-      </c>
-      <c r="F84" t="s">
-        <v>97</v>
-      </c>
-      <c r="G84" t="s">
-        <v>137</v>
-      </c>
-      <c r="H84" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" t="s">
-        <v>26</v>
-      </c>
       <c r="J84" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K84" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="L84" t="s">
         <v>26</v>
       </c>
       <c r="M84" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N84" t="s">
         <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G85" t="s">
         <v>21</v>
@@ -5616,83 +5664,83 @@
         <v>22</v>
       </c>
       <c r="I85" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J85" t="s">
-        <v>374</v>
+        <v>178</v>
       </c>
       <c r="K85" t="s">
-        <v>375</v>
+        <v>295</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
       </c>
       <c r="M85" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N85" t="s">
         <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>380</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D86" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G86" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
       </c>
       <c r="I86" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J86" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K86" t="s">
-        <v>375</v>
+        <v>25</v>
       </c>
       <c r="L86" t="s">
         <v>26</v>
       </c>
       <c r="M86" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N86" t="s">
-        <v>379</v>
+        <v>26</v>
       </c>
       <c r="O86" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
@@ -5701,7 +5749,7 @@
         <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G87" t="s">
         <v>21</v>
@@ -5713,10 +5761,10 @@
         <v>26</v>
       </c>
       <c r="J87" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K87" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="L87" t="s">
         <v>26</v>
@@ -5728,27 +5776,27 @@
         <v>26</v>
       </c>
       <c r="O87" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G88" t="s">
         <v>21</v>
@@ -5757,33 +5805,33 @@
         <v>22</v>
       </c>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K88" t="s">
-        <v>386</v>
+        <v>148</v>
       </c>
       <c r="L88" t="s">
         <v>26</v>
       </c>
       <c r="M88" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N88" t="s">
         <v>26</v>
       </c>
       <c r="O88" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="C89" t="s">
         <v>26</v>
@@ -5795,10 +5843,10 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="G89" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="H89" t="s">
         <v>22</v>
@@ -5807,10 +5855,10 @@
         <v>26</v>
       </c>
       <c r="J89" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K89" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
@@ -5822,18 +5870,18 @@
         <v>26</v>
       </c>
       <c r="O89" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
@@ -5842,10 +5890,10 @@
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G90" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H90" t="s">
         <v>22</v>
@@ -5854,10 +5902,10 @@
         <v>26</v>
       </c>
       <c r="J90" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K90" t="s">
-        <v>32</v>
+        <v>394</v>
       </c>
       <c r="L90" t="s">
         <v>26</v>
@@ -5869,18 +5917,18 @@
         <v>26</v>
       </c>
       <c r="O90" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -5889,10 +5937,10 @@
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="H91" t="s">
         <v>22</v>
@@ -5901,42 +5949,42 @@
         <v>23</v>
       </c>
       <c r="J91" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K91" t="s">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="L91" t="s">
         <v>26</v>
       </c>
       <c r="M91" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N91" t="s">
-        <v>26</v>
+        <v>398</v>
       </c>
       <c r="O91" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C92" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D92" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="G92" t="s">
         <v>21</v>
@@ -5945,13 +5993,13 @@
         <v>22</v>
       </c>
       <c r="I92" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J92" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K92" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="L92" t="s">
         <v>26</v>
@@ -5963,89 +6011,89 @@
         <v>26</v>
       </c>
       <c r="O92" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C93" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G93" t="s">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="H93" t="s">
         <v>22</v>
       </c>
       <c r="I93" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J93" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K93" t="s">
-        <v>75</v>
+        <v>405</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
       </c>
       <c r="M93" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N93" t="s">
         <v>26</v>
       </c>
       <c r="O93" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>52</v>
       </c>
       <c r="C94" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="D94" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E94" t="s">
         <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G94" t="s">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s">
         <v>22</v>
       </c>
       <c r="I94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J94" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K94" t="s">
-        <v>406</v>
+        <v>136</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
@@ -6057,30 +6105,30 @@
         <v>26</v>
       </c>
       <c r="O94" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B95" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G95" t="s">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s">
         <v>22</v>
@@ -6089,10 +6137,10 @@
         <v>26</v>
       </c>
       <c r="J95" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K95" t="s">
-        <v>411</v>
+        <v>67</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -6107,24 +6155,24 @@
         <v>412</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>413</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="D96" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G96" t="s">
         <v>21</v>
@@ -6133,25 +6181,213 @@
         <v>22</v>
       </c>
       <c r="I96" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J96" t="s">
         <v>414</v>
       </c>
       <c r="K96" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L96" t="s">
         <v>26</v>
       </c>
       <c r="M96" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="N96" t="s">
         <v>26</v>
       </c>
       <c r="O96" t="s">
         <v>415</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A97" t="s">
+        <v>416</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" t="s">
+        <v>61</v>
+      </c>
+      <c r="G97" t="s">
+        <v>21</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" t="s">
+        <v>417</v>
+      </c>
+      <c r="K97" t="s">
+        <v>209</v>
+      </c>
+      <c r="L97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" t="s">
+        <v>26</v>
+      </c>
+      <c r="O97" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A98" t="s">
+        <v>419</v>
+      </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98" t="s">
+        <v>143</v>
+      </c>
+      <c r="D98" t="s">
+        <v>60</v>
+      </c>
+      <c r="E98" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" t="s">
+        <v>61</v>
+      </c>
+      <c r="G98" t="s">
+        <v>420</v>
+      </c>
+      <c r="H98" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" t="s">
+        <v>421</v>
+      </c>
+      <c r="K98" t="s">
+        <v>106</v>
+      </c>
+      <c r="L98" t="s">
+        <v>26</v>
+      </c>
+      <c r="M98" t="s">
+        <v>26</v>
+      </c>
+      <c r="N98" t="s">
+        <v>26</v>
+      </c>
+      <c r="O98" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A99" t="s">
+        <v>423</v>
+      </c>
+      <c r="B99" t="s">
+        <v>224</v>
+      </c>
+      <c r="C99" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" t="s">
+        <v>124</v>
+      </c>
+      <c r="G99" t="s">
+        <v>354</v>
+      </c>
+      <c r="H99" t="s">
+        <v>22</v>
+      </c>
+      <c r="I99" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" t="s">
+        <v>424</v>
+      </c>
+      <c r="K99" t="s">
+        <v>425</v>
+      </c>
+      <c r="L99" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" t="s">
+        <v>26</v>
+      </c>
+      <c r="O99" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.75">
+      <c r="A100" t="s">
+        <v>427</v>
+      </c>
+      <c r="B100" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s">
+        <v>70</v>
+      </c>
+      <c r="F100" t="s">
+        <v>71</v>
+      </c>
+      <c r="G100" t="s">
+        <v>428</v>
+      </c>
+      <c r="H100" t="s">
+        <v>22</v>
+      </c>
+      <c r="I100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J100" t="s">
+        <v>429</v>
+      </c>
+      <c r="K100" t="s">
+        <v>430</v>
+      </c>
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" t="s">
+        <v>26</v>
+      </c>
+      <c r="N100" t="s">
+        <v>26</v>
+      </c>
+      <c r="O100" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31B68D0-F1E1-450E-AA17-88984930CEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F759F662-3CA2-4293-AB40-F4B219CACAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="431">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,132 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>04/10/2026 5:23:41 PM</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>Peyton Birchfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>I 20, Bossier City, LA, 71110</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445797e-6cd0-58ca-8001-1881473ac909</t>
+  </si>
+  <si>
+    <t>04/10/2026 10:36:38 AM</t>
+  </si>
+  <si>
+    <t>Truck 6</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Naples, TX, 75568</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457809-c12a-5a86-8703-a98b57a013e8</t>
+  </si>
+  <si>
+    <t>04/07/2026 5:09:08 PM</t>
+  </si>
+  <si>
+    <t>Truck 7</t>
+  </si>
+  <si>
+    <t>Mark Gwin</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Mansfield Road, Shreveport, LA, 71118</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544569fe-0661-5c57-9082-90a02dddf9ad</t>
+  </si>
+  <si>
+    <t>04/06/2026 1:45:01 PM</t>
+  </si>
+  <si>
+    <t>SV2</t>
+  </si>
+  <si>
+    <t>I 49, De Soto Parish, LA</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445641c-c872-5013-8cfe-321d5dbc917e</t>
+  </si>
+  <si>
+    <t>04/05/2026 11:42:36 AM</t>
+  </si>
+  <si>
+    <t>Robert Bailey</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Pedestrians, Light Traffic</t>
+  </si>
+  <si>
+    <t>Melissa H Mericle</t>
+  </si>
+  <si>
+    <t>226 Captain H M Shreve Boulevard, Shreveport, LA, 71115</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455e86-59ac-5113-965f-956c021ba3f1</t>
+  </si>
+  <si>
     <t>04/02/2026 11:35:15 AM</t>
   </si>
   <si>
@@ -74,33 +200,12 @@
     <t>Full fleet , Heavy Duty</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Melissa H Mericle</t>
-  </si>
-  <si>
     <t>US 82, Crossett, AR, 71635</t>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454f0c-8b48-5778-9894-6f4e6ae3b3a7</t>
   </si>
   <si>
@@ -128,9 +233,6 @@
     <t>Chris Mcconnell</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
     <t>Rolling Stop</t>
   </si>
   <si>
@@ -167,12 +269,6 @@
     <t>Daniel Vanwinterswyk</t>
   </si>
   <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
     <t>2796 East 70th Street, Shreveport, LA, 71105</t>
   </si>
   <si>
@@ -188,12 +284,6 @@
     <t>Truck 3</t>
   </si>
   <si>
-    <t>Mark Gwin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
     <t>2116 North Market Street, Shreveport, LA, 71107</t>
   </si>
   <si>
@@ -242,12 +332,6 @@
     <t>Josh Gregory</t>
   </si>
   <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>5258 I 20, West Monroe, LA, 71292</t>
   </si>
   <si>
@@ -272,12 +356,6 @@
     <t>03/23/2026 3:50:01 PM</t>
   </si>
   <si>
-    <t>Truck 6</t>
-  </si>
-  <si>
-    <t>Robert Bailey</t>
-  </si>
-  <si>
     <t>Parking Lot, Light Traffic</t>
   </si>
   <si>
@@ -320,9 +398,6 @@
     <t>03/17/2026 3:43:53 PM</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Pedestrians, Moderate Traffic</t>
   </si>
   <si>
@@ -383,9 +458,6 @@
     <t>03/14/2026 12:08:45 PM</t>
   </si>
   <si>
-    <t>SV1</t>
-  </si>
-  <si>
     <t>Paul Newton</t>
   </si>
   <si>
@@ -527,9 +599,6 @@
     <t>3199 Meriwether Road, Silver Pine Village, LA, 71108</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>0.55</t>
   </si>
   <si>
@@ -626,9 +695,6 @@
     <t>03/02/2026 8:56:51 AM</t>
   </si>
   <si>
-    <t>Peyton Birchfield</t>
-  </si>
-  <si>
     <t>3564 Hollywood Avenue, Shreveport, LA, 71109</t>
   </si>
   <si>
@@ -788,9 +854,6 @@
     <t>I 20, Shreveport, LA, 71129</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544553dc-12e3-544c-80bc-7dd059731cdd</t>
   </si>
   <si>
@@ -809,9 +872,6 @@
     <t>02/10/2026 6:57:07 AM</t>
   </si>
   <si>
-    <t>I 20, Bossier City, LA, 71110</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544547a0-82ec-51c5-87f1-265d7beb84d8</t>
   </si>
   <si>
@@ -905,9 +965,6 @@
     <t>02/03/2026 12:11:01 PM</t>
   </si>
   <si>
-    <t>Truck 7</t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
@@ -962,9 +1019,6 @@
     <t>Slightly Drowsy, Light Traffic, Night</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513b2-6b13-5d50-8752-aa8b3d86bef0</t>
   </si>
   <si>
@@ -1254,60 +1308,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b904-fd06-5276-b0e0-092aa28ca62b</t>
-  </si>
-  <si>
-    <t>01/12/2026 4:27:52 PM</t>
-  </si>
-  <si>
-    <t>2756 East 70th Street, Shreveport, LA, 71105</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b452-9ed7-5263-b375-a20676b51d14</t>
-  </si>
-  <si>
-    <t>01/09/2026 2:14:33 PM</t>
-  </si>
-  <si>
-    <t>Webster Parish, LA</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a465-7ee8-5170-8294-1c9038380db5</t>
-  </si>
-  <si>
-    <t>01/08/2026 10:40:54 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459e7b-889b-5526-a5ec-c0cec579590c</t>
-  </si>
-  <si>
-    <t>01/08/2026 8:04:36 AM</t>
-  </si>
-  <si>
-    <t>Truck 31</t>
-  </si>
-  <si>
-    <t>US 71;LA 1, Shreveport, LA, 71137</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459dec-7061-5fe2-9fcf-ddda463e90ec</t>
-  </si>
-  <si>
-    <t>01/08/2026 7:11:03 AM</t>
-  </si>
-  <si>
-    <t>323 Piney Forest Drive, Bossier Parish, LA, 71037</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459dbb-6a20-5450-afe3-28ca738169c3</t>
-  </si>
-  <si>
-    <t>01/05/2026 11:10:40 AM</t>
-  </si>
-  <si>
-    <t>Hanover Drive, Shreveport, LA, 71115</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f23-b62e-5f2b-8bdf-650b8e7f7b76</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1769,45 +1769,45 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
         <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="G3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
       <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
@@ -1816,30 +1816,30 @@
         <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1848,7 +1848,7 @@
         <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1857,130 +1857,130 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -1989,54 +1989,54 @@
         <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -2045,136 +2045,136 @@
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
         <v>21</v>
@@ -2183,48 +2183,48 @@
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -2233,286 +2233,286 @@
         <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="G17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K17" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="O17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
         <v>118</v>
@@ -2521,13 +2521,13 @@
         <v>119</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N18" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="O18" t="s">
         <v>120</v>
@@ -2538,43 +2538,43 @@
         <v>121</v>
       </c>
       <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
         <v>122</v>
       </c>
-      <c r="C19" t="s">
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>124</v>
       </c>
-      <c r="K19" t="s">
-        <v>89</v>
-      </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O19" t="s">
         <v>125</v>
@@ -2585,22 +2585,22 @@
         <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
         <v>127</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" t="s">
-        <v>21</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -2612,63 +2612,63 @@
         <v>128</v>
       </c>
       <c r="K20" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="O20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
         <v>30</v>
       </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" t="s">
-        <v>43</v>
-      </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K21" t="s">
         <v>133</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O21" t="s">
         <v>134</v>
@@ -2679,69 +2679,69 @@
         <v>135</v>
       </c>
       <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" t="s">
         <v>136</v>
       </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" t="s">
         <v>137</v>
       </c>
-      <c r="H22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" t="s">
         <v>138</v>
       </c>
-      <c r="K22" t="s">
+      <c r="O22" t="s">
         <v>139</v>
-      </c>
-      <c r="L22" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
         <v>141</v>
       </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
@@ -2756,13 +2756,13 @@
         <v>144</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="O23" t="s">
         <v>145</v>
@@ -2773,90 +2773,90 @@
         <v>146</v>
       </c>
       <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
         <v>147</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" t="s">
         <v>148</v>
       </c>
-      <c r="D24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" t="s">
-        <v>142</v>
-      </c>
-      <c r="H24" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" t="s">
-        <v>23</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
+        <v>115</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" t="s">
         <v>149</v>
-      </c>
-      <c r="K24" t="s">
-        <v>144</v>
-      </c>
-      <c r="L24" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
         <v>151</v>
       </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J25" t="s">
         <v>152</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O25" t="s">
         <v>153</v>
@@ -2867,69 +2867,69 @@
         <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
@@ -2938,192 +2938,192 @@
         <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K28" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" t="s">
+        <v>173</v>
+      </c>
+      <c r="K29" t="s">
         <v>168</v>
       </c>
-      <c r="G29" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J29" t="s">
-        <v>169</v>
-      </c>
-      <c r="K29" t="s">
-        <v>170</v>
-      </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="G30" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K30" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M30" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" t="s">
         <v>179</v>
@@ -3132,13 +3132,13 @@
         <v>180</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O31" t="s">
         <v>181</v>
@@ -3149,163 +3149,163 @@
         <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M32" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K33" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N33" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="G34" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K34" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="O34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
@@ -3314,139 +3314,139 @@
         <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K35" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G36" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K36" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>203</v>
+        <v>59</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J37" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K37" t="s">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N37" t="s">
-        <v>205</v>
+        <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -3455,139 +3455,139 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K38" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O38" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J39" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K39" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>218</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J40" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K40" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N40" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O40" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G41" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
@@ -3596,33 +3596,33 @@
         <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K41" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -3631,10 +3631,10 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -3643,74 +3643,74 @@
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K42" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N42" t="s">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="O42" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J43" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K43" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N43" t="s">
-        <v>227</v>
+        <v>23</v>
       </c>
       <c r="O43" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
@@ -3725,10 +3725,10 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
@@ -3737,224 +3737,224 @@
         <v>23</v>
       </c>
       <c r="J44" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K44" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="L44" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N44" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J45" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K45" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N45" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O45" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J46" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K46" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O46" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>243</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J47" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K47" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G48" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J48" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K48" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N48" t="s">
-        <v>26</v>
+        <v>249</v>
       </c>
       <c r="O48" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -3963,336 +3963,336 @@
         <v>38</v>
       </c>
       <c r="G49" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J49" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K49" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N49" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="G50" t="s">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J50" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K50" t="s">
-        <v>108</v>
+        <v>256</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N50" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O50" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="K51" t="s">
-        <v>89</v>
+        <v>260</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O51" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J52" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="K52" t="s">
-        <v>257</v>
+        <v>32</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N52" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O52" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G53" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H53" t="s">
         <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J53" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="K53" t="s">
-        <v>261</v>
+        <v>55</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O53" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>203</v>
+        <v>59</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G54" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="H54" t="s">
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J54" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K54" t="s">
-        <v>238</v>
+        <v>96</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O54" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>267</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
       </c>
       <c r="I55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K55" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O55" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="C56" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G56" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
@@ -4301,136 +4301,136 @@
         <v>23</v>
       </c>
       <c r="J56" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K56" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N56" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D57" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>177</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
-        <v>275</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J57" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K57" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N57" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O57" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K58" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O58" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="G59" t="s">
         <v>21</v>
@@ -4439,22 +4439,22 @@
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J59" t="s">
-        <v>283</v>
+        <v>24</v>
       </c>
       <c r="K59" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N59" t="s">
-        <v>205</v>
+        <v>23</v>
       </c>
       <c r="O59" t="s">
         <v>285</v>
@@ -4465,257 +4465,257 @@
         <v>286</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G60" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K60" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>291</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G61" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K61" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M61" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N61" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="G62" t="s">
-        <v>142</v>
+        <v>295</v>
       </c>
       <c r="H62" t="s">
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J62" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K62" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N62" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O62" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s">
-        <v>296</v>
+        <v>65</v>
       </c>
       <c r="C63" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F63" t="s">
-        <v>297</v>
+        <v>38</v>
       </c>
       <c r="G63" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
         <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>155</v>
+        <v>299</v>
       </c>
       <c r="K63" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N63" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O63" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>267</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J64" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K64" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N64" t="s">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="O64" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="D65" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="G65" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
@@ -4724,19 +4724,19 @@
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K65" t="s">
-        <v>306</v>
+        <v>96</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M65" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N65" t="s">
-        <v>307</v>
+        <v>23</v>
       </c>
       <c r="O65" t="s">
         <v>308</v>
@@ -4747,163 +4747,163 @@
         <v>309</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>203</v>
+        <v>59</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="H66" t="s">
         <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J66" t="s">
         <v>310</v>
       </c>
       <c r="K66" t="s">
+        <v>85</v>
+      </c>
+      <c r="L66" t="s">
+        <v>23</v>
+      </c>
+      <c r="M66" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" t="s">
+        <v>23</v>
+      </c>
+      <c r="O66" t="s">
         <v>311</v>
-      </c>
-      <c r="L66" t="s">
-        <v>26</v>
-      </c>
-      <c r="M66" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" t="s">
-        <v>26</v>
-      </c>
-      <c r="O66" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>312</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
+        <v>72</v>
+      </c>
+      <c r="G67" t="s">
+        <v>166</v>
+      </c>
+      <c r="H67" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" t="s">
+        <v>53</v>
+      </c>
+      <c r="J67" t="s">
         <v>313</v>
       </c>
-      <c r="B67" t="s">
-        <v>122</v>
-      </c>
-      <c r="C67" t="s">
-        <v>203</v>
-      </c>
-      <c r="D67" t="s">
-        <v>58</v>
-      </c>
-      <c r="E67" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" t="s">
-        <v>177</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="K67" t="s">
+        <v>115</v>
+      </c>
+      <c r="L67" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" t="s">
+        <v>23</v>
+      </c>
+      <c r="O67" t="s">
         <v>314</v>
-      </c>
-      <c r="H67" t="s">
-        <v>22</v>
-      </c>
-      <c r="I67" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" t="s">
-        <v>155</v>
-      </c>
-      <c r="K67" t="s">
-        <v>315</v>
-      </c>
-      <c r="L67" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>315</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" t="s">
+        <v>316</v>
+      </c>
+      <c r="G68" t="s">
+        <v>166</v>
+      </c>
+      <c r="H68" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" t="s">
+        <v>179</v>
+      </c>
+      <c r="K68" t="s">
         <v>317</v>
       </c>
-      <c r="B68" t="s">
-        <v>30</v>
-      </c>
-      <c r="C68" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" t="s">
-        <v>30</v>
-      </c>
-      <c r="F68" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="L68" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O68" t="s">
         <v>318</v>
-      </c>
-      <c r="H68" t="s">
-        <v>22</v>
-      </c>
-      <c r="I68" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" t="s">
-        <v>319</v>
-      </c>
-      <c r="K68" t="s">
-        <v>320</v>
-      </c>
-      <c r="L68" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" t="s">
-        <v>27</v>
-      </c>
-      <c r="N68" t="s">
-        <v>26</v>
-      </c>
-      <c r="O68" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B69" t="s">
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>287</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G69" t="s">
-        <v>323</v>
+        <v>30</v>
       </c>
       <c r="H69" t="s">
         <v>22</v>
@@ -4912,207 +4912,207 @@
         <v>23</v>
       </c>
       <c r="J69" t="s">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="K69" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N69" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O69" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>323</v>
+      </c>
+      <c r="B70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" t="s">
+        <v>291</v>
+      </c>
+      <c r="D70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70" t="s">
+        <v>136</v>
+      </c>
+      <c r="H70" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" t="s">
+        <v>53</v>
+      </c>
+      <c r="J70" t="s">
+        <v>324</v>
+      </c>
+      <c r="K70" t="s">
+        <v>325</v>
+      </c>
+      <c r="L70" t="s">
+        <v>23</v>
+      </c>
+      <c r="M70" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" t="s">
         <v>326</v>
       </c>
-      <c r="B70" t="s">
-        <v>122</v>
-      </c>
-      <c r="C70" t="s">
-        <v>203</v>
-      </c>
-      <c r="D70" t="s">
-        <v>58</v>
-      </c>
-      <c r="E70" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" t="s">
-        <v>177</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="O70" t="s">
         <v>327</v>
-      </c>
-      <c r="H70" t="s">
-        <v>22</v>
-      </c>
-      <c r="I70" t="s">
-        <v>26</v>
-      </c>
-      <c r="J70" t="s">
-        <v>328</v>
-      </c>
-      <c r="K70" t="s">
-        <v>180</v>
-      </c>
-      <c r="L70" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>328</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" t="s">
+        <v>329</v>
+      </c>
+      <c r="K71" t="s">
         <v>330</v>
       </c>
-      <c r="B71" t="s">
-        <v>56</v>
-      </c>
-      <c r="C71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" t="s">
-        <v>58</v>
-      </c>
-      <c r="E71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
-        <v>38</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="L71" t="s">
+        <v>23</v>
+      </c>
+      <c r="M71" t="s">
+        <v>23</v>
+      </c>
+      <c r="N71" t="s">
+        <v>23</v>
+      </c>
+      <c r="O71" t="s">
         <v>331</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" t="s">
-        <v>26</v>
-      </c>
-      <c r="J71" t="s">
-        <v>332</v>
-      </c>
-      <c r="K71" t="s">
-        <v>302</v>
-      </c>
-      <c r="L71" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O71" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>200</v>
+      </c>
+      <c r="G72" t="s">
+        <v>333</v>
+      </c>
+      <c r="H72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" t="s">
+        <v>179</v>
+      </c>
+      <c r="K72" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" t="s">
+        <v>23</v>
+      </c>
+      <c r="N72" t="s">
+        <v>23</v>
+      </c>
+      <c r="O72" t="s">
         <v>334</v>
-      </c>
-      <c r="B72" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" t="s">
-        <v>74</v>
-      </c>
-      <c r="D72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>50</v>
-      </c>
-      <c r="G72" t="s">
-        <v>142</v>
-      </c>
-      <c r="H72" t="s">
-        <v>22</v>
-      </c>
-      <c r="I72" t="s">
-        <v>26</v>
-      </c>
-      <c r="J72" t="s">
-        <v>335</v>
-      </c>
-      <c r="K72" t="s">
-        <v>66</v>
-      </c>
-      <c r="L72" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B73" t="s">
-        <v>296</v>
+        <v>65</v>
       </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F73" t="s">
         <v>38</v>
       </c>
       <c r="G73" t="s">
-        <v>137</v>
+        <v>336</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J73" t="s">
+        <v>337</v>
+      </c>
+      <c r="K73" t="s">
         <v>338</v>
       </c>
-      <c r="K73" t="s">
-        <v>40</v>
-      </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N73" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O73" t="s">
         <v>339</v>
@@ -5123,43 +5123,43 @@
         <v>340</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="C74" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="D74" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G74" t="s">
-        <v>137</v>
+        <v>341</v>
       </c>
       <c r="H74" t="s">
         <v>22</v>
       </c>
       <c r="I74" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J74" t="s">
-        <v>341</v>
+        <v>179</v>
       </c>
       <c r="K74" t="s">
         <v>342</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M74" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N74" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O74" t="s">
         <v>343</v>
@@ -5170,22 +5170,22 @@
         <v>344</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="C75" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="G75" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="H75" t="s">
         <v>22</v>
@@ -5194,33 +5194,33 @@
         <v>23</v>
       </c>
       <c r="J75" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K75" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="L75" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M75" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N75" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="C76" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -5229,10 +5229,10 @@
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G76" t="s">
-        <v>142</v>
+        <v>349</v>
       </c>
       <c r="H76" t="s">
         <v>22</v>
@@ -5241,66 +5241,66 @@
         <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K76" t="s">
-        <v>234</v>
+        <v>321</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N76" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O76" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C77" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D77" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>351</v>
+        <v>51</v>
       </c>
       <c r="G77" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H77" t="s">
         <v>22</v>
       </c>
       <c r="I77" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K77" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M77" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N77" t="s">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="O77" t="s">
         <v>354</v>
@@ -5311,398 +5311,398 @@
         <v>355</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G78" t="s">
+        <v>161</v>
+      </c>
+      <c r="H78" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" t="s">
         <v>356</v>
       </c>
-      <c r="H78" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" t="s">
-        <v>26</v>
-      </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
+        <v>74</v>
+      </c>
+      <c r="L78" t="s">
+        <v>23</v>
+      </c>
+      <c r="M78" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" t="s">
+        <v>23</v>
+      </c>
+      <c r="O78" t="s">
         <v>357</v>
-      </c>
-      <c r="K78" t="s">
-        <v>53</v>
-      </c>
-      <c r="L78" t="s">
-        <v>26</v>
-      </c>
-      <c r="M78" t="s">
-        <v>26</v>
-      </c>
-      <c r="N78" t="s">
-        <v>26</v>
-      </c>
-      <c r="O78" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>358</v>
+      </c>
+      <c r="B79" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" t="s">
+        <v>50</v>
+      </c>
+      <c r="E79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G79" t="s">
+        <v>161</v>
+      </c>
+      <c r="H79" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" t="s">
+        <v>53</v>
+      </c>
+      <c r="J79" t="s">
         <v>359</v>
       </c>
-      <c r="B79" t="s">
-        <v>116</v>
-      </c>
-      <c r="C79" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" t="s">
-        <v>26</v>
-      </c>
-      <c r="E79" t="s">
-        <v>19</v>
-      </c>
-      <c r="F79" t="s">
-        <v>177</v>
-      </c>
-      <c r="G79" t="s">
-        <v>314</v>
-      </c>
-      <c r="H79" t="s">
-        <v>22</v>
-      </c>
-      <c r="I79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>360</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" t="s">
+        <v>32</v>
+      </c>
+      <c r="N79" t="s">
+        <v>23</v>
+      </c>
+      <c r="O79" t="s">
         <v>361</v>
-      </c>
-      <c r="L79" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>362</v>
+      </c>
+      <c r="B80" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" t="s">
+        <v>172</v>
+      </c>
+      <c r="D80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>72</v>
+      </c>
+      <c r="G80" t="s">
+        <v>349</v>
+      </c>
+      <c r="H80" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" t="s">
+        <v>53</v>
+      </c>
+      <c r="J80" t="s">
         <v>363</v>
       </c>
-      <c r="B80" t="s">
-        <v>147</v>
-      </c>
-      <c r="C80" t="s">
-        <v>148</v>
-      </c>
-      <c r="D80" t="s">
-        <v>37</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
-        <v>177</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="K80" t="s">
+        <v>282</v>
+      </c>
+      <c r="L80" t="s">
+        <v>23</v>
+      </c>
+      <c r="M80" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80" t="s">
+        <v>23</v>
+      </c>
+      <c r="O80" t="s">
         <v>364</v>
-      </c>
-      <c r="H80" t="s">
-        <v>22</v>
-      </c>
-      <c r="I80" t="s">
-        <v>23</v>
-      </c>
-      <c r="J80" t="s">
-        <v>365</v>
-      </c>
-      <c r="K80" t="s">
-        <v>366</v>
-      </c>
-      <c r="L80" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>26</v>
-      </c>
-      <c r="O80" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B81" t="s">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D81" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E81" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="H81" t="s">
         <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J81" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K81" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M81" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N81" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O81" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>368</v>
+      </c>
+      <c r="B82" t="s">
+        <v>141</v>
+      </c>
+      <c r="C82" t="s">
+        <v>142</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>369</v>
+      </c>
+      <c r="G82" t="s">
+        <v>161</v>
+      </c>
+      <c r="H82" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" t="s">
+        <v>370</v>
+      </c>
+      <c r="K82" t="s">
+        <v>106</v>
+      </c>
+      <c r="L82" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" t="s">
+        <v>371</v>
+      </c>
+      <c r="O82" t="s">
         <v>372</v>
-      </c>
-      <c r="B82" t="s">
-        <v>369</v>
-      </c>
-      <c r="C82" t="s">
-        <v>26</v>
-      </c>
-      <c r="D82" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" t="s">
-        <v>58</v>
-      </c>
-      <c r="F82" t="s">
-        <v>50</v>
-      </c>
-      <c r="G82" t="s">
-        <v>21</v>
-      </c>
-      <c r="H82" t="s">
-        <v>22</v>
-      </c>
-      <c r="I82" t="s">
-        <v>26</v>
-      </c>
-      <c r="J82" t="s">
-        <v>373</v>
-      </c>
-      <c r="K82" t="s">
-        <v>374</v>
-      </c>
-      <c r="L82" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" t="s">
-        <v>26</v>
-      </c>
-      <c r="O82" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>373</v>
+      </c>
+      <c r="B83" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>72</v>
+      </c>
+      <c r="G83" t="s">
+        <v>374</v>
+      </c>
+      <c r="H83" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" t="s">
+        <v>375</v>
+      </c>
+      <c r="K83" t="s">
+        <v>85</v>
+      </c>
+      <c r="L83" t="s">
+        <v>23</v>
+      </c>
+      <c r="M83" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" t="s">
+        <v>23</v>
+      </c>
+      <c r="O83" t="s">
         <v>376</v>
-      </c>
-      <c r="B83" t="s">
-        <v>122</v>
-      </c>
-      <c r="C83" t="s">
-        <v>203</v>
-      </c>
-      <c r="D83" t="s">
-        <v>58</v>
-      </c>
-      <c r="E83" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" t="s">
-        <v>75</v>
-      </c>
-      <c r="G83" t="s">
-        <v>76</v>
-      </c>
-      <c r="H83" t="s">
-        <v>22</v>
-      </c>
-      <c r="I83" t="s">
-        <v>26</v>
-      </c>
-      <c r="J83" t="s">
-        <v>264</v>
-      </c>
-      <c r="K83" t="s">
-        <v>377</v>
-      </c>
-      <c r="L83" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>377</v>
+      </c>
+      <c r="B84" t="s">
+        <v>141</v>
+      </c>
+      <c r="C84" t="s">
+        <v>142</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>200</v>
+      </c>
+      <c r="G84" t="s">
+        <v>333</v>
+      </c>
+      <c r="H84" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" t="s">
+        <v>378</v>
+      </c>
+      <c r="K84" t="s">
         <v>379</v>
       </c>
-      <c r="B84" t="s">
-        <v>116</v>
-      </c>
-      <c r="C84" t="s">
-        <v>117</v>
-      </c>
-      <c r="D84" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" t="s">
-        <v>19</v>
-      </c>
-      <c r="F84" t="s">
-        <v>177</v>
-      </c>
-      <c r="G84" t="s">
-        <v>327</v>
-      </c>
-      <c r="H84" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" t="s">
-        <v>26</v>
-      </c>
-      <c r="J84" t="s">
+      <c r="L84" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" t="s">
         <v>380</v>
-      </c>
-      <c r="K84" t="s">
-        <v>78</v>
-      </c>
-      <c r="L84" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>381</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" t="s">
+        <v>172</v>
+      </c>
+      <c r="D85" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>200</v>
+      </c>
+      <c r="G85" t="s">
         <v>382</v>
       </c>
-      <c r="B85" t="s">
-        <v>85</v>
-      </c>
-      <c r="C85" t="s">
-        <v>86</v>
-      </c>
-      <c r="D85" t="s">
-        <v>37</v>
-      </c>
-      <c r="E85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F85" t="s">
-        <v>50</v>
-      </c>
-      <c r="G85" t="s">
-        <v>142</v>
-      </c>
       <c r="H85" t="s">
         <v>22</v>
       </c>
       <c r="I85" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J85" t="s">
         <v>383</v>
       </c>
       <c r="K85" t="s">
-        <v>200</v>
+        <v>384</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M85" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N85" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O85" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B86" t="s">
-        <v>296</v>
+        <v>387</v>
       </c>
       <c r="C86" t="s">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" t="s">
         <v>18</v>
       </c>
-      <c r="E86" t="s">
-        <v>19</v>
-      </c>
       <c r="F86" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G86" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
@@ -5711,139 +5711,139 @@
         <v>23</v>
       </c>
       <c r="J86" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K86" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M86" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N86" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O86" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>387</v>
       </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H87" t="s">
         <v>22</v>
       </c>
       <c r="I87" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J87" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K87" t="s">
-        <v>170</v>
+        <v>392</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M87" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N87" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O87" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H88" t="s">
         <v>22</v>
       </c>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="K88" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O88" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="H89" t="s">
         <v>22</v>
@@ -5852,139 +5852,139 @@
         <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K89" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O89" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="G90" t="s">
-        <v>398</v>
+        <v>166</v>
       </c>
       <c r="H90" t="s">
         <v>22</v>
       </c>
       <c r="I90" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J90" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K90" t="s">
-        <v>324</v>
+        <v>223</v>
       </c>
       <c r="L90" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M90" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N90" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O90" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="C91" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D91" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H91" t="s">
         <v>22</v>
       </c>
       <c r="I91" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J91" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K91" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O91" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B92" t="s">
         <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>287</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
         <v>22</v>
@@ -5993,168 +5993,168 @@
         <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K92" t="s">
-        <v>406</v>
+        <v>55</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M92" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N92" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O92" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>57</v>
+        <v>287</v>
       </c>
       <c r="D93" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G93" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="H93" t="s">
         <v>22</v>
       </c>
       <c r="I93" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J93" t="s">
-        <v>380</v>
+        <v>152</v>
       </c>
       <c r="K93" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M93" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N93" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O93" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B94" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C94" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D94" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E94" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="G94" t="s">
-        <v>398</v>
+        <v>30</v>
       </c>
       <c r="H94" t="s">
         <v>22</v>
       </c>
       <c r="I94" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J94" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K94" t="s">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O94" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B95" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="D95" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G95" t="s">
-        <v>51</v>
+        <v>416</v>
       </c>
       <c r="H95" t="s">
         <v>22</v>
       </c>
       <c r="I95" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J95" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K95" t="s">
-        <v>27</v>
+        <v>342</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M95" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N95" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O95" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B96" t="s">
         <v>16</v>
@@ -6172,7 +6172,7 @@
         <v>20</v>
       </c>
       <c r="G96" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="H96" t="s">
         <v>22</v>
@@ -6181,83 +6181,83 @@
         <v>23</v>
       </c>
       <c r="J96" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K96" t="s">
-        <v>119</v>
+        <v>330</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M96" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N96" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O96" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H97" t="s">
         <v>22</v>
       </c>
       <c r="I97" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J97" t="s">
-        <v>230</v>
+        <v>423</v>
       </c>
       <c r="K97" t="s">
-        <v>342</v>
+        <v>424</v>
       </c>
       <c r="L97" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M97" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N97" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O97" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B98" t="s">
-        <v>422</v>
+        <v>88</v>
       </c>
       <c r="C98" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D98" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E98" t="s">
         <v>19</v>
@@ -6266,124 +6266,77 @@
         <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H98" t="s">
         <v>22</v>
       </c>
       <c r="I98" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J98" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="K98" t="s">
-        <v>98</v>
+        <v>424</v>
       </c>
       <c r="L98" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M98" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N98" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O98" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B99" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C99" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="D99" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F99" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="G99" t="s">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="H99" t="s">
         <v>22</v>
       </c>
       <c r="I99" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="J99" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K99" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="L99" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M99" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N99" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O99" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>428</v>
-      </c>
-      <c r="B100" t="s">
-        <v>85</v>
-      </c>
-      <c r="C100" t="s">
-        <v>86</v>
-      </c>
-      <c r="D100" t="s">
-        <v>37</v>
-      </c>
-      <c r="E100" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" t="s">
-        <v>38</v>
-      </c>
-      <c r="G100" t="s">
-        <v>21</v>
-      </c>
-      <c r="H100" t="s">
-        <v>22</v>
-      </c>
-      <c r="I100" t="s">
-        <v>23</v>
-      </c>
-      <c r="J100" t="s">
-        <v>429</v>
-      </c>
-      <c r="K100" t="s">
-        <v>200</v>
-      </c>
-      <c r="L100" t="s">
-        <v>26</v>
-      </c>
-      <c r="M100" t="s">
-        <v>26</v>
-      </c>
-      <c r="N100" t="s">
-        <v>26</v>
-      </c>
-      <c r="O100" t="s">
         <v>430</v>
       </c>
     </row>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F759F662-3CA2-4293-AB40-F4B219CACAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6254EF3-4FF3-464F-8133-3238D77E3314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="415">
   <si>
     <t>Time</t>
   </si>
@@ -1260,54 +1260,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6e8-9159-56eb-822c-8fe322d043fd</t>
-  </si>
-  <si>
-    <t>01/18/2026 6:01:44 PM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Light Traffic</t>
-  </si>
-  <si>
-    <t>647 TX 7, Center, TX, 75954</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d38e-b73a-5a21-9ebe-d64f24cfc021</t>
-  </si>
-  <si>
-    <t>01/18/2026 10:55:21 AM</t>
-  </si>
-  <si>
-    <t>1573 Texas Avenue, Shreveport, LA, 71103</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d208-5a9a-5458-ac42-41c9c62bbaaa</t>
-  </si>
-  <si>
-    <t>01/16/2026 4:41:09 PM</t>
-  </si>
-  <si>
-    <t>7278 HWY 371, Coushatta, LA, 71019</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c8f8-3a80-507b-93bd-a3fc1615a5ca</t>
-  </si>
-  <si>
-    <t>01/15/2026 7:19:04 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c1cf-431e-5b2c-bc89-4936aaf42cb6</t>
-  </si>
-  <si>
-    <t>01/13/2026 2:21:10 PM</t>
-  </si>
-  <si>
-    <t>Joseph D. Waggonner Jr. Memorial Highway, Shreveport, LA, 71119</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b904-fd06-5276-b0e0-092aa28ca62b</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6105,241 +6057,6 @@
         <v>414</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>415</v>
-      </c>
-      <c r="B95" t="s">
-        <v>171</v>
-      </c>
-      <c r="C95" t="s">
-        <v>172</v>
-      </c>
-      <c r="D95" t="s">
-        <v>50</v>
-      </c>
-      <c r="E95" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" t="s">
-        <v>200</v>
-      </c>
-      <c r="G95" t="s">
-        <v>416</v>
-      </c>
-      <c r="H95" t="s">
-        <v>22</v>
-      </c>
-      <c r="I95" t="s">
-        <v>53</v>
-      </c>
-      <c r="J95" t="s">
-        <v>417</v>
-      </c>
-      <c r="K95" t="s">
-        <v>342</v>
-      </c>
-      <c r="L95" t="s">
-        <v>23</v>
-      </c>
-      <c r="M95" t="s">
-        <v>23</v>
-      </c>
-      <c r="N95" t="s">
-        <v>23</v>
-      </c>
-      <c r="O95" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>419</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="s">
-        <v>17</v>
-      </c>
-      <c r="D96" t="s">
-        <v>18</v>
-      </c>
-      <c r="E96" t="s">
-        <v>19</v>
-      </c>
-      <c r="F96" t="s">
-        <v>20</v>
-      </c>
-      <c r="G96" t="s">
-        <v>30</v>
-      </c>
-      <c r="H96" t="s">
-        <v>22</v>
-      </c>
-      <c r="I96" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" t="s">
-        <v>420</v>
-      </c>
-      <c r="K96" t="s">
-        <v>330</v>
-      </c>
-      <c r="L96" t="s">
-        <v>23</v>
-      </c>
-      <c r="M96" t="s">
-        <v>23</v>
-      </c>
-      <c r="N96" t="s">
-        <v>23</v>
-      </c>
-      <c r="O96" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>422</v>
-      </c>
-      <c r="B97" t="s">
-        <v>58</v>
-      </c>
-      <c r="C97" t="s">
-        <v>59</v>
-      </c>
-      <c r="D97" t="s">
-        <v>60</v>
-      </c>
-      <c r="E97" t="s">
-        <v>19</v>
-      </c>
-      <c r="F97" t="s">
-        <v>38</v>
-      </c>
-      <c r="G97" t="s">
-        <v>30</v>
-      </c>
-      <c r="H97" t="s">
-        <v>22</v>
-      </c>
-      <c r="I97" t="s">
-        <v>53</v>
-      </c>
-      <c r="J97" t="s">
-        <v>423</v>
-      </c>
-      <c r="K97" t="s">
-        <v>424</v>
-      </c>
-      <c r="L97" t="s">
-        <v>23</v>
-      </c>
-      <c r="M97" t="s">
-        <v>32</v>
-      </c>
-      <c r="N97" t="s">
-        <v>23</v>
-      </c>
-      <c r="O97" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>426</v>
-      </c>
-      <c r="B98" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" t="s">
-        <v>37</v>
-      </c>
-      <c r="D98" t="s">
-        <v>18</v>
-      </c>
-      <c r="E98" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" t="s">
-        <v>39</v>
-      </c>
-      <c r="H98" t="s">
-        <v>22</v>
-      </c>
-      <c r="I98" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" t="s">
-        <v>398</v>
-      </c>
-      <c r="K98" t="s">
-        <v>424</v>
-      </c>
-      <c r="L98" t="s">
-        <v>23</v>
-      </c>
-      <c r="M98" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" t="s">
-        <v>23</v>
-      </c>
-      <c r="O98" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>428</v>
-      </c>
-      <c r="B99" t="s">
-        <v>93</v>
-      </c>
-      <c r="C99" t="s">
-        <v>94</v>
-      </c>
-      <c r="D99" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" t="s">
-        <v>200</v>
-      </c>
-      <c r="G99" t="s">
-        <v>416</v>
-      </c>
-      <c r="H99" t="s">
-        <v>22</v>
-      </c>
-      <c r="I99" t="s">
-        <v>53</v>
-      </c>
-      <c r="J99" t="s">
-        <v>429</v>
-      </c>
-      <c r="K99" t="s">
-        <v>203</v>
-      </c>
-      <c r="L99" t="s">
-        <v>23</v>
-      </c>
-      <c r="M99" t="s">
-        <v>23</v>
-      </c>
-      <c r="N99" t="s">
-        <v>23</v>
-      </c>
-      <c r="O99" t="s">
-        <v>430</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6254EF3-4FF3-464F-8133-3238D77E3314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD3D4AB-BEFE-482A-B2D9-C4994F8FF175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="389">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,39 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>04/18/2026 1:57:17 AM</t>
+  </si>
+  <si>
+    <t>Truck 12</t>
+  </si>
+  <si>
+    <t>Kendall Mckerley</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Slightly Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>I 20, Haughton, LA, 71037</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459f61-26fd-5c26-9f57-0f4d1a54e66b</t>
+  </si>
+  <si>
     <t>04/10/2026 5:23:41 PM</t>
   </si>
   <si>
@@ -74,21 +107,12 @@
     <t xml:space="preserve">Full fleet </t>
   </si>
   <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Following Distance</t>
   </si>
   <si>
     <t>Construction, Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>I 20, Bossier City, LA, 71110</t>
   </si>
   <si>
@@ -416,9 +440,6 @@
     <t>03/17/2026 12:44:39 PM</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fce6-554c-5558-a57e-9e8a5b08a13c</t>
   </si>
   <si>
@@ -440,12 +461,6 @@
     <t>03/17/2026 8:14:03 AM</t>
   </si>
   <si>
-    <t>Truck 12</t>
-  </si>
-  <si>
-    <t>Kendall Mckerley</t>
-  </si>
-  <si>
     <t>I 20;US 71, Bossier City, LA, 71171</t>
   </si>
   <si>
@@ -617,9 +632,6 @@
     <t>03/05/2026 2:26:58 AM</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Slightly Drowsy, Construction, Light Traffic, Night</t>
   </si>
   <si>
@@ -1016,9 +1028,6 @@
     <t>01/31/2026 4:56:25 AM</t>
   </si>
   <si>
-    <t>Slightly Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513b2-6b13-5d50-8752-aa8b3d86bef0</t>
   </si>
   <si>
@@ -1173,93 +1182,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fde4-681c-591d-a5a7-20693eb12ed3</t>
-  </si>
-  <si>
-    <t>01/23/2026 1:35:38 PM</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>7784 Dixie Blanchard Road, Blanchard, LA, 71107</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ec5a-e3f7-5836-99a7-b446161cb7d1</t>
-  </si>
-  <si>
-    <t>01/23/2026 12:58:50 PM</t>
-  </si>
-  <si>
-    <t>3397 North Market Street, Shreveport, LA, 71107</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ec39-35b0-5622-b3a5-87c95d1f6514</t>
-  </si>
-  <si>
-    <t>01/22/2026 5:16:35 PM</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e7fe-d3e3-5f5f-af68-d06ddbb28f96</t>
-  </si>
-  <si>
-    <t>01/22/2026 12:11:30 AM</t>
-  </si>
-  <si>
-    <t>I 20, Haughton, LA, 71037</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e454-54c4-5a32-938f-5051b5d2e9af</t>
-  </si>
-  <si>
-    <t>01/21/2026 5:03:03 PM</t>
-  </si>
-  <si>
-    <t>Donald Tynes, Natchitoches Parish, LA</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e2cc-112c-5297-beb7-92d38141ff31</t>
-  </si>
-  <si>
-    <t>01/20/2026 10:25:40 AM</t>
-  </si>
-  <si>
-    <t>Frances Street, Shreveport, LA, 71129</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dc39-e4c8-5d2f-bb3a-0ecc90f63838</t>
-  </si>
-  <si>
-    <t>01/20/2026 7:22:21 AM</t>
-  </si>
-  <si>
-    <t>6525 West 70th Street, Shreveport, LA, 71129</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445db92-1291-5968-8d3b-4ec180368445</t>
-  </si>
-  <si>
-    <t>01/19/2026 10:44:43 AM</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d724-fc47-55aa-990c-75f27643a447</t>
-  </si>
-  <si>
-    <t>01/19/2026 9:38:44 AM</t>
-  </si>
-  <si>
-    <t>800 East Washington Street, Shreveport, LA, 71104</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6e8-9159-56eb-822c-8fe322d043fd</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1712,69 +1634,69 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -1788,40 +1710,40 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
         <v>41</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>23</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
@@ -1835,806 +1757,806 @@
         <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
       </c>
       <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
         <v>53</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>54</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" t="s">
         <v>55</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>57</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>58</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
         <v>59</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
         <v>38</v>
       </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
       <c r="H8" t="s">
         <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
         <v>38</v>
       </c>
-      <c r="G10" t="s">
-        <v>77</v>
-      </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
         <v>38</v>
       </c>
-      <c r="G14" t="s">
-        <v>30</v>
-      </c>
       <c r="H14" t="s">
         <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
         <v>112</v>
       </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
         <v>58</v>
       </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>60</v>
-      </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M18" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="K21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -2643,219 +2565,219 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N22" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="O22" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N23" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="O23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
         <v>148</v>
       </c>
       <c r="K24" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="O24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K25" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K26" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O26" t="s">
         <v>158</v>
@@ -2866,66 +2788,66 @@
         <v>159</v>
       </c>
       <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" t="s">
         <v>160</v>
       </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
       <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
         <v>161</v>
       </c>
-      <c r="H27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>162</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" t="s">
         <v>163</v>
-      </c>
-      <c r="L27" t="s">
-        <v>23</v>
-      </c>
-      <c r="M27" t="s">
-        <v>23</v>
-      </c>
-      <c r="N27" t="s">
-        <v>23</v>
-      </c>
-      <c r="O27" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" t="s">
         <v>165</v>
       </c>
-      <c r="B28" t="s">
-        <v>58</v>
-      </c>
       <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
         <v>59</v>
-      </c>
-      <c r="D28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
       </c>
       <c r="G28" t="s">
         <v>166</v>
@@ -2934,7 +2856,7 @@
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
         <v>167</v>
@@ -2943,13 +2865,13 @@
         <v>168</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O28" t="s">
         <v>169</v>
@@ -2960,43 +2882,43 @@
         <v>170</v>
       </c>
       <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
         <v>171</v>
       </c>
-      <c r="C29" t="s">
+      <c r="H29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>61</v>
+      </c>
+      <c r="J29" t="s">
         <v>172</v>
       </c>
-      <c r="D29" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" t="s">
-        <v>166</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" t="s">
-        <v>53</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>173</v>
       </c>
-      <c r="K29" t="s">
-        <v>168</v>
-      </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O29" t="s">
         <v>174</v>
@@ -3007,122 +2929,122 @@
         <v>175</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J30" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K30" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K31" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
         <v>59</v>
       </c>
-      <c r="D32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
-      </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
         <v>184</v>
@@ -3131,13 +3053,13 @@
         <v>185</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O32" t="s">
         <v>186</v>
@@ -3148,19 +3070,19 @@
         <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G33" t="s">
         <v>188</v>
@@ -3169,69 +3091,69 @@
         <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
         <v>189</v>
       </c>
       <c r="K33" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K34" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N34" t="s">
-        <v>194</v>
+        <v>18</v>
       </c>
       <c r="O34" t="s">
         <v>195</v>
@@ -3242,122 +3164,122 @@
         <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
+        <v>197</v>
+      </c>
+      <c r="G35" t="s">
         <v>38</v>
       </c>
-      <c r="G35" t="s">
-        <v>77</v>
-      </c>
       <c r="H35" t="s">
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M35" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="O35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="G36" t="s">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
         <v>202</v>
       </c>
       <c r="K36" t="s">
+        <v>137</v>
+      </c>
+      <c r="L36" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N36" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36" t="s">
         <v>203</v>
-      </c>
-      <c r="L36" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" t="s">
         <v>205</v>
       </c>
-      <c r="B37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" t="s">
-        <v>30</v>
-      </c>
       <c r="H37" t="s">
         <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
         <v>206</v>
@@ -3366,13 +3288,13 @@
         <v>207</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M37" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O37" t="s">
         <v>208</v>
@@ -3383,28 +3305,28 @@
         <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G38" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J38" t="s">
         <v>210</v>
@@ -3413,13 +3335,13 @@
         <v>211</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O38" t="s">
         <v>212</v>
@@ -3430,28 +3352,28 @@
         <v>213</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="G39" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
         <v>214</v>
@@ -3460,13 +3382,13 @@
         <v>215</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O39" t="s">
         <v>216</v>
@@ -3477,43 +3399,43 @@
         <v>217</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" t="s">
+        <v>166</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" t="s">
         <v>218</v>
       </c>
-      <c r="D40" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>38</v>
-      </c>
-      <c r="G40" t="s">
-        <v>30</v>
-      </c>
-      <c r="H40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" t="s">
-        <v>53</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>219</v>
       </c>
-      <c r="K40" t="s">
-        <v>144</v>
-      </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O40" t="s">
         <v>220</v>
@@ -3524,43 +3446,43 @@
         <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E41" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G41" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K41" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O41" t="s">
         <v>224</v>
@@ -3571,43 +3493,43 @@
         <v>225</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G42" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s">
         <v>226</v>
       </c>
       <c r="K42" t="s">
-        <v>85</v>
+        <v>227</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N42" t="s">
-        <v>227</v>
+        <v>18</v>
       </c>
       <c r="O42" t="s">
         <v>228</v>
@@ -3618,90 +3540,90 @@
         <v>229</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
         <v>230</v>
       </c>
       <c r="K43" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M43" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>231</v>
       </c>
       <c r="O43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="G44" t="s">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J44" t="s">
         <v>234</v>
       </c>
       <c r="K44" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O44" t="s">
         <v>235</v>
@@ -3712,137 +3634,137 @@
         <v>236</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>237</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K45" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O45" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G46" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K46" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
         <v>244</v>
       </c>
       <c r="K47" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O47" t="s">
         <v>245</v>
@@ -3853,137 +3775,137 @@
         <v>246</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>247</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K48" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" t="s">
         <v>249</v>
-      </c>
-      <c r="O48" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>250</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" t="s">
+        <v>38</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s">
         <v>251</v>
       </c>
-      <c r="B49" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>38</v>
-      </c>
-      <c r="G49" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>252</v>
       </c>
-      <c r="K49" t="s">
-        <v>133</v>
-      </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M49" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N49" t="s">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="O49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K50" t="s">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="L50" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M50" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N50" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O50" t="s">
         <v>257</v>
@@ -3994,28 +3916,28 @@
         <v>258</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J51" t="s">
         <v>259</v>
@@ -4024,13 +3946,13 @@
         <v>260</v>
       </c>
       <c r="L51" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N51" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O51" t="s">
         <v>261</v>
@@ -4041,325 +3963,325 @@
         <v>262</v>
       </c>
       <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" t="s">
         <v>28</v>
       </c>
-      <c r="C52" t="s">
-        <v>49</v>
-      </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>237</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J52" t="s">
         <v>263</v>
       </c>
       <c r="K52" t="s">
-        <v>32</v>
+        <v>264</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O52" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G53" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="H53" t="s">
         <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K53" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H54" t="s">
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K54" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
       </c>
       <c r="I55" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K55" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>237</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K56" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O56" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
         <v>59</v>
       </c>
-      <c r="D57" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>38</v>
       </c>
-      <c r="G57" t="s">
-        <v>30</v>
-      </c>
       <c r="H57" t="s">
         <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K57" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M57" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O57" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B58" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G58" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J58" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K58" t="s">
-        <v>282</v>
+        <v>33</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N58" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O58" t="s">
         <v>283</v>
@@ -4370,7 +4292,7 @@
         <v>284</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
@@ -4382,78 +4304,78 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="K59" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O59" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J60" t="s">
-        <v>288</v>
+        <v>32</v>
       </c>
       <c r="K60" t="s">
-        <v>115</v>
+        <v>264</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O60" t="s">
         <v>289</v>
@@ -4464,43 +4386,43 @@
         <v>290</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
         <v>291</v>
       </c>
       <c r="D61" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J61" t="s">
         <v>292</v>
       </c>
       <c r="K61" t="s">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N61" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O61" t="s">
         <v>293</v>
@@ -4511,43 +4433,43 @@
         <v>294</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>295</v>
       </c>
       <c r="D62" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="G62" t="s">
-        <v>295</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J62" t="s">
         <v>296</v>
       </c>
       <c r="K62" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O62" t="s">
         <v>297</v>
@@ -4558,43 +4480,43 @@
         <v>298</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E63" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>299</v>
       </c>
       <c r="H63" t="s">
         <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K63" t="s">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M63" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O63" t="s">
         <v>301</v>
@@ -4605,28 +4527,28 @@
         <v>302</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
         <v>303</v>
@@ -4635,13 +4557,13 @@
         <v>304</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M64" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N64" t="s">
-        <v>227</v>
+        <v>18</v>
       </c>
       <c r="O64" t="s">
         <v>305</v>
@@ -4652,66 +4574,66 @@
         <v>306</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>72</v>
+        <v>197</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
       </c>
       <c r="I65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
         <v>307</v>
       </c>
       <c r="K65" t="s">
-        <v>96</v>
+        <v>308</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N65" t="s">
-        <v>23</v>
+        <v>231</v>
       </c>
       <c r="O65" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B66" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s">
         <v>166</v>
@@ -4720,116 +4642,116 @@
         <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K66" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O66" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
+        <v>67</v>
+      </c>
+      <c r="D67" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
         <v>59</v>
       </c>
-      <c r="D67" t="s">
-        <v>60</v>
-      </c>
-      <c r="E67" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" t="s">
-        <v>72</v>
-      </c>
       <c r="G67" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J67" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K67" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="L67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O67" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J68" t="s">
-        <v>179</v>
+        <v>317</v>
       </c>
       <c r="K68" t="s">
-        <v>317</v>
+        <v>123</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O68" t="s">
         <v>318</v>
@@ -4840,43 +4762,43 @@
         <v>319</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>287</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="H69" t="s">
         <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J69" t="s">
-        <v>320</v>
+        <v>184</v>
       </c>
       <c r="K69" t="s">
         <v>321</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M69" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N69" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O69" t="s">
         <v>322</v>
@@ -4887,28 +4809,28 @@
         <v>323</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
         <v>291</v>
       </c>
       <c r="D70" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="H70" t="s">
         <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J70" t="s">
         <v>324</v>
@@ -4917,60 +4839,60 @@
         <v>325</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M70" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N70" t="s">
+        <v>18</v>
+      </c>
+      <c r="O70" t="s">
         <v>326</v>
-      </c>
-      <c r="O70" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>327</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" t="s">
+        <v>295</v>
+      </c>
+      <c r="D71" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>37</v>
+      </c>
+      <c r="G71" t="s">
+        <v>143</v>
+      </c>
+      <c r="H71" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" t="s">
+        <v>61</v>
+      </c>
+      <c r="J71" t="s">
         <v>328</v>
       </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" t="s">
-        <v>18</v>
-      </c>
-      <c r="E71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" t="s">
-        <v>39</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" t="s">
-        <v>23</v>
-      </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>329</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
+        <v>18</v>
+      </c>
+      <c r="M71" t="s">
+        <v>18</v>
+      </c>
+      <c r="N71" t="s">
         <v>330</v>
-      </c>
-      <c r="L71" t="s">
-        <v>23</v>
-      </c>
-      <c r="M71" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" t="s">
-        <v>23</v>
       </c>
       <c r="O71" t="s">
         <v>331</v>
@@ -4981,278 +4903,278 @@
         <v>332</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
+        <v>47</v>
+      </c>
+      <c r="H72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s">
         <v>333</v>
       </c>
-      <c r="H72" t="s">
-        <v>22</v>
-      </c>
-      <c r="I72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J72" t="s">
-        <v>179</v>
-      </c>
       <c r="K72" t="s">
-        <v>46</v>
+        <v>334</v>
       </c>
       <c r="L72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B73" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J73" t="s">
+        <v>184</v>
+      </c>
+      <c r="K73" t="s">
+        <v>54</v>
+      </c>
+      <c r="L73" t="s">
+        <v>18</v>
+      </c>
+      <c r="M73" t="s">
+        <v>18</v>
+      </c>
+      <c r="N73" t="s">
+        <v>18</v>
+      </c>
+      <c r="O73" t="s">
         <v>337</v>
-      </c>
-      <c r="K73" t="s">
-        <v>338</v>
-      </c>
-      <c r="L73" t="s">
-        <v>23</v>
-      </c>
-      <c r="M73" t="s">
-        <v>32</v>
-      </c>
-      <c r="N73" t="s">
-        <v>23</v>
-      </c>
-      <c r="O73" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>338</v>
+      </c>
+      <c r="B74" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>73</v>
+      </c>
+      <c r="F74" t="s">
+        <v>46</v>
+      </c>
+      <c r="G74" t="s">
+        <v>339</v>
+      </c>
+      <c r="H74" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" t="s">
         <v>340</v>
       </c>
-      <c r="B74" t="s">
-        <v>58</v>
-      </c>
-      <c r="C74" t="s">
-        <v>59</v>
-      </c>
-      <c r="D74" t="s">
-        <v>60</v>
-      </c>
-      <c r="E74" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" t="s">
-        <v>51</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="K74" t="s">
         <v>341</v>
       </c>
-      <c r="H74" t="s">
-        <v>22</v>
-      </c>
-      <c r="I74" t="s">
-        <v>53</v>
-      </c>
-      <c r="J74" t="s">
-        <v>179</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="L74" t="s">
+        <v>18</v>
+      </c>
+      <c r="M74" t="s">
+        <v>40</v>
+      </c>
+      <c r="N74" t="s">
+        <v>18</v>
+      </c>
+      <c r="O74" t="s">
         <v>342</v>
-      </c>
-      <c r="L74" t="s">
-        <v>23</v>
-      </c>
-      <c r="M74" t="s">
-        <v>23</v>
-      </c>
-      <c r="N74" t="s">
-        <v>23</v>
-      </c>
-      <c r="O74" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>343</v>
+      </c>
+      <c r="B75" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" t="s">
+        <v>67</v>
+      </c>
+      <c r="D75" t="s">
+        <v>68</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" t="s">
         <v>344</v>
       </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" t="s">
-        <v>18</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
-        <v>200</v>
-      </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" t="s">
+        <v>61</v>
+      </c>
+      <c r="J75" t="s">
+        <v>184</v>
+      </c>
+      <c r="K75" t="s">
         <v>345</v>
       </c>
-      <c r="H75" t="s">
-        <v>22</v>
-      </c>
-      <c r="I75" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" t="s">
+      <c r="L75" t="s">
+        <v>18</v>
+      </c>
+      <c r="M75" t="s">
+        <v>18</v>
+      </c>
+      <c r="N75" t="s">
+        <v>18</v>
+      </c>
+      <c r="O75" t="s">
         <v>346</v>
-      </c>
-      <c r="K75" t="s">
-        <v>203</v>
-      </c>
-      <c r="L75" t="s">
-        <v>23</v>
-      </c>
-      <c r="M75" t="s">
-        <v>23</v>
-      </c>
-      <c r="N75" t="s">
-        <v>23</v>
-      </c>
-      <c r="O75" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" t="s">
         <v>348</v>
       </c>
-      <c r="B76" t="s">
-        <v>88</v>
-      </c>
-      <c r="C76" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" t="s">
-        <v>72</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" t="s">
         <v>349</v>
       </c>
-      <c r="H76" t="s">
-        <v>22</v>
-      </c>
-      <c r="I76" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
+        <v>207</v>
+      </c>
+      <c r="L76" t="s">
+        <v>18</v>
+      </c>
+      <c r="M76" t="s">
+        <v>18</v>
+      </c>
+      <c r="N76" t="s">
+        <v>18</v>
+      </c>
+      <c r="O76" t="s">
         <v>350</v>
-      </c>
-      <c r="K76" t="s">
-        <v>321</v>
-      </c>
-      <c r="L76" t="s">
-        <v>23</v>
-      </c>
-      <c r="M76" t="s">
-        <v>23</v>
-      </c>
-      <c r="N76" t="s">
-        <v>23</v>
-      </c>
-      <c r="O76" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" t="s">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s">
         <v>352</v>
       </c>
-      <c r="B77" t="s">
-        <v>103</v>
-      </c>
-      <c r="C77" t="s">
-        <v>104</v>
-      </c>
-      <c r="D77" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" t="s">
-        <v>51</v>
-      </c>
-      <c r="G77" t="s">
-        <v>166</v>
-      </c>
       <c r="H77" t="s">
         <v>22</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J77" t="s">
         <v>353</v>
       </c>
       <c r="K77" t="s">
-        <v>96</v>
+        <v>325</v>
       </c>
       <c r="L77" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M77" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N77" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O77" t="s">
         <v>354</v>
@@ -5263,43 +5185,43 @@
         <v>355</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G78" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H78" t="s">
         <v>22</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
         <v>356</v>
       </c>
       <c r="K78" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="L78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O78" t="s">
         <v>357</v>
@@ -5310,90 +5232,90 @@
         <v>358</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H79" t="s">
         <v>22</v>
       </c>
       <c r="I79" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s">
         <v>359</v>
       </c>
       <c r="K79" t="s">
+        <v>82</v>
+      </c>
+      <c r="L79" t="s">
+        <v>18</v>
+      </c>
+      <c r="M79" t="s">
+        <v>18</v>
+      </c>
+      <c r="N79" t="s">
+        <v>18</v>
+      </c>
+      <c r="O79" t="s">
         <v>360</v>
-      </c>
-      <c r="L79" t="s">
-        <v>23</v>
-      </c>
-      <c r="M79" t="s">
-        <v>32</v>
-      </c>
-      <c r="N79" t="s">
-        <v>23</v>
-      </c>
-      <c r="O79" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>361</v>
+      </c>
+      <c r="B80" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>46</v>
+      </c>
+      <c r="G80" t="s">
+        <v>166</v>
+      </c>
+      <c r="H80" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" t="s">
+        <v>61</v>
+      </c>
+      <c r="J80" t="s">
         <v>362</v>
       </c>
-      <c r="B80" t="s">
-        <v>171</v>
-      </c>
-      <c r="C80" t="s">
-        <v>172</v>
-      </c>
-      <c r="D80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
-        <v>72</v>
-      </c>
-      <c r="G80" t="s">
-        <v>349</v>
-      </c>
-      <c r="H80" t="s">
-        <v>22</v>
-      </c>
-      <c r="I80" t="s">
-        <v>53</v>
-      </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>363</v>
       </c>
-      <c r="K80" t="s">
-        <v>282</v>
-      </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M80" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N80" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O80" t="s">
         <v>364</v>
@@ -5404,43 +5326,43 @@
         <v>365</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s">
-        <v>166</v>
+        <v>352</v>
       </c>
       <c r="H81" t="s">
         <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J81" t="s">
         <v>366</v>
       </c>
       <c r="K81" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M81" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N81" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O81" t="s">
         <v>367</v>
@@ -5451,610 +5373,234 @@
         <v>368</v>
       </c>
       <c r="B82" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C82" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
       </c>
       <c r="F82" t="s">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s">
+        <v>171</v>
+      </c>
+      <c r="H82" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" t="s">
+        <v>61</v>
+      </c>
+      <c r="J82" t="s">
         <v>369</v>
       </c>
-      <c r="G82" t="s">
-        <v>161</v>
-      </c>
-      <c r="H82" t="s">
-        <v>22</v>
-      </c>
-      <c r="I82" t="s">
-        <v>23</v>
-      </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
+        <v>260</v>
+      </c>
+      <c r="L82" t="s">
+        <v>18</v>
+      </c>
+      <c r="M82" t="s">
+        <v>18</v>
+      </c>
+      <c r="N82" t="s">
+        <v>18</v>
+      </c>
+      <c r="O82" t="s">
         <v>370</v>
-      </c>
-      <c r="K82" t="s">
-        <v>106</v>
-      </c>
-      <c r="L82" t="s">
-        <v>23</v>
-      </c>
-      <c r="M82" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" t="s">
-        <v>371</v>
-      </c>
-      <c r="O82" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>371</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>372</v>
+      </c>
+      <c r="G83" t="s">
+        <v>166</v>
+      </c>
+      <c r="H83" t="s">
+        <v>22</v>
+      </c>
+      <c r="I83" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" t="s">
         <v>373</v>
       </c>
-      <c r="B83" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" t="s">
-        <v>37</v>
-      </c>
-      <c r="D83" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" t="s">
-        <v>72</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="K83" t="s">
+        <v>114</v>
+      </c>
+      <c r="L83" t="s">
+        <v>18</v>
+      </c>
+      <c r="M83" t="s">
+        <v>18</v>
+      </c>
+      <c r="N83" t="s">
         <v>374</v>
       </c>
-      <c r="H83" t="s">
-        <v>22</v>
-      </c>
-      <c r="I83" t="s">
-        <v>23</v>
-      </c>
-      <c r="J83" t="s">
+      <c r="O83" t="s">
         <v>375</v>
-      </c>
-      <c r="K83" t="s">
-        <v>85</v>
-      </c>
-      <c r="L83" t="s">
-        <v>23</v>
-      </c>
-      <c r="M83" t="s">
-        <v>23</v>
-      </c>
-      <c r="N83" t="s">
-        <v>23</v>
-      </c>
-      <c r="O83" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>376</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s">
         <v>377</v>
       </c>
-      <c r="B84" t="s">
-        <v>141</v>
-      </c>
-      <c r="C84" t="s">
-        <v>142</v>
-      </c>
-      <c r="D84" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" t="s">
-        <v>19</v>
-      </c>
-      <c r="F84" t="s">
-        <v>200</v>
-      </c>
-      <c r="G84" t="s">
-        <v>333</v>
-      </c>
       <c r="H84" t="s">
         <v>22</v>
       </c>
       <c r="I84" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s">
         <v>378</v>
       </c>
       <c r="K84" t="s">
+        <v>93</v>
+      </c>
+      <c r="L84" t="s">
+        <v>18</v>
+      </c>
+      <c r="M84" t="s">
+        <v>18</v>
+      </c>
+      <c r="N84" t="s">
+        <v>18</v>
+      </c>
+      <c r="O84" t="s">
         <v>379</v>
-      </c>
-      <c r="L84" t="s">
-        <v>23</v>
-      </c>
-      <c r="M84" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" t="s">
-        <v>23</v>
-      </c>
-      <c r="O84" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>380</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" t="s">
         <v>381</v>
       </c>
-      <c r="B85" t="s">
-        <v>171</v>
-      </c>
-      <c r="C85" t="s">
-        <v>172</v>
-      </c>
-      <c r="D85" t="s">
-        <v>50</v>
-      </c>
-      <c r="E85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F85" t="s">
-        <v>200</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="K85" t="s">
         <v>382</v>
       </c>
-      <c r="H85" t="s">
-        <v>22</v>
-      </c>
-      <c r="I85" t="s">
-        <v>53</v>
-      </c>
-      <c r="J85" t="s">
+      <c r="L85" t="s">
+        <v>18</v>
+      </c>
+      <c r="M85" t="s">
+        <v>18</v>
+      </c>
+      <c r="N85" t="s">
+        <v>18</v>
+      </c>
+      <c r="O85" t="s">
         <v>383</v>
-      </c>
-      <c r="K85" t="s">
-        <v>384</v>
-      </c>
-      <c r="L85" t="s">
-        <v>23</v>
-      </c>
-      <c r="M85" t="s">
-        <v>23</v>
-      </c>
-      <c r="N85" t="s">
-        <v>23</v>
-      </c>
-      <c r="O85" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>384</v>
+      </c>
+      <c r="B86" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" t="s">
+        <v>177</v>
+      </c>
+      <c r="D86" t="s">
+        <v>58</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" t="s">
+        <v>385</v>
+      </c>
+      <c r="H86" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" t="s">
+        <v>61</v>
+      </c>
+      <c r="J86" t="s">
         <v>386</v>
       </c>
-      <c r="B86" t="s">
+      <c r="K86" t="s">
         <v>387</v>
       </c>
-      <c r="C86" t="s">
-        <v>23</v>
-      </c>
-      <c r="D86" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" t="s">
-        <v>51</v>
-      </c>
-      <c r="G86" t="s">
-        <v>30</v>
-      </c>
-      <c r="H86" t="s">
-        <v>22</v>
-      </c>
-      <c r="I86" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" t="s">
+      <c r="L86" t="s">
+        <v>18</v>
+      </c>
+      <c r="M86" t="s">
+        <v>18</v>
+      </c>
+      <c r="N86" t="s">
+        <v>18</v>
+      </c>
+      <c r="O86" t="s">
         <v>388</v>
-      </c>
-      <c r="K86" t="s">
-        <v>304</v>
-      </c>
-      <c r="L86" t="s">
-        <v>23</v>
-      </c>
-      <c r="M86" t="s">
-        <v>23</v>
-      </c>
-      <c r="N86" t="s">
-        <v>23</v>
-      </c>
-      <c r="O86" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>390</v>
-      </c>
-      <c r="B87" t="s">
-        <v>387</v>
-      </c>
-      <c r="C87" t="s">
-        <v>23</v>
-      </c>
-      <c r="D87" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" t="s">
-        <v>51</v>
-      </c>
-      <c r="G87" t="s">
-        <v>30</v>
-      </c>
-      <c r="H87" t="s">
-        <v>22</v>
-      </c>
-      <c r="I87" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" t="s">
-        <v>391</v>
-      </c>
-      <c r="K87" t="s">
-        <v>392</v>
-      </c>
-      <c r="L87" t="s">
-        <v>23</v>
-      </c>
-      <c r="M87" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" t="s">
-        <v>23</v>
-      </c>
-      <c r="O87" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>394</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" t="s">
-        <v>39</v>
-      </c>
-      <c r="H88" t="s">
-        <v>22</v>
-      </c>
-      <c r="I88" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" t="s">
-        <v>24</v>
-      </c>
-      <c r="K88" t="s">
-        <v>395</v>
-      </c>
-      <c r="L88" t="s">
-        <v>23</v>
-      </c>
-      <c r="M88" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" t="s">
-        <v>23</v>
-      </c>
-      <c r="O88" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>397</v>
-      </c>
-      <c r="B89" t="s">
-        <v>141</v>
-      </c>
-      <c r="C89" t="s">
-        <v>142</v>
-      </c>
-      <c r="D89" t="s">
-        <v>23</v>
-      </c>
-      <c r="E89" t="s">
-        <v>19</v>
-      </c>
-      <c r="F89" t="s">
-        <v>200</v>
-      </c>
-      <c r="G89" t="s">
-        <v>345</v>
-      </c>
-      <c r="H89" t="s">
-        <v>22</v>
-      </c>
-      <c r="I89" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" t="s">
-        <v>398</v>
-      </c>
-      <c r="K89" t="s">
-        <v>106</v>
-      </c>
-      <c r="L89" t="s">
-        <v>23</v>
-      </c>
-      <c r="M89" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" t="s">
-        <v>23</v>
-      </c>
-      <c r="O89" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>400</v>
-      </c>
-      <c r="B90" t="s">
-        <v>28</v>
-      </c>
-      <c r="C90" t="s">
-        <v>49</v>
-      </c>
-      <c r="D90" t="s">
-        <v>50</v>
-      </c>
-      <c r="E90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" t="s">
-        <v>51</v>
-      </c>
-      <c r="G90" t="s">
-        <v>166</v>
-      </c>
-      <c r="H90" t="s">
-        <v>22</v>
-      </c>
-      <c r="I90" t="s">
-        <v>53</v>
-      </c>
-      <c r="J90" t="s">
-        <v>401</v>
-      </c>
-      <c r="K90" t="s">
-        <v>223</v>
-      </c>
-      <c r="L90" t="s">
-        <v>23</v>
-      </c>
-      <c r="M90" t="s">
-        <v>23</v>
-      </c>
-      <c r="N90" t="s">
-        <v>23</v>
-      </c>
-      <c r="O90" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>403</v>
-      </c>
-      <c r="B91" t="s">
-        <v>36</v>
-      </c>
-      <c r="C91" t="s">
-        <v>218</v>
-      </c>
-      <c r="D91" t="s">
-        <v>60</v>
-      </c>
-      <c r="E91" t="s">
-        <v>19</v>
-      </c>
-      <c r="F91" t="s">
-        <v>51</v>
-      </c>
-      <c r="G91" t="s">
-        <v>113</v>
-      </c>
-      <c r="H91" t="s">
-        <v>22</v>
-      </c>
-      <c r="I91" t="s">
-        <v>53</v>
-      </c>
-      <c r="J91" t="s">
-        <v>404</v>
-      </c>
-      <c r="K91" t="s">
-        <v>321</v>
-      </c>
-      <c r="L91" t="s">
-        <v>23</v>
-      </c>
-      <c r="M91" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" t="s">
-        <v>23</v>
-      </c>
-      <c r="O91" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>406</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="s">
-        <v>287</v>
-      </c>
-      <c r="D92" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" t="s">
-        <v>19</v>
-      </c>
-      <c r="F92" t="s">
-        <v>72</v>
-      </c>
-      <c r="G92" t="s">
-        <v>30</v>
-      </c>
-      <c r="H92" t="s">
-        <v>22</v>
-      </c>
-      <c r="I92" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" t="s">
-        <v>407</v>
-      </c>
-      <c r="K92" t="s">
-        <v>55</v>
-      </c>
-      <c r="L92" t="s">
-        <v>23</v>
-      </c>
-      <c r="M92" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" t="s">
-        <v>23</v>
-      </c>
-      <c r="O92" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>409</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="s">
-        <v>287</v>
-      </c>
-      <c r="D93" t="s">
-        <v>23</v>
-      </c>
-      <c r="E93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" t="s">
-        <v>72</v>
-      </c>
-      <c r="G93" t="s">
-        <v>30</v>
-      </c>
-      <c r="H93" t="s">
-        <v>22</v>
-      </c>
-      <c r="I93" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" t="s">
-        <v>152</v>
-      </c>
-      <c r="K93" t="s">
-        <v>410</v>
-      </c>
-      <c r="L93" t="s">
-        <v>23</v>
-      </c>
-      <c r="M93" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" t="s">
-        <v>23</v>
-      </c>
-      <c r="O93" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>412</v>
-      </c>
-      <c r="B94" t="s">
-        <v>58</v>
-      </c>
-      <c r="C94" t="s">
-        <v>59</v>
-      </c>
-      <c r="D94" t="s">
-        <v>60</v>
-      </c>
-      <c r="E94" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" t="s">
-        <v>51</v>
-      </c>
-      <c r="G94" t="s">
-        <v>30</v>
-      </c>
-      <c r="H94" t="s">
-        <v>22</v>
-      </c>
-      <c r="I94" t="s">
-        <v>53</v>
-      </c>
-      <c r="J94" t="s">
-        <v>413</v>
-      </c>
-      <c r="K94" t="s">
-        <v>256</v>
-      </c>
-      <c r="L94" t="s">
-        <v>23</v>
-      </c>
-      <c r="M94" t="s">
-        <v>23</v>
-      </c>
-      <c r="N94" t="s">
-        <v>23</v>
-      </c>
-      <c r="O94" t="s">
-        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD3D4AB-BEFE-482A-B2D9-C4994F8FF175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26E8C65A-B3D3-4BBA-B032-889665F6535E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="1635" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="349">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,156 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>05/02/2026 12:19:44 PM</t>
+  </si>
+  <si>
+    <t>Truck 1</t>
+  </si>
+  <si>
+    <t>John Arnold</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>I 49, Brown Park Estates, LA, 71106</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e9b4-0f61-5508-ac64-ec6a03919a24</t>
+  </si>
+  <si>
+    <t>05/01/2026 4:32:04 PM</t>
+  </si>
+  <si>
+    <t>Truck 60</t>
+  </si>
+  <si>
+    <t>Daniel Vanwinterswyk</t>
+  </si>
+  <si>
+    <t>Full fleet , Heavy Duty</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Shreveport, LA, 71103</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e574-b7a1-5e28-96a1-5bf164776383</t>
+  </si>
+  <si>
+    <t>04/28/2026 5:47:36 PM</t>
+  </si>
+  <si>
+    <t>Truck 22</t>
+  </si>
+  <si>
+    <t>Josh Gregory</t>
+  </si>
+  <si>
+    <t>Construction, Passengers, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>1512 East Bert Kouns Industrial Loop, Shreveport, LA, 71105</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d646-c988-5cd9-a47e-8bafc996366e</t>
+  </si>
+  <si>
+    <t>04/27/2026 5:32:25 AM</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>3901 Hilry Huckaby III Avenue, Shreveport, LA, 71107</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ce7f-5702-59fe-b50c-fbf25865a2dc</t>
+  </si>
+  <si>
+    <t>04/24/2026 5:24:06 PM</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>Peyton Birchfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t>Construction, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Bossier City, LA, 71110</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c197-d662-5f98-875f-828cba2d84a2</t>
+  </si>
+  <si>
+    <t>04/24/2026 5:02:20 PM</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>Jason Scott</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Swan Lake Spur, Bossier City, LA, 71110</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c183-e715-5584-8f77-10fa858fef63</t>
+  </si>
+  <si>
     <t>04/18/2026 1:57:17 AM</t>
   </si>
   <si>
@@ -71,51 +221,24 @@
     <t>Kendall Mckerley</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Drowsiness</t>
   </si>
   <si>
     <t>Slightly Drowsy, Light Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>I 20, Haughton, LA, 71037</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459f61-26fd-5c26-9f57-0f4d1a54e66b</t>
   </si>
   <si>
     <t>04/10/2026 5:23:41 PM</t>
   </si>
   <si>
-    <t>SV1</t>
-  </si>
-  <si>
-    <t>Peyton Birchfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
     <t>Construction, Light Traffic</t>
   </si>
   <si>
-    <t>I 20, Bossier City, LA, 71110</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
@@ -131,15 +254,9 @@
     <t>Harsh Brake</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>Naples, TX, 75568</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>0.86</t>
   </si>
   <si>
@@ -155,12 +272,6 @@
     <t>Mark Gwin</t>
   </si>
   <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>Mansfield Road, Shreveport, LA, 71118</t>
   </si>
   <si>
@@ -191,12 +302,6 @@
     <t>Robert Bailey</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
     <t>Pedestrians, Light Traffic</t>
   </si>
   <si>
@@ -221,9 +326,6 @@
     <t>Chico Leone</t>
   </si>
   <si>
-    <t>Full fleet , Heavy Duty</t>
-  </si>
-  <si>
     <t>US 82, Crossett, AR, 71635</t>
   </si>
   <si>
@@ -287,12 +389,6 @@
     <t>03/26/2026 4:42:38 PM</t>
   </si>
   <si>
-    <t>Truck 60</t>
-  </si>
-  <si>
-    <t>Daniel Vanwinterswyk</t>
-  </si>
-  <si>
     <t>2796 East 70th Street, Shreveport, LA, 71105</t>
   </si>
   <si>
@@ -311,9 +407,6 @@
     <t>2116 North Market Street, Shreveport, LA, 71107</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ad5-4050-5cbe-b8a4-8aff22a8fa37</t>
   </si>
   <si>
@@ -323,9 +416,6 @@
     <t>S2</t>
   </si>
   <si>
-    <t>Jason Scott</t>
-  </si>
-  <si>
     <t>590 Dowling Street, Shreveport, LA, 71101</t>
   </si>
   <si>
@@ -350,18 +440,9 @@
     <t>03/24/2026 9:24:17 AM</t>
   </si>
   <si>
-    <t>Truck 22</t>
-  </si>
-  <si>
-    <t>Josh Gregory</t>
-  </si>
-  <si>
     <t>5258 I 20, West Monroe, LA, 71292</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445203b-696f-5cf3-bdab-5d778e998dc8</t>
   </si>
   <si>
@@ -413,9 +494,6 @@
     <t>7101 US 79, River Hill, TX, 75639</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450799-f498-5512-add6-e9823215d7df</t>
   </si>
   <si>
@@ -515,9 +593,6 @@
     <t>Truck 23</t>
   </si>
   <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
     <t>911 TX 147, McClelland, TX, 75935</t>
   </si>
   <si>
@@ -650,9 +725,6 @@
     <t>3531 Highway 157, Bossier Parish, LA, 71051</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b5d8-96fd-5a76-a6f1-c869c6291cf5</t>
   </si>
   <si>
@@ -902,9 +974,6 @@
     <t>02/07/2026 8:24:25 AM</t>
   </si>
   <si>
-    <t>John Arnold</t>
-  </si>
-  <si>
     <t>256 Montgomery Street, Shreveport, LA, 71107</t>
   </si>
   <si>
@@ -977,9 +1046,6 @@
     <t>02/03/2026 12:11:01 PM</t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>34</t>
   </si>
   <si>
@@ -996,192 +1062,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523b6-3878-57eb-a332-fbf8ba64a1c5</t>
-  </si>
-  <si>
-    <t>02/02/2026 4:29:47 PM</t>
-  </si>
-  <si>
-    <t>2125 Hollywood Avenue, Shreveport, LA, 71108</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452079-ed44-5004-af2e-e0ab31526ef2</t>
-  </si>
-  <si>
-    <t>02/02/2026 7:08:41 AM</t>
-  </si>
-  <si>
-    <t>Bossier City, LA</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e78-3b4b-591a-a7d7-9564465fa6aa</t>
-  </si>
-  <si>
-    <t>01/31/2026 4:56:25 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513b2-6b13-5d50-8752-aa8b3d86bef0</t>
-  </si>
-  <si>
-    <t>01/30/2026 10:51:20 PM</t>
-  </si>
-  <si>
-    <t>Wet Road, Passengers, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>447 Greenacres Boulevard, Bossier City, LA, 71111</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451264-2b4d-56a0-b3cd-dd6e70621dac</t>
-  </si>
-  <si>
-    <t>01/30/2026 7:05:17 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450f02-0a9e-5e8b-9f01-161cd27e4452</t>
-  </si>
-  <si>
-    <t>01/29/2026 2:55:08 AM</t>
-  </si>
-  <si>
-    <t>Moderately Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>744 Winfield Road, Bossier Parish, LA, 71067</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544508f6-a7aa-52cf-a161-5fbecefa6c5f</t>
-  </si>
-  <si>
-    <t>01/29/2026 1:31:17 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>2907 Amherst Street, Shreveport, LA, 71108</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544508a9-e540-52ff-9756-353c82232761</t>
-  </si>
-  <si>
-    <t>01/28/2026 1:16:03 PM</t>
-  </si>
-  <si>
-    <t>1331 Highway 3074, Lincoln Parish, LA, 71245</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450608-c242-51c6-a803-02bc9a65849b</t>
-  </si>
-  <si>
-    <t>01/27/2026 9:48:21 PM</t>
-  </si>
-  <si>
-    <t>183 Piney Forest Drive, Bossier Parish, LA, 71037</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544502b7-6f47-5f28-9e8a-c84192be9d2f</t>
-  </si>
-  <si>
-    <t>01/27/2026 8:20:22 PM</t>
-  </si>
-  <si>
-    <t>I 20, Tallulah, LA</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450266-e184-5b68-8bd9-9b0ce0b55a67</t>
-  </si>
-  <si>
-    <t>01/27/2026 7:05:50 PM</t>
-  </si>
-  <si>
-    <t>552 Gould Boulevard, Lake Providence, LA, 71254</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450222-a57a-50a0-a344-42f71385bbc9</t>
-  </si>
-  <si>
-    <t>01/27/2026 3:18:33 PM</t>
-  </si>
-  <si>
-    <t>East Pine, Castor, LA, 71076</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450152-8fee-5f78-b5e6-3eb9f01e9a0f</t>
-  </si>
-  <si>
-    <t>01/27/2026 4:57:29 AM</t>
-  </si>
-  <si>
-    <t>Crash</t>
-  </si>
-  <si>
-    <t>I 20, Rayville, LA, 71269</t>
-  </si>
-  <si>
-    <t>2.19</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff19-f3c1-57dc-a875-9d9fe4cd46f9</t>
-  </si>
-  <si>
-    <t>01/27/2026 4:10:43 AM</t>
-  </si>
-  <si>
-    <t>Snowy Road, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>299 West Georgia Avenue, Ruston, LA, 71270</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445feef-247a-5c81-96df-ab6ac9479a63</t>
-  </si>
-  <si>
-    <t>01/26/2026 11:37:24 PM</t>
-  </si>
-  <si>
-    <t>I 20, Choudrant, LA, 71270</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdf4-e979-5d7e-8dbe-4df5ef5e5cd6</t>
-  </si>
-  <si>
-    <t>01/26/2026 11:19:23 PM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Snowy Road, Moderate Traffic, Night</t>
-  </si>
-  <si>
-    <t>I 20, Grambling, LA, 71272</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fde4-681c-591d-a5a7-20693eb12ed3</t>
   </si>
 </sst>
 </file>
@@ -1558,7 +1438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1634,242 +1514,242 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
       <c r="N4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>48</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
         <v>49</v>
-      </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
         <v>51</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J7" t="s">
         <v>62</v>
@@ -1878,13 +1758,13 @@
         <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
         <v>64</v>
@@ -1901,37 +1781,37 @@
         <v>67</v>
       </c>
       <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
         <v>68</v>
       </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
@@ -1942,216 +1822,216 @@
         <v>72</v>
       </c>
       <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
         <v>73</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
       <c r="H9" t="s">
         <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" t="s">
         <v>74</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" t="s">
         <v>75</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="K10" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
         <v>80</v>
       </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="O10" t="s">
         <v>81</v>
-      </c>
-      <c r="K10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
         <v>84</v>
       </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>85</v>
       </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>86</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" t="s">
         <v>87</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>40</v>
-      </c>
-      <c r="N11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
         <v>89</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
         <v>90</v>
       </c>
-      <c r="C12" t="s">
+      <c r="K12" t="s">
         <v>91</v>
       </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" t="s">
         <v>92</v>
-      </c>
-      <c r="K12" t="s">
-        <v>93</v>
-      </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s">
         <v>95</v>
       </c>
-      <c r="B13" t="s">
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
         <v>96</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
       </c>
       <c r="J13" t="s">
         <v>97</v>
@@ -2160,13 +2040,13 @@
         <v>98</v>
       </c>
       <c r="L13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
         <v>99</v>
@@ -2183,22 +2063,22 @@
         <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s">
         <v>103</v>
@@ -2207,13 +2087,13 @@
         <v>104</v>
       </c>
       <c r="L14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
         <v>105</v>
@@ -2224,57 +2104,57 @@
         <v>106</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -2283,266 +2163,266 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K19" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="L19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N21" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="O21" t="s">
         <v>139</v>
@@ -2553,90 +2433,90 @@
         <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K22" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J23" t="s">
         <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="L23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="O23" t="s">
         <v>146</v>
@@ -2647,10 +2527,10 @@
         <v>147</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -2659,609 +2539,609 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L24" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="O24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J25" t="s">
         <v>153</v>
       </c>
       <c r="K25" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
         <v>96</v>
       </c>
-      <c r="C26" t="s">
-        <v>156</v>
-      </c>
-      <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>80</v>
-      </c>
-      <c r="G26" t="s">
-        <v>38</v>
-      </c>
-      <c r="H26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" t="s">
-        <v>61</v>
-      </c>
       <c r="J26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K26" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="L26" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="O27" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" t="s">
         <v>167</v>
-      </c>
-      <c r="K28" t="s">
-        <v>168</v>
-      </c>
-      <c r="L28" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" t="s">
-        <v>18</v>
-      </c>
-      <c r="N28" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" t="s">
         <v>170</v>
       </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="K29" t="s">
+        <v>150</v>
+      </c>
+      <c r="L29" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" t="s">
         <v>171</v>
       </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" t="s">
-        <v>61</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="O29" t="s">
         <v>172</v>
-      </c>
-      <c r="K29" t="s">
-        <v>173</v>
-      </c>
-      <c r="L29" t="s">
-        <v>18</v>
-      </c>
-      <c r="M29" t="s">
-        <v>18</v>
-      </c>
-      <c r="N29" t="s">
-        <v>18</v>
-      </c>
-      <c r="O29" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" t="s">
+        <v>174</v>
+      </c>
+      <c r="K30" t="s">
         <v>175</v>
       </c>
-      <c r="B30" t="s">
+      <c r="L30" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" t="s">
+        <v>164</v>
+      </c>
+      <c r="O30" t="s">
         <v>176</v>
-      </c>
-      <c r="C30" t="s">
-        <v>177</v>
-      </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" t="s">
-        <v>171</v>
-      </c>
-      <c r="H30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" t="s">
-        <v>61</v>
-      </c>
-      <c r="J30" t="s">
-        <v>178</v>
-      </c>
-      <c r="K30" t="s">
-        <v>173</v>
-      </c>
-      <c r="L30" t="s">
-        <v>18</v>
-      </c>
-      <c r="M30" t="s">
-        <v>18</v>
-      </c>
-      <c r="N30" t="s">
-        <v>18</v>
-      </c>
-      <c r="O30" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>96</v>
+      </c>
+      <c r="J31" t="s">
+        <v>179</v>
+      </c>
+      <c r="K31" t="s">
+        <v>150</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" t="s">
         <v>180</v>
-      </c>
-      <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" t="s">
-        <v>80</v>
-      </c>
-      <c r="G31" t="s">
-        <v>166</v>
-      </c>
-      <c r="H31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" t="s">
-        <v>61</v>
-      </c>
-      <c r="J31" t="s">
-        <v>181</v>
-      </c>
-      <c r="K31" t="s">
-        <v>93</v>
-      </c>
-      <c r="L31" t="s">
-        <v>18</v>
-      </c>
-      <c r="M31" t="s">
-        <v>18</v>
-      </c>
-      <c r="N31" t="s">
-        <v>18</v>
-      </c>
-      <c r="O31" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>182</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" t="s">
         <v>183</v>
       </c>
-      <c r="B32" t="s">
-        <v>165</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" t="s">
-        <v>85</v>
-      </c>
-      <c r="H32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
+        <v>134</v>
+      </c>
+      <c r="L32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" t="s">
         <v>184</v>
-      </c>
-      <c r="K32" t="s">
-        <v>185</v>
-      </c>
-      <c r="L32" t="s">
-        <v>18</v>
-      </c>
-      <c r="M32" t="s">
-        <v>18</v>
-      </c>
-      <c r="N32" t="s">
-        <v>18</v>
-      </c>
-      <c r="O32" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
         <v>187</v>
       </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="K33" t="s">
         <v>188</v>
       </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" t="s">
-        <v>61</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="L33" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" t="s">
         <v>189</v>
-      </c>
-      <c r="K33" t="s">
-        <v>190</v>
-      </c>
-      <c r="L33" t="s">
-        <v>18</v>
-      </c>
-      <c r="M33" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
         <v>192</v>
       </c>
-      <c r="B34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>80</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="K34" t="s">
         <v>193</v>
       </c>
-      <c r="H34" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" t="s">
-        <v>61</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="L34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" t="s">
         <v>194</v>
-      </c>
-      <c r="K34" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" t="s">
-        <v>18</v>
-      </c>
-      <c r="M34" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" t="s">
         <v>196</v>
       </c>
-      <c r="B35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" t="s">
         <v>197</v>
       </c>
-      <c r="G35" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" t="s">
-        <v>61</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>198</v>
       </c>
-      <c r="K35" t="s">
-        <v>63</v>
-      </c>
       <c r="L35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N35" t="s">
+        <v>23</v>
+      </c>
+      <c r="O35" t="s">
         <v>199</v>
-      </c>
-      <c r="O35" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" t="s">
         <v>201</v>
       </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>202</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K36" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="L36" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N36" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -3270,110 +3150,110 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="G37" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J37" t="s">
         <v>206</v>
       </c>
       <c r="K37" t="s">
+        <v>125</v>
+      </c>
+      <c r="L37" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" t="s">
+        <v>23</v>
+      </c>
+      <c r="O37" t="s">
         <v>207</v>
-      </c>
-      <c r="L37" t="s">
-        <v>18</v>
-      </c>
-      <c r="M37" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G38" t="s">
+        <v>119</v>
+      </c>
+      <c r="H38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" t="s">
         <v>209</v>
       </c>
-      <c r="B38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" t="s">
-        <v>61</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>210</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" t="s">
         <v>211</v>
-      </c>
-      <c r="L38" t="s">
-        <v>18</v>
-      </c>
-      <c r="M38" t="s">
-        <v>40</v>
-      </c>
-      <c r="N38" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" t="s">
         <v>213</v>
       </c>
-      <c r="B39" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" t="s">
-        <v>121</v>
-      </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J39" t="s">
         <v>214</v>
@@ -3382,13 +3262,13 @@
         <v>215</v>
       </c>
       <c r="L39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O39" t="s">
         <v>216</v>
@@ -3399,43 +3279,43 @@
         <v>217</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="G40" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K40" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O40" t="s">
         <v>220</v>
@@ -3446,90 +3326,90 @@
         <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
         <v>222</v>
       </c>
-      <c r="D41" t="s">
-        <v>68</v>
-      </c>
-      <c r="E41" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" t="s">
-        <v>46</v>
-      </c>
       <c r="G41" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J41" t="s">
         <v>223</v>
       </c>
       <c r="K41" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="L41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N41" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="O41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K42" t="s">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O42" t="s">
         <v>228</v>
@@ -3540,762 +3420,762 @@
         <v>229</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K43" t="s">
-        <v>93</v>
+        <v>232</v>
       </c>
       <c r="L43" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N43" t="s">
-        <v>231</v>
+        <v>23</v>
       </c>
       <c r="O43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K44" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G45" t="s">
-        <v>237</v>
+        <v>148</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J45" t="s">
         <v>238</v>
       </c>
       <c r="K45" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="L45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K46" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="L46" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N46" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O46" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J47" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K47" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="L47" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N47" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B48" t="s">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G48" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J48" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K48" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="L48" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N48" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O48" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J49" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K49" t="s">
-        <v>252</v>
+        <v>125</v>
       </c>
       <c r="L49" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N49" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O49" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J50" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L50" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N50" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O50" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
         <v>68</v>
       </c>
-      <c r="E51" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" t="s">
-        <v>80</v>
-      </c>
       <c r="G51" t="s">
-        <v>38</v>
+        <v>261</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K51" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="L51" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N51" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G52" t="s">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J52" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K52" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="L52" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N52" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G53" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="H53" t="s">
         <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K53" t="s">
-        <v>40</v>
+        <v>251</v>
       </c>
       <c r="L53" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M53" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N53" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
+        <v>45</v>
+      </c>
+      <c r="G54" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" t="s">
         <v>96</v>
       </c>
-      <c r="C54" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" t="s">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s">
-        <v>171</v>
-      </c>
-      <c r="H54" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" t="s">
-        <v>18</v>
-      </c>
       <c r="J54" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K54" t="s">
-        <v>63</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N54" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O54" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
       </c>
       <c r="I55" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K55" t="s">
-        <v>104</v>
+        <v>276</v>
       </c>
       <c r="L55" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>18</v>
+        <v>277</v>
       </c>
       <c r="O55" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" t="s">
         <v>96</v>
       </c>
-      <c r="C56" t="s">
-        <v>45</v>
-      </c>
-      <c r="D56" t="s">
-        <v>29</v>
-      </c>
-      <c r="E56" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" t="s">
-        <v>237</v>
-      </c>
-      <c r="H56" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" t="s">
-        <v>18</v>
-      </c>
       <c r="J56" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L56" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N56" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B57" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G57" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K57" t="s">
-        <v>123</v>
+        <v>284</v>
       </c>
       <c r="L57" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N57" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O57" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C58" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D58" t="s">
+        <v>53</v>
+      </c>
+      <c r="E58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" t="s">
         <v>68</v>
       </c>
-      <c r="E58" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" t="s">
-        <v>46</v>
-      </c>
       <c r="G58" t="s">
-        <v>38</v>
+        <v>261</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>288</v>
       </c>
       <c r="L58" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N58" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O58" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -4304,642 +4184,642 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G59" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J59" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="K59" t="s">
-        <v>286</v>
+        <v>35</v>
       </c>
       <c r="L59" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M59" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N59" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O59" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="G60" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="K60" t="s">
-        <v>264</v>
+        <v>98</v>
       </c>
       <c r="L60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>102</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G61" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J61" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K61" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M61" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N61" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="H62" t="s">
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K62" t="s">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="L62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O62" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G63" t="s">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="H63" t="s">
         <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K63" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N63" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O63" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G64" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J64" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K64" t="s">
-        <v>304</v>
+        <v>74</v>
       </c>
       <c r="L64" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N64" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O64" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>201</v>
       </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="G65" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
       </c>
       <c r="I65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K65" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N65" t="s">
-        <v>231</v>
+        <v>23</v>
       </c>
       <c r="O65" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="H66" t="s">
         <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J66" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="K66" t="s">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="L66" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M66" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N66" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O66" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G67" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J67" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K67" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="L67" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M67" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N67" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O67" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G68" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J68" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K68" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="L68" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M68" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N68" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O68" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="D69" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>320</v>
+        <v>68</v>
       </c>
       <c r="G69" t="s">
-        <v>171</v>
+        <v>322</v>
       </c>
       <c r="H69" t="s">
         <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J69" t="s">
-        <v>184</v>
+        <v>323</v>
       </c>
       <c r="K69" t="s">
-        <v>321</v>
+        <v>163</v>
       </c>
       <c r="L69" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N69" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O69" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="C70" t="s">
-        <v>291</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="F70" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="G70" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
         <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J70" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K70" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M70" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O70" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C71" t="s">
-        <v>295</v>
+        <v>52</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>37</v>
+        <v>222</v>
       </c>
       <c r="G71" t="s">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="H71" t="s">
         <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="J71" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K71" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L71" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M71" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N71" t="s">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="O71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="D72" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="G72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H72" t="s">
         <v>22</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K72" t="s">
-        <v>334</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M72" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N72" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O72" t="s">
         <v>335</v>
@@ -4950,657 +4830,187 @@
         <v>336</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G73" t="s">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J73" t="s">
-        <v>184</v>
+        <v>337</v>
       </c>
       <c r="K73" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="L73" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N73" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O73" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C74" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="G74" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="H74" t="s">
         <v>22</v>
       </c>
       <c r="I74" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="J74" t="s">
         <v>340</v>
       </c>
       <c r="K74" t="s">
+        <v>150</v>
+      </c>
+      <c r="L74" t="s">
+        <v>23</v>
+      </c>
+      <c r="M74" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" t="s">
+        <v>23</v>
+      </c>
+      <c r="O74" t="s">
         <v>341</v>
-      </c>
-      <c r="L74" t="s">
-        <v>18</v>
-      </c>
-      <c r="M74" t="s">
-        <v>40</v>
-      </c>
-      <c r="N74" t="s">
-        <v>18</v>
-      </c>
-      <c r="O74" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>342</v>
+      </c>
+      <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" t="s">
+        <v>84</v>
+      </c>
+      <c r="D75" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>61</v>
+      </c>
+      <c r="G75" t="s">
+        <v>196</v>
+      </c>
+      <c r="H75" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" t="s">
+        <v>209</v>
+      </c>
+      <c r="K75" t="s">
         <v>343</v>
       </c>
-      <c r="B75" t="s">
-        <v>66</v>
-      </c>
-      <c r="C75" t="s">
-        <v>67</v>
-      </c>
-      <c r="D75" t="s">
-        <v>68</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
-        <v>59</v>
-      </c>
-      <c r="G75" t="s">
+      <c r="L75" t="s">
+        <v>23</v>
+      </c>
+      <c r="M75" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" t="s">
+        <v>23</v>
+      </c>
+      <c r="O75" t="s">
         <v>344</v>
-      </c>
-      <c r="H75" t="s">
-        <v>22</v>
-      </c>
-      <c r="I75" t="s">
-        <v>61</v>
-      </c>
-      <c r="J75" t="s">
-        <v>184</v>
-      </c>
-      <c r="K75" t="s">
-        <v>345</v>
-      </c>
-      <c r="L75" t="s">
-        <v>18</v>
-      </c>
-      <c r="M75" t="s">
-        <v>18</v>
-      </c>
-      <c r="N75" t="s">
-        <v>18</v>
-      </c>
-      <c r="O75" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>345</v>
+      </c>
+      <c r="B76" t="s">
+        <v>51</v>
+      </c>
+      <c r="C76" t="s">
+        <v>315</v>
+      </c>
+      <c r="D76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" t="s">
+        <v>114</v>
+      </c>
+      <c r="G76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" t="s">
+        <v>346</v>
+      </c>
+      <c r="K76" t="s">
         <v>347</v>
       </c>
-      <c r="B76" t="s">
-        <v>27</v>
-      </c>
-      <c r="C76" t="s">
-        <v>28</v>
-      </c>
-      <c r="D76" t="s">
-        <v>29</v>
-      </c>
-      <c r="E76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" t="s">
-        <v>20</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="L76" t="s">
+        <v>23</v>
+      </c>
+      <c r="M76" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" t="s">
+        <v>23</v>
+      </c>
+      <c r="O76" t="s">
         <v>348</v>
-      </c>
-      <c r="H76" t="s">
-        <v>22</v>
-      </c>
-      <c r="I76" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" t="s">
-        <v>349</v>
-      </c>
-      <c r="K76" t="s">
-        <v>207</v>
-      </c>
-      <c r="L76" t="s">
-        <v>18</v>
-      </c>
-      <c r="M76" t="s">
-        <v>18</v>
-      </c>
-      <c r="N76" t="s">
-        <v>18</v>
-      </c>
-      <c r="O76" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>351</v>
-      </c>
-      <c r="B77" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" t="s">
-        <v>45</v>
-      </c>
-      <c r="D77" t="s">
-        <v>29</v>
-      </c>
-      <c r="E77" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" t="s">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s">
-        <v>352</v>
-      </c>
-      <c r="H77" t="s">
-        <v>22</v>
-      </c>
-      <c r="I77" t="s">
-        <v>18</v>
-      </c>
-      <c r="J77" t="s">
-        <v>353</v>
-      </c>
-      <c r="K77" t="s">
-        <v>325</v>
-      </c>
-      <c r="L77" t="s">
-        <v>18</v>
-      </c>
-      <c r="M77" t="s">
-        <v>18</v>
-      </c>
-      <c r="N77" t="s">
-        <v>18</v>
-      </c>
-      <c r="O77" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>355</v>
-      </c>
-      <c r="B78" t="s">
-        <v>111</v>
-      </c>
-      <c r="C78" t="s">
-        <v>112</v>
-      </c>
-      <c r="D78" t="s">
-        <v>18</v>
-      </c>
-      <c r="E78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F78" t="s">
-        <v>59</v>
-      </c>
-      <c r="G78" t="s">
-        <v>171</v>
-      </c>
-      <c r="H78" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" t="s">
-        <v>356</v>
-      </c>
-      <c r="K78" t="s">
-        <v>104</v>
-      </c>
-      <c r="L78" t="s">
-        <v>18</v>
-      </c>
-      <c r="M78" t="s">
-        <v>18</v>
-      </c>
-      <c r="N78" t="s">
-        <v>18</v>
-      </c>
-      <c r="O78" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>358</v>
-      </c>
-      <c r="B79" t="s">
-        <v>44</v>
-      </c>
-      <c r="C79" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E79" t="s">
-        <v>19</v>
-      </c>
-      <c r="F79" t="s">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s">
-        <v>166</v>
-      </c>
-      <c r="H79" t="s">
-        <v>22</v>
-      </c>
-      <c r="I79" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" t="s">
-        <v>359</v>
-      </c>
-      <c r="K79" t="s">
-        <v>82</v>
-      </c>
-      <c r="L79" t="s">
-        <v>18</v>
-      </c>
-      <c r="M79" t="s">
-        <v>18</v>
-      </c>
-      <c r="N79" t="s">
-        <v>18</v>
-      </c>
-      <c r="O79" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>361</v>
-      </c>
-      <c r="B80" t="s">
-        <v>176</v>
-      </c>
-      <c r="C80" t="s">
-        <v>177</v>
-      </c>
-      <c r="D80" t="s">
-        <v>58</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
-        <v>46</v>
-      </c>
-      <c r="G80" t="s">
-        <v>166</v>
-      </c>
-      <c r="H80" t="s">
-        <v>22</v>
-      </c>
-      <c r="I80" t="s">
-        <v>61</v>
-      </c>
-      <c r="J80" t="s">
-        <v>362</v>
-      </c>
-      <c r="K80" t="s">
-        <v>363</v>
-      </c>
-      <c r="L80" t="s">
-        <v>18</v>
-      </c>
-      <c r="M80" t="s">
-        <v>40</v>
-      </c>
-      <c r="N80" t="s">
-        <v>18</v>
-      </c>
-      <c r="O80" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>365</v>
-      </c>
-      <c r="B81" t="s">
-        <v>176</v>
-      </c>
-      <c r="C81" t="s">
-        <v>177</v>
-      </c>
-      <c r="D81" t="s">
-        <v>58</v>
-      </c>
-      <c r="E81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" t="s">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s">
-        <v>352</v>
-      </c>
-      <c r="H81" t="s">
-        <v>22</v>
-      </c>
-      <c r="I81" t="s">
-        <v>61</v>
-      </c>
-      <c r="J81" t="s">
-        <v>366</v>
-      </c>
-      <c r="K81" t="s">
-        <v>286</v>
-      </c>
-      <c r="L81" t="s">
-        <v>18</v>
-      </c>
-      <c r="M81" t="s">
-        <v>18</v>
-      </c>
-      <c r="N81" t="s">
-        <v>18</v>
-      </c>
-      <c r="O81" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>368</v>
-      </c>
-      <c r="B82" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" t="s">
-        <v>91</v>
-      </c>
-      <c r="D82" t="s">
-        <v>68</v>
-      </c>
-      <c r="E82" t="s">
-        <v>19</v>
-      </c>
-      <c r="F82" t="s">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s">
-        <v>171</v>
-      </c>
-      <c r="H82" t="s">
-        <v>22</v>
-      </c>
-      <c r="I82" t="s">
-        <v>61</v>
-      </c>
-      <c r="J82" t="s">
-        <v>369</v>
-      </c>
-      <c r="K82" t="s">
-        <v>260</v>
-      </c>
-      <c r="L82" t="s">
-        <v>18</v>
-      </c>
-      <c r="M82" t="s">
-        <v>18</v>
-      </c>
-      <c r="N82" t="s">
-        <v>18</v>
-      </c>
-      <c r="O82" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>371</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" t="s">
-        <v>372</v>
-      </c>
-      <c r="G83" t="s">
-        <v>166</v>
-      </c>
-      <c r="H83" t="s">
-        <v>22</v>
-      </c>
-      <c r="I83" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" t="s">
-        <v>373</v>
-      </c>
-      <c r="K83" t="s">
-        <v>114</v>
-      </c>
-      <c r="L83" t="s">
-        <v>18</v>
-      </c>
-      <c r="M83" t="s">
-        <v>18</v>
-      </c>
-      <c r="N83" t="s">
-        <v>374</v>
-      </c>
-      <c r="O83" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>376</v>
-      </c>
-      <c r="B84" t="s">
-        <v>96</v>
-      </c>
-      <c r="C84" t="s">
-        <v>45</v>
-      </c>
-      <c r="D84" t="s">
-        <v>29</v>
-      </c>
-      <c r="E84" t="s">
-        <v>19</v>
-      </c>
-      <c r="F84" t="s">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s">
-        <v>377</v>
-      </c>
-      <c r="H84" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" t="s">
-        <v>378</v>
-      </c>
-      <c r="K84" t="s">
-        <v>93</v>
-      </c>
-      <c r="L84" t="s">
-        <v>18</v>
-      </c>
-      <c r="M84" t="s">
-        <v>18</v>
-      </c>
-      <c r="N84" t="s">
-        <v>18</v>
-      </c>
-      <c r="O84" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>380</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" t="s">
-        <v>18</v>
-      </c>
-      <c r="E85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F85" t="s">
-        <v>20</v>
-      </c>
-      <c r="G85" t="s">
-        <v>21</v>
-      </c>
-      <c r="H85" t="s">
-        <v>22</v>
-      </c>
-      <c r="I85" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" t="s">
-        <v>381</v>
-      </c>
-      <c r="K85" t="s">
-        <v>382</v>
-      </c>
-      <c r="L85" t="s">
-        <v>18</v>
-      </c>
-      <c r="M85" t="s">
-        <v>18</v>
-      </c>
-      <c r="N85" t="s">
-        <v>18</v>
-      </c>
-      <c r="O85" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>384</v>
-      </c>
-      <c r="B86" t="s">
-        <v>176</v>
-      </c>
-      <c r="C86" t="s">
-        <v>177</v>
-      </c>
-      <c r="D86" t="s">
-        <v>58</v>
-      </c>
-      <c r="E86" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" t="s">
-        <v>20</v>
-      </c>
-      <c r="G86" t="s">
-        <v>385</v>
-      </c>
-      <c r="H86" t="s">
-        <v>22</v>
-      </c>
-      <c r="I86" t="s">
-        <v>61</v>
-      </c>
-      <c r="J86" t="s">
-        <v>386</v>
-      </c>
-      <c r="K86" t="s">
-        <v>387</v>
-      </c>
-      <c r="L86" t="s">
-        <v>18</v>
-      </c>
-      <c r="M86" t="s">
-        <v>18</v>
-      </c>
-      <c r="N86" t="s">
-        <v>18</v>
-      </c>
-      <c r="O86" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26E8C65A-B3D3-4BBA-B032-889665F6535E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3225C079-A98B-4B46-AB4B-3A3515541199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1635" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="323">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,66 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>05/06/2026 10:32:16 AM</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>Donald White</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Parking Lot, Congested</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>5949 Financial Plaza, Shreveport, LA, 71129</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdeb-1af8-5128-a674-bf7cc3b04f19</t>
+  </si>
+  <si>
+    <t>05/06/2026 8:26:47 AM</t>
+  </si>
+  <si>
+    <t>Truck 26</t>
+  </si>
+  <si>
+    <t>Chico Leone</t>
+  </si>
+  <si>
+    <t>Full fleet , Heavy Duty</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Minden, LA, 71080</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd78-370b-53d4-86fa-85c570133c70</t>
+  </si>
+  <si>
     <t>05/02/2026 12:19:44 PM</t>
   </si>
   <si>
@@ -74,21 +134,9 @@
     <t>Full fleet , Light Duty</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
     <t>Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>I 49, Brown Park Estates, LA, 71106</t>
   </si>
   <si>
@@ -107,15 +155,9 @@
     <t>Daniel Vanwinterswyk</t>
   </si>
   <si>
-    <t>Full fleet , Heavy Duty</t>
-  </si>
-  <si>
     <t>Inattentive Driving</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>I 20, Shreveport, LA, 71103</t>
   </si>
   <si>
@@ -152,9 +194,6 @@
     <t>04/27/2026 5:32:25 AM</t>
   </si>
   <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
@@ -170,9 +209,6 @@
     <t>04/24/2026 5:24:06 PM</t>
   </si>
   <si>
-    <t>SV1</t>
-  </si>
-  <si>
     <t>Peyton Birchfield</t>
   </si>
   <si>
@@ -320,12 +356,6 @@
     <t>04/02/2026 11:35:15 AM</t>
   </si>
   <si>
-    <t>Truck 26</t>
-  </si>
-  <si>
-    <t>Chico Leone</t>
-  </si>
-  <si>
     <t>US 82, Crossett, AR, 71635</t>
   </si>
   <si>
@@ -392,9 +422,6 @@
     <t>2796 East 70th Street, Shreveport, LA, 71105</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c19-7101-52ac-b4c8-e817acb3fbc7</t>
   </si>
   <si>
@@ -957,111 +984,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544547a0-82ec-51c5-87f1-265d7beb84d8</t>
-  </si>
-  <si>
-    <t>02/07/2026 2:31:45 PM</t>
-  </si>
-  <si>
-    <t>Donald White</t>
-  </si>
-  <si>
-    <t>7001 Glenleaf Road, Shreveport, LA, 71129</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544539cd-a80c-5e63-aa44-090c0841d706</t>
-  </si>
-  <si>
-    <t>02/07/2026 8:24:25 AM</t>
-  </si>
-  <si>
-    <t>256 Montgomery Street, Shreveport, LA, 71107</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445387d-5ab8-55c5-b716-4f0975d3fe6f</t>
-  </si>
-  <si>
-    <t>02/06/2026 3:34:10 PM</t>
-  </si>
-  <si>
-    <t>Slightly Drowsy, Light Traffic</t>
-  </si>
-  <si>
-    <t>2620 Airline Drive, Bossier City, LA, 71111</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544534e0-7177-5f0f-8fc7-941b43783b92</t>
-  </si>
-  <si>
-    <t>02/06/2026 12:23:04 PM</t>
-  </si>
-  <si>
-    <t>167 Wemple Road, Bossier City, LA, 71111</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453431-7caa-5cf5-a4cf-d9790c3a7512</t>
-  </si>
-  <si>
-    <t>02/05/2026 5:27:09 PM</t>
-  </si>
-  <si>
-    <t>277 Winfield Road, Bossier Parish, LA, 71037</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453021-84f5-5b69-b632-cf7b75545e35</t>
-  </si>
-  <si>
-    <t>02/04/2026 7:27:44 PM</t>
-  </si>
-  <si>
-    <t>1482 Lash Street, Shreveport, LA, 71108</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b69-9244-5abc-869f-3a7c61c21cae</t>
-  </si>
-  <si>
-    <t>02/03/2026 1:32:40 PM</t>
-  </si>
-  <si>
-    <t>1937 Ray Avenue, Bossier City, LA, 71112</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524fe-239b-5ae5-bf6c-c973ce58d705</t>
-  </si>
-  <si>
-    <t>02/03/2026 1:29:32 PM</t>
-  </si>
-  <si>
-    <t>1900 Ray Avenue, Bossier City, LA, 71112</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524fb-4525-5409-9a16-6f2de05e5cde</t>
-  </si>
-  <si>
-    <t>02/03/2026 12:11:01 PM</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524b3-605c-5999-abbd-72c7e206afd2</t>
-  </si>
-  <si>
-    <t>02/03/2026 7:34:30 AM</t>
-  </si>
-  <si>
-    <t>6523 West 70th Street, Shreveport, LA, 71129</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523b6-3878-57eb-a332-fbf8ba64a1c5</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1514,148 +1436,148 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
         <v>34</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>40</v>
       </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>41</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
         <v>42</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
         <v>47</v>
@@ -1664,36 +1586,36 @@
         <v>48</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
         <v>54</v>
@@ -1702,7 +1624,7 @@
         <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
         <v>55</v>
@@ -1711,13 +1633,13 @@
         <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
         <v>57</v>
@@ -1728,231 +1650,231 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
         <v>59</v>
       </c>
-      <c r="C7" t="s">
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>60</v>
       </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="K7" t="s">
         <v>61</v>
       </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
         <v>62</v>
-      </c>
-      <c r="K7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="C8" t="s">
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
         <v>67</v>
       </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>68</v>
       </c>
-      <c r="G8" t="s">
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
         <v>69</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="K11" t="s">
         <v>86</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O11" t="s">
         <v>87</v>
@@ -1966,72 +1888,72 @@
         <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="O12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
         <v>97</v>
@@ -2040,13 +1962,13 @@
         <v>98</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O13" t="s">
         <v>99</v>
@@ -2060,322 +1982,322 @@
         <v>101</v>
       </c>
       <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
         <v>102</v>
       </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>103</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
         <v>104</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
         <v>106</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
         <v>107</v>
       </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" t="s">
-        <v>21</v>
-      </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
         <v>113</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="K16" t="s">
         <v>114</v>
       </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" t="s">
         <v>115</v>
-      </c>
-      <c r="K16" t="s">
-        <v>116</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" t="s">
-        <v>23</v>
-      </c>
-      <c r="O16" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
         <v>118</v>
       </c>
-      <c r="B17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="K17" t="s">
         <v>119</v>
       </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" t="s">
         <v>120</v>
-      </c>
-      <c r="K17" t="s">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K19" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K20" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
         <v>135</v>
@@ -2386,43 +2308,43 @@
         <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K21" t="s">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O21" t="s">
         <v>139</v>
@@ -2433,104 +2355,104 @@
         <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" t="s">
         <v>39</v>
       </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" t="s">
-        <v>32</v>
-      </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
         <v>39</v>
       </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" t="s">
-        <v>21</v>
-      </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -2539,31 +2461,31 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K24" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O24" t="s">
         <v>151</v>
@@ -2574,28 +2496,28 @@
         <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
         <v>30</v>
       </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>31</v>
-      </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
         <v>153</v>
@@ -2604,13 +2526,13 @@
         <v>154</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M25" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O25" t="s">
         <v>155</v>
@@ -2621,75 +2543,75 @@
         <v>156</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" t="s">
         <v>157</v>
       </c>
-      <c r="G26" t="s">
-        <v>21</v>
-      </c>
       <c r="H26" t="s">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J26" t="s">
         <v>158</v>
       </c>
       <c r="K26" t="s">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
         <v>162</v>
@@ -2698,154 +2620,154 @@
         <v>163</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" t="s">
         <v>164</v>
-      </c>
-      <c r="O27" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
         <v>166</v>
       </c>
-      <c r="B28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="G28" t="s">
         <v>39</v>
       </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" t="s">
-        <v>21</v>
-      </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="K28" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K29" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K30" t="s">
-        <v>175</v>
+        <v>41</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N30" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="O30" t="s">
         <v>176</v>
@@ -2856,137 +2778,137 @@
         <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
         <v>178</v>
       </c>
-      <c r="D31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" t="s">
-        <v>21</v>
-      </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
         <v>179</v>
       </c>
       <c r="K31" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="O31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
         <v>183</v>
       </c>
       <c r="K32" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="O32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K33" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O33" t="s">
         <v>189</v>
@@ -2997,278 +2919,278 @@
         <v>190</v>
       </c>
       <c r="B34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" t="s">
         <v>191</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" t="s">
         <v>39</v>
       </c>
-      <c r="D34" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" t="s">
-        <v>46</v>
-      </c>
       <c r="H34" t="s">
         <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
         <v>192</v>
       </c>
       <c r="K34" t="s">
+        <v>143</v>
+      </c>
+      <c r="L34" t="s">
+        <v>18</v>
+      </c>
+      <c r="M34" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34" t="s">
         <v>193</v>
-      </c>
-      <c r="L34" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" t="s">
-        <v>23</v>
-      </c>
-      <c r="N34" t="s">
-        <v>23</v>
-      </c>
-      <c r="O34" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" t="s">
         <v>195</v>
       </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>45</v>
-      </c>
       <c r="G35" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s">
         <v>196</v>
       </c>
-      <c r="H35" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>197</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" t="s">
         <v>198</v>
-      </c>
-      <c r="L35" t="s">
-        <v>23</v>
-      </c>
-      <c r="M35" t="s">
-        <v>23</v>
-      </c>
-      <c r="N35" t="s">
-        <v>23</v>
-      </c>
-      <c r="O35" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" t="s">
         <v>200</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s">
         <v>201</v>
       </c>
-      <c r="C36" t="s">
+      <c r="K36" t="s">
         <v>202</v>
       </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>114</v>
-      </c>
-      <c r="G36" t="s">
-        <v>196</v>
-      </c>
-      <c r="H36" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" t="s">
-        <v>96</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="L36" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36" t="s">
         <v>203</v>
-      </c>
-      <c r="K36" t="s">
-        <v>198</v>
-      </c>
-      <c r="L36" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" t="s">
         <v>205</v>
       </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>114</v>
-      </c>
-      <c r="G37" t="s">
-        <v>46</v>
-      </c>
       <c r="H37" t="s">
         <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
         <v>206</v>
       </c>
       <c r="K37" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="G38" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J38" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K38" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s">
-        <v>213</v>
+        <v>59</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K39" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O39" t="s">
         <v>216</v>
@@ -3279,43 +3201,43 @@
         <v>217</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" t="s">
         <v>218</v>
       </c>
-      <c r="H40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" t="s">
-        <v>96</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>219</v>
       </c>
-      <c r="K40" t="s">
-        <v>134</v>
-      </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O40" t="s">
         <v>220</v>
@@ -3326,43 +3248,43 @@
         <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
         <v>222</v>
       </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J41" t="s">
         <v>223</v>
       </c>
       <c r="K41" t="s">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N41" t="s">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="O41" t="s">
         <v>225</v>
@@ -3373,654 +3295,654 @@
         <v>226</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G42" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K42" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M42" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>68</v>
+        <v>231</v>
       </c>
       <c r="G43" t="s">
-        <v>230</v>
+        <v>39</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K43" t="s">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>233</v>
       </c>
       <c r="O43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M44" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K45" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G46" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K46" t="s">
-        <v>243</v>
+        <v>61</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B47" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>246</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J47" t="s">
         <v>247</v>
       </c>
       <c r="K47" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M47" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O48" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>255</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G49" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J49" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K49" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N49" t="s">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="O49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K50" t="s">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="L50" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M50" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N50" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K51" t="s">
-        <v>232</v>
+        <v>24</v>
       </c>
       <c r="L51" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N51" t="s">
-        <v>23</v>
+        <v>264</v>
       </c>
       <c r="O51" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J52" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K52" t="s">
-        <v>239</v>
+        <v>41</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O52" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="H53" t="s">
         <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J53" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K53" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O53" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B54" t="s">
-        <v>271</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H54" t="s">
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J54" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K54" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O54" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="D55" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
       </c>
       <c r="I55" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="J55" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K55" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N55" t="s">
-        <v>277</v>
+        <v>18</v>
       </c>
       <c r="O55" t="s">
         <v>278</v>
@@ -4031,986 +3953,610 @@
         <v>279</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="C56" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K56" t="s">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M56" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>286</v>
       </c>
       <c r="O57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="G58" t="s">
-        <v>261</v>
+        <v>39</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K58" t="s">
-        <v>288</v>
+        <v>41</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N58" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K59" t="s">
-        <v>35</v>
+        <v>293</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O59" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B60" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J60" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K60" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O60" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>196</v>
+        <v>39</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J61" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K61" t="s">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N61" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O61" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="G62" t="s">
-        <v>261</v>
+        <v>205</v>
       </c>
       <c r="H62" t="s">
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J62" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K62" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O62" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B63" t="s">
-        <v>201</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="H63" t="s">
         <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K63" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N63" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O63" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K64" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M64" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N64" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O64" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B65" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
       </c>
       <c r="I65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K65" t="s">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N65" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O65" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G66" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H66" t="s">
         <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>55</v>
+        <v>315</v>
       </c>
       <c r="K66" t="s">
-        <v>288</v>
+        <v>86</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O66" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C67" t="s">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K67" t="s">
-        <v>150</v>
+        <v>319</v>
       </c>
       <c r="L67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N67" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O67" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J68" t="s">
-        <v>319</v>
+        <v>67</v>
       </c>
       <c r="K68" t="s">
-        <v>239</v>
+        <v>297</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O68" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>321</v>
-      </c>
-      <c r="B69" t="s">
-        <v>112</v>
-      </c>
-      <c r="C69" t="s">
-        <v>113</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" t="s">
-        <v>68</v>
-      </c>
-      <c r="G69" t="s">
         <v>322</v>
-      </c>
-      <c r="H69" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" t="s">
-        <v>96</v>
-      </c>
-      <c r="J69" t="s">
-        <v>323</v>
-      </c>
-      <c r="K69" t="s">
-        <v>163</v>
-      </c>
-      <c r="L69" t="s">
-        <v>23</v>
-      </c>
-      <c r="M69" t="s">
-        <v>23</v>
-      </c>
-      <c r="N69" t="s">
-        <v>23</v>
-      </c>
-      <c r="O69" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>325</v>
-      </c>
-      <c r="B70" t="s">
-        <v>107</v>
-      </c>
-      <c r="C70" t="s">
-        <v>23</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" t="s">
-        <v>107</v>
-      </c>
-      <c r="F70" t="s">
-        <v>31</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>22</v>
-      </c>
-      <c r="I70" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" t="s">
-        <v>326</v>
-      </c>
-      <c r="K70" t="s">
-        <v>327</v>
-      </c>
-      <c r="L70" t="s">
-        <v>23</v>
-      </c>
-      <c r="M70" t="s">
-        <v>35</v>
-      </c>
-      <c r="N70" t="s">
-        <v>23</v>
-      </c>
-      <c r="O70" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>329</v>
-      </c>
-      <c r="B71" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" t="s">
-        <v>52</v>
-      </c>
-      <c r="D71" t="s">
-        <v>53</v>
-      </c>
-      <c r="E71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
-        <v>222</v>
-      </c>
-      <c r="G71" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" t="s">
-        <v>23</v>
-      </c>
-      <c r="J71" t="s">
-        <v>330</v>
-      </c>
-      <c r="K71" t="s">
-        <v>331</v>
-      </c>
-      <c r="L71" t="s">
-        <v>23</v>
-      </c>
-      <c r="M71" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" t="s">
-        <v>255</v>
-      </c>
-      <c r="O71" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>333</v>
-      </c>
-      <c r="B72" t="s">
-        <v>66</v>
-      </c>
-      <c r="C72" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>114</v>
-      </c>
-      <c r="G72" t="s">
-        <v>46</v>
-      </c>
-      <c r="H72" t="s">
-        <v>22</v>
-      </c>
-      <c r="I72" t="s">
-        <v>23</v>
-      </c>
-      <c r="J72" t="s">
-        <v>334</v>
-      </c>
-      <c r="K72" t="s">
-        <v>134</v>
-      </c>
-      <c r="L72" t="s">
-        <v>23</v>
-      </c>
-      <c r="M72" t="s">
-        <v>23</v>
-      </c>
-      <c r="N72" t="s">
-        <v>23</v>
-      </c>
-      <c r="O72" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>336</v>
-      </c>
-      <c r="B73" t="s">
-        <v>101</v>
-      </c>
-      <c r="C73" t="s">
-        <v>102</v>
-      </c>
-      <c r="D73" t="s">
-        <v>30</v>
-      </c>
-      <c r="E73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" t="s">
-        <v>45</v>
-      </c>
-      <c r="G73" t="s">
-        <v>196</v>
-      </c>
-      <c r="H73" t="s">
-        <v>22</v>
-      </c>
-      <c r="I73" t="s">
-        <v>96</v>
-      </c>
-      <c r="J73" t="s">
-        <v>337</v>
-      </c>
-      <c r="K73" t="s">
-        <v>125</v>
-      </c>
-      <c r="L73" t="s">
-        <v>23</v>
-      </c>
-      <c r="M73" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" t="s">
-        <v>23</v>
-      </c>
-      <c r="O73" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>339</v>
-      </c>
-      <c r="B74" t="s">
-        <v>101</v>
-      </c>
-      <c r="C74" t="s">
-        <v>102</v>
-      </c>
-      <c r="D74" t="s">
-        <v>30</v>
-      </c>
-      <c r="E74" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" t="s">
-        <v>114</v>
-      </c>
-      <c r="G74" t="s">
-        <v>196</v>
-      </c>
-      <c r="H74" t="s">
-        <v>22</v>
-      </c>
-      <c r="I74" t="s">
-        <v>96</v>
-      </c>
-      <c r="J74" t="s">
-        <v>340</v>
-      </c>
-      <c r="K74" t="s">
-        <v>150</v>
-      </c>
-      <c r="L74" t="s">
-        <v>23</v>
-      </c>
-      <c r="M74" t="s">
-        <v>23</v>
-      </c>
-      <c r="N74" t="s">
-        <v>23</v>
-      </c>
-      <c r="O74" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>342</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" t="s">
-        <v>84</v>
-      </c>
-      <c r="D75" t="s">
-        <v>53</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
-        <v>61</v>
-      </c>
-      <c r="G75" t="s">
-        <v>196</v>
-      </c>
-      <c r="H75" t="s">
-        <v>22</v>
-      </c>
-      <c r="I75" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" t="s">
-        <v>209</v>
-      </c>
-      <c r="K75" t="s">
-        <v>343</v>
-      </c>
-      <c r="L75" t="s">
-        <v>23</v>
-      </c>
-      <c r="M75" t="s">
-        <v>23</v>
-      </c>
-      <c r="N75" t="s">
-        <v>23</v>
-      </c>
-      <c r="O75" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>345</v>
-      </c>
-      <c r="B76" t="s">
-        <v>51</v>
-      </c>
-      <c r="C76" t="s">
-        <v>315</v>
-      </c>
-      <c r="D76" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" t="s">
-        <v>114</v>
-      </c>
-      <c r="G76" t="s">
-        <v>21</v>
-      </c>
-      <c r="H76" t="s">
-        <v>22</v>
-      </c>
-      <c r="I76" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" t="s">
-        <v>346</v>
-      </c>
-      <c r="K76" t="s">
-        <v>347</v>
-      </c>
-      <c r="L76" t="s">
-        <v>23</v>
-      </c>
-      <c r="M76" t="s">
-        <v>23</v>
-      </c>
-      <c r="N76" t="s">
-        <v>23</v>
-      </c>
-      <c r="O76" t="s">
-        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31D1DDBA-5FF5-4E75-804E-F864514F4ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4C5C866-D44C-40DD-A9C1-5F0281C6698A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="297">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,70 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>05/10/2026 10:46:38 PM</t>
+    <t>05/19/2026 10:16:58 PM</t>
+  </si>
+  <si>
+    <t>Truck 6</t>
+  </si>
+  <si>
+    <t>Robert Bailey</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>142 Captain H M Shreve Boulevard, Shreveport, LA, 71115</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454362-f189-557c-ba35-902c6f5a2ed3</t>
+  </si>
+  <si>
+    <t>05/19/2026 4:22:07 AM</t>
+  </si>
+  <si>
+    <t>Truck 3</t>
+  </si>
+  <si>
+    <t>Mark Gwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>I 20, Haughton, LA, 71037</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f8a-e21f-55c1-85e2-c9d26ee5074d</t>
+  </si>
+  <si>
+    <t>05/10/2026 11:46:38 PM</t>
   </si>
   <si>
     <t>Truck 8</t>
@@ -71,37 +134,22 @@
     <t>Chris Mcconnell</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Harsh Brake</t>
   </si>
   <si>
     <t>Cyclist/Motorcyclist, Light Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>1087 McDade Street, Bossier City, LA, 71112</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>0.94</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445155b-ccf6-5abf-82bd-50e48d633720</t>
   </si>
   <si>
-    <t>05/08/2026 5:49:37 AM</t>
+    <t>05/08/2026 6:49:37 AM</t>
   </si>
   <si>
     <t>Truck 7</t>
@@ -125,7 +173,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445076b-fa15-5277-a1eb-c46d844f1914</t>
   </si>
   <si>
-    <t>05/06/2026 9:32:16 AM</t>
+    <t>05/06/2026 10:32:16 AM</t>
   </si>
   <si>
     <t>SV1</t>
@@ -134,9 +182,6 @@
     <t>Donald White</t>
   </si>
   <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
     <t>Parking Lot, Congested</t>
   </si>
   <si>
@@ -146,7 +191,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdeb-1af8-5128-a674-bf7cc3b04f19</t>
   </si>
   <si>
-    <t>05/06/2026 7:26:47 AM</t>
+    <t>05/06/2026 8:26:47 AM</t>
   </si>
   <si>
     <t>Truck 26</t>
@@ -173,7 +218,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd78-370b-53d4-86fa-85c570133c70</t>
   </si>
   <si>
-    <t>05/02/2026 11:19:44 AM</t>
+    <t>05/02/2026 12:19:44 PM</t>
   </si>
   <si>
     <t>Truck 1</t>
@@ -191,7 +236,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e9b4-0f61-5508-ac64-ec6a03919a24</t>
   </si>
   <si>
-    <t>05/01/2026 3:32:04 PM</t>
+    <t>05/01/2026 4:32:04 PM</t>
   </si>
   <si>
     <t>Truck 60</t>
@@ -215,7 +260,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e574-b7a1-5e28-96a1-5bf164776383</t>
   </si>
   <si>
-    <t>04/28/2026 4:47:36 PM</t>
+    <t>04/28/2026 5:47:36 PM</t>
   </si>
   <si>
     <t>Truck 22</t>
@@ -236,7 +281,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d646-c988-5cd9-a47e-8bafc996366e</t>
   </si>
   <si>
-    <t>04/27/2026 4:32:25 AM</t>
+    <t>04/27/2026 5:32:25 AM</t>
   </si>
   <si>
     <t>Light Traffic, Night</t>
@@ -251,15 +296,12 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ce7f-5702-59fe-b50c-fbf25865a2dc</t>
   </si>
   <si>
-    <t>04/24/2026 4:24:06 PM</t>
+    <t>04/24/2026 5:24:06 PM</t>
   </si>
   <si>
     <t>Peyton Birchfield</t>
   </si>
   <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
     <t>Construction, Moderate Traffic</t>
   </si>
   <si>
@@ -272,7 +314,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c197-d662-5f98-875f-828cba2d84a2</t>
   </si>
   <si>
-    <t>04/24/2026 4:02:20 PM</t>
+    <t>04/24/2026 5:02:20 PM</t>
   </si>
   <si>
     <t>S1</t>
@@ -293,7 +335,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c183-e715-5584-8f77-10fa858fef63</t>
   </si>
   <si>
-    <t>04/18/2026 12:57:17 AM</t>
+    <t>04/18/2026 1:57:17 AM</t>
   </si>
   <si>
     <t>Truck 12</t>
@@ -302,19 +344,13 @@
     <t>Kendall Mckerley</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Slightly Drowsy, Light Traffic, Night</t>
   </si>
   <si>
-    <t>I 20, Haughton, LA, 71037</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459f61-26fd-5c26-9f57-0f4d1a54e66b</t>
   </si>
   <si>
-    <t>04/10/2026 4:23:41 PM</t>
+    <t>04/10/2026 5:23:41 PM</t>
   </si>
   <si>
     <t>Construction, Light Traffic</t>
@@ -326,10 +362,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445797e-6cd0-58ca-8001-1881473ac909</t>
   </si>
   <si>
-    <t>04/10/2026 9:36:38 AM</t>
-  </si>
-  <si>
-    <t>Truck 6</t>
+    <t>04/10/2026 10:36:38 AM</t>
   </si>
   <si>
     <t>Naples, TX, 75568</t>
@@ -341,10 +374,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457809-c12a-5a86-8703-a98b57a013e8</t>
   </si>
   <si>
-    <t>04/07/2026 4:09:08 PM</t>
-  </si>
-  <si>
-    <t>Mark Gwin</t>
+    <t>04/07/2026 5:09:08 PM</t>
   </si>
   <si>
     <t>Mansfield Road, Shreveport, LA, 71118</t>
@@ -356,7 +386,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544569fe-0661-5c57-9082-90a02dddf9ad</t>
   </si>
   <si>
-    <t>04/06/2026 12:45:01 PM</t>
+    <t>04/06/2026 1:45:01 PM</t>
   </si>
   <si>
     <t>SV2</t>
@@ -371,256 +401,250 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445641c-c872-5013-8cfe-321d5dbc917e</t>
   </si>
   <si>
-    <t>04/05/2026 10:42:36 AM</t>
-  </si>
-  <si>
-    <t>Robert Bailey</t>
+    <t>04/05/2026 11:42:36 AM</t>
   </si>
   <si>
     <t>Pedestrians, Light Traffic</t>
   </si>
   <si>
+    <t>226 Captain H M Shreve Boulevard, Shreveport, LA, 71115</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455e86-59ac-5113-965f-956c021ba3f1</t>
+  </si>
+  <si>
+    <t>04/02/2026 11:35:15 AM</t>
+  </si>
+  <si>
+    <t>US 82, Crossett, AR, 71635</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454f0c-8b48-5778-9894-6f4e6ae3b3a7</t>
+  </si>
+  <si>
+    <t>03/30/2026 7:46:29 AM</t>
+  </si>
+  <si>
+    <t>Evan</t>
+  </si>
+  <si>
+    <t>121 Lakewood Point Drive, Bossier Parish, LA, 71111</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453ec8-0786-56e8-801b-52fe84aa5748</t>
+  </si>
+  <si>
+    <t>03/29/2026 7:41:24 PM</t>
+  </si>
+  <si>
+    <t>Rolling Stop</t>
+  </si>
+  <si>
+    <t>2804 Dupont Street, Shreveport, LA, 71109</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453c30-32dc-52ca-b7da-4e104f8cd8f5</t>
+  </si>
+  <si>
+    <t>03/28/2026 2:45:32 PM</t>
+  </si>
+  <si>
+    <t>Passengers, Light Traffic</t>
+  </si>
+  <si>
+    <t>321 Greenacres Boulevard, Bossier City, LA, 71111</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544535fa-f512-51ff-b7ad-9e0dc2547809</t>
+  </si>
+  <si>
+    <t>03/26/2026 4:42:38 PM</t>
+  </si>
+  <si>
+    <t>2796 East 70th Street, Shreveport, LA, 71105</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c19-7101-52ac-b4c8-e817acb3fbc7</t>
+  </si>
+  <si>
+    <t>03/26/2026 10:48:31 AM</t>
+  </si>
+  <si>
+    <t>2116 North Market Street, Shreveport, LA, 71107</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ad5-4050-5cbe-b8a4-8aff22a8fa37</t>
+  </si>
+  <si>
+    <t>03/25/2026 3:03:49 PM</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>590 Dowling Street, Shreveport, LA, 71101</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452698-a049-538e-b7a2-6711343bda6a</t>
+  </si>
+  <si>
+    <t>03/24/2026 10:00:41 AM</t>
+  </si>
+  <si>
+    <t>I 20, West Monroe, LA, 71225</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445205c-babd-5784-9af6-1aec9227df37</t>
+  </si>
+  <si>
+    <t>03/24/2026 9:24:17 AM</t>
+  </si>
+  <si>
+    <t>5258 I 20, West Monroe, LA, 71292</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445203b-696f-5cf3-bdab-5d778e998dc8</t>
+  </si>
+  <si>
+    <t>03/23/2026 4:13:30 PM</t>
+  </si>
+  <si>
+    <t>Airline Highway, Livonia, LA, 70755</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c8b-b175-5a59-918e-879eb3f9af1e</t>
+  </si>
+  <si>
+    <t>03/23/2026 3:50:01 PM</t>
+  </si>
+  <si>
+    <t>Parking Lot, Light Traffic</t>
+  </si>
+  <si>
+    <t>Shreveport, LA, 71118</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c76-3465-53e9-83e8-4d07fac3caf0</t>
+  </si>
+  <si>
+    <t>03/23/2026 1:09:15 PM</t>
+  </si>
+  <si>
+    <t>I 20, Webster Parish, LA, 71067</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451be3-0267-5712-b998-32a6b40a984f</t>
+  </si>
+  <si>
+    <t>03/19/2026 2:37:03 PM</t>
+  </si>
+  <si>
+    <t>Forward Collision Warning</t>
+  </si>
+  <si>
+    <t>7101 US 79, River Hill, TX, 75639</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450799-f498-5512-add6-e9823215d7df</t>
+  </si>
+  <si>
+    <t>03/17/2026 3:43:53 PM</t>
+  </si>
+  <si>
+    <t>Pedestrians, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>5221 Jewella Avenue, Shreveport, LA, 71109</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd8a-6c12-52ce-baf3-303addf7bdf3</t>
+  </si>
+  <si>
+    <t>03/17/2026 12:44:39 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fce6-554c-5558-a57e-9e8a5b08a13c</t>
+  </si>
+  <si>
+    <t>03/17/2026 8:28:46 AM</t>
+  </si>
+  <si>
+    <t>Congested</t>
+  </si>
+  <si>
+    <t>Inner Loop Expressway, Shreveport, LA, 71118</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbfc-1056-531a-8556-dc31dc98a53f</t>
+  </si>
+  <si>
+    <t>03/17/2026 8:14:03 AM</t>
+  </si>
+  <si>
+    <t>I 20;US 71, Bossier City, LA, 71171</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbee-9601-5000-bd9a-cc9c81f9757b</t>
+  </si>
+  <si>
+    <t>03/14/2026 12:08:45 PM</t>
+  </si>
+  <si>
+    <t>Paul Newton</t>
+  </si>
+  <si>
     <t>Melissa H Mericle</t>
   </si>
   <si>
-    <t>226 Captain H M Shreve Boulevard, Shreveport, LA, 71115</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455e86-59ac-5113-965f-956c021ba3f1</t>
-  </si>
-  <si>
-    <t>04/02/2026 10:35:15 AM</t>
-  </si>
-  <si>
-    <t>US 82, Crossett, AR, 71635</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454f0c-8b48-5778-9894-6f4e6ae3b3a7</t>
-  </si>
-  <si>
-    <t>03/30/2026 6:46:29 AM</t>
-  </si>
-  <si>
-    <t>Evan</t>
-  </si>
-  <si>
-    <t>121 Lakewood Point Drive, Bossier Parish, LA, 71111</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453ec8-0786-56e8-801b-52fe84aa5748</t>
-  </si>
-  <si>
-    <t>03/29/2026 6:41:24 PM</t>
-  </si>
-  <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
-    <t>2804 Dupont Street, Shreveport, LA, 71109</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453c30-32dc-52ca-b7da-4e104f8cd8f5</t>
-  </si>
-  <si>
-    <t>03/28/2026 1:45:32 PM</t>
-  </si>
-  <si>
-    <t>Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>321 Greenacres Boulevard, Bossier City, LA, 71111</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544535fa-f512-51ff-b7ad-9e0dc2547809</t>
-  </si>
-  <si>
-    <t>03/26/2026 3:42:38 PM</t>
-  </si>
-  <si>
-    <t>2796 East 70th Street, Shreveport, LA, 71105</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c19-7101-52ac-b4c8-e817acb3fbc7</t>
-  </si>
-  <si>
-    <t>03/26/2026 9:48:31 AM</t>
-  </si>
-  <si>
-    <t>Truck 3</t>
-  </si>
-  <si>
-    <t>2116 North Market Street, Shreveport, LA, 71107</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ad5-4050-5cbe-b8a4-8aff22a8fa37</t>
-  </si>
-  <si>
-    <t>03/25/2026 2:03:49 PM</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>590 Dowling Street, Shreveport, LA, 71101</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452698-a049-538e-b7a2-6711343bda6a</t>
-  </si>
-  <si>
-    <t>03/24/2026 9:00:41 AM</t>
-  </si>
-  <si>
-    <t>I 20, West Monroe, LA, 71225</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445205c-babd-5784-9af6-1aec9227df37</t>
-  </si>
-  <si>
-    <t>03/24/2026 8:24:17 AM</t>
-  </si>
-  <si>
-    <t>5258 I 20, West Monroe, LA, 71292</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445203b-696f-5cf3-bdab-5d778e998dc8</t>
-  </si>
-  <si>
-    <t>03/23/2026 3:13:30 PM</t>
-  </si>
-  <si>
-    <t>Airline Highway, Livonia, LA, 70755</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c8b-b175-5a59-918e-879eb3f9af1e</t>
-  </si>
-  <si>
-    <t>03/23/2026 2:50:01 PM</t>
-  </si>
-  <si>
-    <t>Parking Lot, Light Traffic</t>
-  </si>
-  <si>
-    <t>Shreveport, LA, 71118</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c76-3465-53e9-83e8-4d07fac3caf0</t>
-  </si>
-  <si>
-    <t>03/23/2026 12:09:15 PM</t>
-  </si>
-  <si>
-    <t>I 20, Webster Parish, LA, 71067</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451be3-0267-5712-b998-32a6b40a984f</t>
-  </si>
-  <si>
-    <t>03/19/2026 1:37:03 PM</t>
-  </si>
-  <si>
-    <t>Forward Collision Warning</t>
-  </si>
-  <si>
-    <t>7101 US 79, River Hill, TX, 75639</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450799-f498-5512-add6-e9823215d7df</t>
-  </si>
-  <si>
-    <t>03/17/2026 2:43:53 PM</t>
-  </si>
-  <si>
-    <t>Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>5221 Jewella Avenue, Shreveport, LA, 71109</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd8a-6c12-52ce-baf3-303addf7bdf3</t>
-  </si>
-  <si>
-    <t>03/17/2026 11:44:39 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fce6-554c-5558-a57e-9e8a5b08a13c</t>
-  </si>
-  <si>
-    <t>03/17/2026 7:28:46 AM</t>
-  </si>
-  <si>
-    <t>Congested</t>
-  </si>
-  <si>
-    <t>Inner Loop Expressway, Shreveport, LA, 71118</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbfc-1056-531a-8556-dc31dc98a53f</t>
-  </si>
-  <si>
-    <t>03/17/2026 7:14:03 AM</t>
-  </si>
-  <si>
-    <t>I 20;US 71, Bossier City, LA, 71171</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbee-9601-5000-bd9a-cc9c81f9757b</t>
-  </si>
-  <si>
-    <t>03/14/2026 11:08:45 AM</t>
-  </si>
-  <si>
-    <t>Paul Newton</t>
-  </si>
-  <si>
     <t>1999 Venus Drive, Bossier City, LA, 71112</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ed52-6229-5cf8-b84a-6b5c83872cd3</t>
   </si>
   <si>
-    <t>03/13/2026 11:28:19 AM</t>
+    <t>03/13/2026 12:28:19 PM</t>
   </si>
   <si>
     <t>Will Ordoyne</t>
@@ -632,7 +656,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e83d-f2ef-5392-9a20-58f41831cd3e</t>
   </si>
   <si>
-    <t>03/12/2026 3:17:01 PM</t>
+    <t>03/12/2026 4:17:01 PM</t>
   </si>
   <si>
     <t>Lane Departure</t>
@@ -647,7 +671,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e3e8-f84a-5470-b503-519204b6e552</t>
   </si>
   <si>
-    <t>03/11/2026 9:45:25 PM</t>
+    <t>03/11/2026 10:45:25 PM</t>
   </si>
   <si>
     <t>Truck 23</t>
@@ -662,7 +686,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e026-324c-5197-a11d-4224e3ab2b26</t>
   </si>
   <si>
-    <t>03/11/2026 4:00:58 PM</t>
+    <t>03/11/2026 5:00:58 PM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic</t>
@@ -677,7 +701,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445deea-d89d-5a50-9310-5a4d36ffcd56</t>
   </si>
   <si>
-    <t>03/11/2026 10:26:09 AM</t>
+    <t>03/11/2026 11:26:09 AM</t>
   </si>
   <si>
     <t>Truck 13</t>
@@ -692,7 +716,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ddb8-50bd-597c-8e05-088e950d18f6</t>
   </si>
   <si>
-    <t>03/10/2026 9:37:33 PM</t>
+    <t>03/10/2026 10:37:33 PM</t>
   </si>
   <si>
     <t>8400 East Kings Highway, Shreveport, LA, 71115</t>
@@ -701,7 +725,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445daf8-a407-516a-8b8e-359c6a7cb9d4</t>
   </si>
   <si>
-    <t>03/09/2026 2:28:41 PM</t>
+    <t>03/09/2026 3:28:41 PM</t>
   </si>
   <si>
     <t>I 20, Shreveport, LA, 71109</t>
@@ -713,7 +737,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d449-a473-526a-abd8-26656c4c62bd</t>
   </si>
   <si>
-    <t>03/09/2026 8:02:20 AM</t>
+    <t>03/09/2026 9:02:20 AM</t>
   </si>
   <si>
     <t>Wet Road, Parking Lot, Light Traffic</t>
@@ -728,7 +752,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d2e7-eb74-5890-9219-940b501c29ac</t>
   </si>
   <si>
-    <t>03/08/2026 4:02:11 PM</t>
+    <t>03/08/2026 5:02:11 PM</t>
   </si>
   <si>
     <t>Construction, Parking Lot, Light Traffic</t>
@@ -740,7 +764,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cf78-e278-547b-b6fb-c2524edb1afd</t>
   </si>
   <si>
-    <t>03/06/2026 4:20:36 PM</t>
+    <t>03/06/2026 5:20:36 PM</t>
   </si>
   <si>
     <t>3199 Meriwether Road, Silver Pine Village, LA, 71108</t>
@@ -752,7 +776,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c573-f383-582c-a26b-8fe29f48c2a8</t>
   </si>
   <si>
-    <t>03/06/2026 2:50:47 PM</t>
+    <t>03/06/2026 3:50:47 PM</t>
   </si>
   <si>
     <t>143 Lakewood Point Drive, Bossier Parish, LA, 71111</t>
@@ -761,7 +785,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c521-b95f-5b37-8fed-74e8cff3d32e</t>
   </si>
   <si>
-    <t>03/05/2026 1:26:58 AM</t>
+    <t>03/05/2026 2:26:58 AM</t>
   </si>
   <si>
     <t>Slightly Drowsy, Construction, Light Traffic, Night</t>
@@ -776,7 +800,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bd1b-73cc-511a-8985-2fe097d14553</t>
   </si>
   <si>
-    <t>03/03/2026 3:36:36 PM</t>
+    <t>03/03/2026 4:36:36 PM</t>
   </si>
   <si>
     <t>3531 Highway 157, Bossier Parish, LA, 71051</t>
@@ -785,7 +809,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b5d8-96fd-5a76-a6f1-c869c6291cf5</t>
   </si>
   <si>
-    <t>03/03/2026 6:47:53 AM</t>
+    <t>03/03/2026 7:47:53 AM</t>
   </si>
   <si>
     <t>Stanley Avenue, Shreveport, LA, 71109</t>
@@ -797,7 +821,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b3f4-88a5-5d8a-bfcf-ea0ba52fd125</t>
   </si>
   <si>
-    <t>03/02/2026 6:20:02 PM</t>
+    <t>03/02/2026 7:20:02 PM</t>
   </si>
   <si>
     <t>746 East Flournoy Lucas Road, Shreveport, LA, 71115</t>
@@ -809,7 +833,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b147-dd39-54c4-98db-7c5bd41fcdfb</t>
   </si>
   <si>
-    <t>03/02/2026 2:24:14 PM</t>
+    <t>03/02/2026 3:24:14 PM</t>
   </si>
   <si>
     <t>Nick Whitaker</t>
@@ -821,7 +845,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b06f-f8d0-57b8-bab8-41729cacf1db</t>
   </si>
   <si>
-    <t>03/02/2026 10:23:46 AM</t>
+    <t>03/02/2026 11:23:46 AM</t>
   </si>
   <si>
     <t>Autoplex Drive, Bossier City, LA, 71111</t>
@@ -833,7 +857,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445af93-d1fb-5245-99dc-8ad07d858aa8</t>
   </si>
   <si>
-    <t>03/02/2026 7:56:51 AM</t>
+    <t>03/02/2026 8:56:51 AM</t>
   </si>
   <si>
     <t>3564 Hollywood Avenue, Shreveport, LA, 71109</t>
@@ -845,7 +869,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445af0d-5312-5b1b-b4d2-91482240a61e</t>
   </si>
   <si>
-    <t>02/27/2026 11:43:46 AM</t>
+    <t>02/27/2026 12:43:46 PM</t>
   </si>
   <si>
     <t>I 20;US 371, Minden, LA, 71055</t>
@@ -854,7 +878,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a069-fc2c-5020-a12e-3af0b806a496</t>
   </si>
   <si>
-    <t>02/25/2026 7:33:02 PM</t>
+    <t>02/25/2026 8:33:02 PM</t>
   </si>
   <si>
     <t>Very Drowsy, Light Traffic, Night</t>
@@ -866,7 +890,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544597ca-e498-5ff2-8d88-7cc0ba7db099</t>
   </si>
   <si>
-    <t>02/25/2026 9:22:33 AM</t>
+    <t>02/25/2026 10:22:33 AM</t>
   </si>
   <si>
     <t>Colquitt Road, Shreveport, LA, 71047</t>
@@ -875,82 +899,13 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445959b-fbbe-5890-aa78-1fbf13f0d0d0</t>
   </si>
   <si>
-    <t>02/24/2026 8:32:15 AM</t>
+    <t>02/24/2026 9:32:15 AM</t>
   </si>
   <si>
     <t>7796 West 70th Street, Shreveport, LA, 71129</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459047-9212-56a0-892c-040c457aef56</t>
-  </si>
-  <si>
-    <t>02/22/2026 5:24:17 PM</t>
-  </si>
-  <si>
-    <t>Truck 32</t>
-  </si>
-  <si>
-    <t>400 Mohawk Street, Bossier City, LA, 71111</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544587e1-f1a0-5bc7-861f-1b9b99a80fc5</t>
-  </si>
-  <si>
-    <t>02/19/2026 2:42:11 PM</t>
-  </si>
-  <si>
-    <t>256 Lake Street, Shreveport, LA, 71101</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544577da-7412-5f6c-bdf8-93d6ff5f4596</t>
-  </si>
-  <si>
-    <t>02/18/2026 7:11:25 AM</t>
-  </si>
-  <si>
-    <t>Purple Heart Trail, Sylverino, AR, 71837</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457117-68f6-57d2-b199-3ec2fb8c6ed5</t>
-  </si>
-  <si>
-    <t>02/18/2026 6:16:07 AM</t>
-  </si>
-  <si>
-    <t>2885 East 19th Street, Texarkana, AR, 71854</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544570e4-c994-5119-93b7-f44ae8331bb3</t>
-  </si>
-  <si>
-    <t>02/17/2026 8:34:39 PM</t>
-  </si>
-  <si>
-    <t>3253 North Market Street, Shreveport, LA, 71107</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456ed0-6ec9-532e-b61f-a1271f020eb5</t>
-  </si>
-  <si>
-    <t>02/17/2026 9:42:24 AM</t>
-  </si>
-  <si>
-    <t>499 White Street, Belcher, LA, 71004</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456c7b-45c0-5ae6-8d93-17dfded89504</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1418,33 +1373,33 @@
         <v>23</v>
       </c>
       <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
         <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -1453,10 +1408,10 @@
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
         <v>23</v>
@@ -1465,7 +1420,7 @@
         <v>23</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O3" t="s">
         <v>35</v>
@@ -1482,7 +1437,7 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1512,54 +1467,54 @@
         <v>23</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>47</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
         <v>48</v>
       </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>49</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
         <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" t="s">
-        <v>23</v>
       </c>
       <c r="O5" t="s">
         <v>51</v>
@@ -1576,16 +1531,16 @@
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1594,10 +1549,10 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -1623,16 +1578,16 @@
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1641,45 +1596,45 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N7" t="s">
         <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1697,7 +1652,7 @@
         <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
         <v>23</v>
@@ -1711,22 +1666,22 @@
         <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1735,92 +1690,92 @@
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N9" t="s">
         <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
-        <v>82</v>
-      </c>
-      <c r="K10" t="s">
-        <v>83</v>
-      </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" t="s">
-        <v>23</v>
-      </c>
       <c r="N10" t="s">
         <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1829,10 +1784,10 @@
         <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L11" t="s">
         <v>23</v>
@@ -1844,42 +1799,42 @@
         <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" t="s">
         <v>95</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
         <v>96</v>
       </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>97</v>
-      </c>
-      <c r="K12" t="s">
-        <v>56</v>
       </c>
       <c r="L12" t="s">
         <v>23</v>
@@ -1899,23 +1854,23 @@
         <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" t="s">
         <v>47</v>
       </c>
-      <c r="G13" t="s">
-        <v>100</v>
-      </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
@@ -1923,10 +1878,10 @@
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="K13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s">
         <v>23</v>
@@ -1938,18 +1893,18 @@
         <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -1958,10 +1913,10 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -1970,10 +1925,10 @@
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="K14" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L14" t="s">
         <v>23</v>
@@ -1982,33 +1937,33 @@
         <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2017,58 +1972,58 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="K15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s">
         <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N15" t="s">
         <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" t="s">
         <v>79</v>
       </c>
-      <c r="D16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
-        <v>115</v>
-      </c>
-      <c r="K16" t="s">
-        <v>116</v>
-      </c>
       <c r="L16" t="s">
         <v>23</v>
       </c>
@@ -2076,280 +2031,280 @@
         <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="O16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
         <v>120</v>
       </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>121</v>
       </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" t="s">
+        <v>79</v>
+      </c>
+      <c r="N17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" t="s">
         <v>122</v>
-      </c>
-      <c r="K17" t="s">
-        <v>123</v>
-      </c>
-      <c r="L17" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
         <v>125</v>
       </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>126</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" t="s">
         <v>127</v>
-      </c>
-      <c r="L18" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" t="s">
-        <v>64</v>
-      </c>
-      <c r="N18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
         <v>129</v>
       </c>
-      <c r="B19" t="s">
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
         <v>130</v>
       </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>131</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
         <v>132</v>
-      </c>
-      <c r="L19" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" t="s">
-        <v>64</v>
-      </c>
-      <c r="N19" t="s">
-        <v>23</v>
-      </c>
-      <c r="O19" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
         <v>134</v>
       </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="K20" t="s">
         <v>135</v>
       </c>
-      <c r="G20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" t="s">
+        <v>79</v>
+      </c>
+      <c r="N20" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" t="s">
         <v>136</v>
-      </c>
-      <c r="K20" t="s">
-        <v>137</v>
-      </c>
-      <c r="L20" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" t="s">
-        <v>23</v>
-      </c>
-      <c r="N20" t="s">
-        <v>23</v>
-      </c>
-      <c r="O20" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
         <v>139</v>
       </c>
-      <c r="B21" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>130</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="K21" t="s">
         <v>140</v>
       </c>
-      <c r="H21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="L21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" t="s">
+        <v>79</v>
+      </c>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" t="s">
         <v>141</v>
-      </c>
-      <c r="K21" t="s">
-        <v>142</v>
-      </c>
-      <c r="L21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M21" t="s">
-        <v>64</v>
-      </c>
-      <c r="N21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" t="s">
         <v>144</v>
       </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>145</v>
-      </c>
-      <c r="K22" t="s">
-        <v>25</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
@@ -2369,22 +2324,22 @@
         <v>147</v>
       </c>
       <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" t="s">
         <v>148</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>135</v>
-      </c>
-      <c r="G23" t="s">
-        <v>31</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
@@ -2396,42 +2351,42 @@
         <v>149</v>
       </c>
       <c r="K23" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s">
         <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N23" t="s">
         <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
@@ -2443,101 +2398,101 @@
         <v>153</v>
       </c>
       <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" t="s">
         <v>154</v>
-      </c>
-      <c r="L24" t="s">
-        <v>23</v>
-      </c>
-      <c r="M24" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" t="s">
-        <v>23</v>
-      </c>
-      <c r="O24" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" t="s">
         <v>156</v>
       </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
+        <v>86</v>
+      </c>
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" t="s">
         <v>157</v>
-      </c>
-      <c r="K25" t="s">
-        <v>158</v>
-      </c>
-      <c r="L25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M25" t="s">
-        <v>64</v>
-      </c>
-      <c r="N25" t="s">
-        <v>23</v>
-      </c>
-      <c r="O25" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
         <v>160</v>
       </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>161</v>
-      </c>
-      <c r="K26" t="s">
-        <v>63</v>
       </c>
       <c r="L26" t="s">
         <v>23</v>
@@ -2557,22 +2512,22 @@
         <v>163</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
         <v>47</v>
-      </c>
-      <c r="G27" t="s">
-        <v>31</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
@@ -2590,7 +2545,7 @@
         <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N27" t="s">
         <v>23</v>
@@ -2604,104 +2559,104 @@
         <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" t="s">
         <v>168</v>
       </c>
-      <c r="H28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" t="s">
-        <v>121</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" t="s">
         <v>169</v>
-      </c>
-      <c r="K28" t="s">
-        <v>170</v>
-      </c>
-      <c r="L28" t="s">
-        <v>23</v>
-      </c>
-      <c r="M28" t="s">
-        <v>23</v>
-      </c>
-      <c r="N28" t="s">
-        <v>23</v>
-      </c>
-      <c r="O28" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" t="s">
         <v>172</v>
       </c>
-      <c r="B29" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" t="s">
-        <v>23</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="L29" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" t="s">
+        <v>23</v>
+      </c>
+      <c r="O29" t="s">
         <v>173</v>
-      </c>
-      <c r="K29" t="s">
-        <v>174</v>
-      </c>
-      <c r="L29" t="s">
-        <v>23</v>
-      </c>
-      <c r="M29" t="s">
-        <v>64</v>
-      </c>
-      <c r="N29" t="s">
-        <v>23</v>
-      </c>
-      <c r="O29" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -2710,163 +2665,163 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
+        <v>143</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" t="s">
+        <v>176</v>
+      </c>
+      <c r="K30" t="s">
         <v>177</v>
       </c>
-      <c r="G30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" t="s">
-        <v>121</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="L30" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30" t="s">
         <v>178</v>
-      </c>
-      <c r="K30" t="s">
-        <v>90</v>
-      </c>
-      <c r="L30" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" t="s">
-        <v>23</v>
-      </c>
-      <c r="N30" t="s">
-        <v>23</v>
-      </c>
-      <c r="O30" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
         <v>180</v>
       </c>
-      <c r="B31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="K31" t="s">
         <v>181</v>
       </c>
-      <c r="H31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
+        <v>79</v>
+      </c>
+      <c r="N31" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" t="s">
         <v>182</v>
-      </c>
-      <c r="K31" t="s">
-        <v>183</v>
-      </c>
-      <c r="L31" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" t="s">
-        <v>23</v>
-      </c>
-      <c r="N31" t="s">
-        <v>184</v>
-      </c>
-      <c r="O31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>184</v>
+      </c>
+      <c r="G32" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" t="s">
+        <v>185</v>
+      </c>
+      <c r="K32" t="s">
+        <v>104</v>
+      </c>
+      <c r="L32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" t="s">
         <v>186</v>
-      </c>
-      <c r="B32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>47</v>
-      </c>
-      <c r="G32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" t="s">
-        <v>173</v>
-      </c>
-      <c r="K32" t="s">
-        <v>56</v>
-      </c>
-      <c r="L32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M32" t="s">
-        <v>23</v>
-      </c>
-      <c r="N32" t="s">
-        <v>23</v>
-      </c>
-      <c r="O32" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" t="s">
         <v>188</v>
       </c>
-      <c r="B33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
         <v>189</v>
       </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>190</v>
-      </c>
-      <c r="K33" t="s">
-        <v>170</v>
       </c>
       <c r="L33" t="s">
         <v>23</v>
@@ -2886,10 +2841,10 @@
         <v>193</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -2898,10 +2853,10 @@
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -2910,339 +2865,339 @@
         <v>23</v>
       </c>
       <c r="J34" t="s">
+        <v>180</v>
+      </c>
+      <c r="K34" t="s">
+        <v>71</v>
+      </c>
+      <c r="L34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" t="s">
         <v>194</v>
-      </c>
-      <c r="K34" t="s">
-        <v>195</v>
-      </c>
-      <c r="L34" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" t="s">
-        <v>23</v>
-      </c>
-      <c r="N34" t="s">
-        <v>184</v>
-      </c>
-      <c r="O34" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" t="s">
         <v>197</v>
       </c>
-      <c r="B35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="K35" t="s">
+        <v>177</v>
+      </c>
+      <c r="L35" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" t="s">
         <v>198</v>
       </c>
-      <c r="D35" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" t="s">
-        <v>121</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="O35" t="s">
         <v>199</v>
-      </c>
-      <c r="K35" t="s">
-        <v>170</v>
-      </c>
-      <c r="L35" t="s">
-        <v>23</v>
-      </c>
-      <c r="M35" t="s">
-        <v>23</v>
-      </c>
-      <c r="N35" t="s">
-        <v>23</v>
-      </c>
-      <c r="O35" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>39</v>
+      </c>
+      <c r="G36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
         <v>201</v>
       </c>
-      <c r="B36" t="s">
-        <v>148</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="K36" t="s">
         <v>202</v>
       </c>
-      <c r="D36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>135</v>
-      </c>
-      <c r="G36" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" t="s">
-        <v>121</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="L36" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" t="s">
+        <v>191</v>
+      </c>
+      <c r="O36" t="s">
         <v>203</v>
-      </c>
-      <c r="K36" t="s">
-        <v>154</v>
-      </c>
-      <c r="L36" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
         <v>205</v>
       </c>
-      <c r="B37" t="s">
-        <v>130</v>
-      </c>
-      <c r="C37" t="s">
-        <v>23</v>
-      </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" t="s">
         <v>206</v>
-      </c>
-      <c r="G37" t="s">
-        <v>140</v>
-      </c>
-      <c r="H37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" t="s">
-        <v>23</v>
       </c>
       <c r="J37" t="s">
         <v>207</v>
       </c>
       <c r="K37" t="s">
+        <v>177</v>
+      </c>
+      <c r="L37" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" t="s">
+        <v>23</v>
+      </c>
+      <c r="O37" t="s">
         <v>208</v>
-      </c>
-      <c r="L37" t="s">
-        <v>23</v>
-      </c>
-      <c r="M37" t="s">
-        <v>23</v>
-      </c>
-      <c r="N37" t="s">
-        <v>23</v>
-      </c>
-      <c r="O37" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
         <v>210</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>206</v>
+      </c>
+      <c r="J38" t="s">
         <v>211</v>
       </c>
-      <c r="C38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>39</v>
-      </c>
-      <c r="G38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L38" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" t="s">
         <v>212</v>
-      </c>
-      <c r="K38" t="s">
-        <v>213</v>
-      </c>
-      <c r="L38" t="s">
-        <v>23</v>
-      </c>
-      <c r="M38" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" t="s">
-        <v>23</v>
-      </c>
-      <c r="O38" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>138</v>
+      </c>
+      <c r="F39" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
         <v>215</v>
       </c>
-      <c r="B39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>39</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="K39" t="s">
         <v>216</v>
       </c>
-      <c r="H39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="L39" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" t="s">
         <v>217</v>
-      </c>
-      <c r="K39" t="s">
-        <v>218</v>
-      </c>
-      <c r="L39" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
         <v>220</v>
       </c>
-      <c r="B40" t="s">
+      <c r="K40" t="s">
         <v>221</v>
       </c>
-      <c r="C40" t="s">
+      <c r="L40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" t="s">
         <v>222</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>135</v>
-      </c>
-      <c r="G40" t="s">
-        <v>216</v>
-      </c>
-      <c r="H40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" t="s">
-        <v>121</v>
-      </c>
-      <c r="J40" t="s">
-        <v>223</v>
-      </c>
-      <c r="K40" t="s">
-        <v>218</v>
-      </c>
-      <c r="L40" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N40" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>224</v>
+      </c>
+      <c r="H41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" t="s">
         <v>225</v>
       </c>
-      <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" t="s">
-        <v>135</v>
-      </c>
-      <c r="G41" t="s">
-        <v>74</v>
-      </c>
-      <c r="H41" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" t="s">
-        <v>121</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>226</v>
-      </c>
-      <c r="K41" t="s">
-        <v>25</v>
       </c>
       <c r="L41" t="s">
         <v>23</v>
@@ -3262,34 +3217,34 @@
         <v>228</v>
       </c>
       <c r="B42" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="J42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K42" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="L42" t="s">
         <v>23</v>
@@ -3301,30 +3256,30 @@
         <v>23</v>
       </c>
       <c r="O42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="G43" t="s">
-        <v>233</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -3336,101 +3291,101 @@
         <v>234</v>
       </c>
       <c r="K43" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" t="s">
         <v>235</v>
-      </c>
-      <c r="L43" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>148</v>
+      </c>
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
         <v>237</v>
       </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="s">
-        <v>198</v>
-      </c>
-      <c r="D44" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" t="s">
-        <v>135</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="K44" t="s">
         <v>238</v>
       </c>
-      <c r="H44" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" t="s">
-        <v>121</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="L44" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" t="s">
         <v>239</v>
-      </c>
-      <c r="K44" t="s">
-        <v>154</v>
-      </c>
-      <c r="L44" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" t="s">
-        <v>23</v>
-      </c>
-      <c r="N44" t="s">
-        <v>23</v>
-      </c>
-      <c r="O44" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>240</v>
+      </c>
+      <c r="B45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
         <v>241</v>
       </c>
-      <c r="B45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" t="s">
-        <v>119</v>
-      </c>
-      <c r="D45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" t="s">
-        <v>30</v>
-      </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="J45" t="s">
         <v>242</v>
       </c>
       <c r="K45" t="s">
-        <v>123</v>
+        <v>243</v>
       </c>
       <c r="L45" t="s">
         <v>23</v>
@@ -3439,7 +3394,7 @@
         <v>23</v>
       </c>
       <c r="N45" t="s">
-        <v>243</v>
+        <v>23</v>
       </c>
       <c r="O45" t="s">
         <v>244</v>
@@ -3450,69 +3405,69 @@
         <v>245</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G46" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="J46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K46" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s">
         <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N46" t="s">
         <v>23</v>
       </c>
       <c r="O46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="G47" t="s">
-        <v>249</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
@@ -3524,16 +3479,16 @@
         <v>250</v>
       </c>
       <c r="K47" t="s">
+        <v>131</v>
+      </c>
+      <c r="L47" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" t="s">
         <v>251</v>
-      </c>
-      <c r="L47" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" t="s">
-        <v>23</v>
       </c>
       <c r="O47" t="s">
         <v>252</v>
@@ -3544,22 +3499,22 @@
         <v>253</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="F48" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
@@ -3571,13 +3526,13 @@
         <v>254</v>
       </c>
       <c r="K48" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s">
         <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="N48" t="s">
         <v>23</v>
@@ -3591,10 +3546,10 @@
         <v>256</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -3603,10 +3558,10 @@
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>257</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
@@ -3615,10 +3570,10 @@
         <v>23</v>
       </c>
       <c r="J49" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L49" t="s">
         <v>23</v>
@@ -3630,48 +3585,48 @@
         <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s">
         <v>47</v>
       </c>
-      <c r="G50" t="s">
-        <v>74</v>
-      </c>
       <c r="H50" t="s">
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="J50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K50" t="s">
-        <v>262</v>
+        <v>91</v>
       </c>
       <c r="L50" t="s">
         <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N50" t="s">
         <v>23</v>
@@ -3685,40 +3640,40 @@
         <v>264</v>
       </c>
       <c r="B51" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" t="s">
+        <v>175</v>
+      </c>
+      <c r="H51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" t="s">
         <v>265</v>
       </c>
-      <c r="D51" t="s">
-        <v>46</v>
-      </c>
-      <c r="E51" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" t="s">
-        <v>61</v>
-      </c>
-      <c r="G51" t="s">
-        <v>31</v>
-      </c>
-      <c r="H51" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" t="s">
-        <v>121</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>266</v>
       </c>
-      <c r="K51" t="s">
-        <v>195</v>
-      </c>
       <c r="L51" t="s">
         <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N51" t="s">
         <v>23</v>
@@ -3732,22 +3687,22 @@
         <v>268</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G52" t="s">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
@@ -3779,43 +3734,43 @@
         <v>272</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="C53" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
+        <v>206</v>
+      </c>
+      <c r="J53" t="s">
+        <v>274</v>
+      </c>
+      <c r="K53" t="s">
+        <v>202</v>
+      </c>
+      <c r="L53" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" t="s">
         <v>79</v>
       </c>
-      <c r="D53" t="s">
-        <v>80</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" t="s">
-        <v>168</v>
-      </c>
-      <c r="H53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J53" t="s">
-        <v>273</v>
-      </c>
-      <c r="K53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L53" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" t="s">
-        <v>23</v>
-      </c>
       <c r="N53" t="s">
-        <v>274</v>
+        <v>23</v>
       </c>
       <c r="O53" t="s">
         <v>275</v>
@@ -3826,22 +3781,22 @@
         <v>276</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="F54" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="H54" t="s">
         <v>22</v>
@@ -3853,42 +3808,42 @@
         <v>277</v>
       </c>
       <c r="K54" t="s">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="L54" t="s">
         <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N54" t="s">
         <v>23</v>
       </c>
       <c r="O54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
@@ -3900,7 +3855,7 @@
         <v>281</v>
       </c>
       <c r="K55" t="s">
-        <v>251</v>
+        <v>25</v>
       </c>
       <c r="L55" t="s">
         <v>23</v>
@@ -3909,33 +3864,33 @@
         <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="O55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
@@ -3944,57 +3899,57 @@
         <v>23</v>
       </c>
       <c r="J56" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K56" t="s">
-        <v>258</v>
+        <v>71</v>
       </c>
       <c r="L56" t="s">
         <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N56" t="s">
         <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>202</v>
+        <v>94</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G57" t="s">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K57" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="L57" t="s">
         <v>23</v>
@@ -4006,42 +3961,42 @@
         <v>23</v>
       </c>
       <c r="O57" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B58" t="s">
-        <v>290</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>198</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K58" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L58" t="s">
         <v>23</v>
@@ -4053,21 +4008,21 @@
         <v>23</v>
       </c>
       <c r="O58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -4076,19 +4031,19 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="J59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K59" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="L59" t="s">
         <v>23</v>
@@ -4097,198 +4052,10 @@
         <v>23</v>
       </c>
       <c r="N59" t="s">
+        <v>23</v>
+      </c>
+      <c r="O59" t="s">
         <v>296</v>
-      </c>
-      <c r="O59" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>298</v>
-      </c>
-      <c r="B60" t="s">
-        <v>44</v>
-      </c>
-      <c r="C60" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" t="s">
-        <v>61</v>
-      </c>
-      <c r="G60" t="s">
-        <v>31</v>
-      </c>
-      <c r="H60" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" t="s">
-        <v>299</v>
-      </c>
-      <c r="K60" t="s">
-        <v>56</v>
-      </c>
-      <c r="L60" t="s">
-        <v>23</v>
-      </c>
-      <c r="M60" t="s">
-        <v>64</v>
-      </c>
-      <c r="N60" t="s">
-        <v>23</v>
-      </c>
-      <c r="O60" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>301</v>
-      </c>
-      <c r="B61" t="s">
-        <v>44</v>
-      </c>
-      <c r="C61" t="s">
-        <v>45</v>
-      </c>
-      <c r="D61" t="s">
-        <v>46</v>
-      </c>
-      <c r="E61" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" t="s">
-        <v>135</v>
-      </c>
-      <c r="G61" t="s">
-        <v>31</v>
-      </c>
-      <c r="H61" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" t="s">
-        <v>23</v>
-      </c>
-      <c r="J61" t="s">
-        <v>302</v>
-      </c>
-      <c r="K61" t="s">
-        <v>303</v>
-      </c>
-      <c r="L61" t="s">
-        <v>23</v>
-      </c>
-      <c r="M61" t="s">
-        <v>23</v>
-      </c>
-      <c r="N61" t="s">
-        <v>23</v>
-      </c>
-      <c r="O61" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>305</v>
-      </c>
-      <c r="B62" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62" t="s">
-        <v>80</v>
-      </c>
-      <c r="E62" t="s">
-        <v>19</v>
-      </c>
-      <c r="F62" t="s">
-        <v>95</v>
-      </c>
-      <c r="G62" t="s">
-        <v>280</v>
-      </c>
-      <c r="H62" t="s">
-        <v>22</v>
-      </c>
-      <c r="I62" t="s">
-        <v>23</v>
-      </c>
-      <c r="J62" t="s">
-        <v>306</v>
-      </c>
-      <c r="K62" t="s">
-        <v>307</v>
-      </c>
-      <c r="L62" t="s">
-        <v>23</v>
-      </c>
-      <c r="M62" t="s">
-        <v>23</v>
-      </c>
-      <c r="N62" t="s">
-        <v>23</v>
-      </c>
-      <c r="O62" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>309</v>
-      </c>
-      <c r="B63" t="s">
-        <v>104</v>
-      </c>
-      <c r="C63" t="s">
-        <v>119</v>
-      </c>
-      <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" t="s">
-        <v>19</v>
-      </c>
-      <c r="F63" t="s">
-        <v>39</v>
-      </c>
-      <c r="G63" t="s">
-        <v>31</v>
-      </c>
-      <c r="H63" t="s">
-        <v>22</v>
-      </c>
-      <c r="I63" t="s">
-        <v>121</v>
-      </c>
-      <c r="J63" t="s">
-        <v>310</v>
-      </c>
-      <c r="K63" t="s">
-        <v>64</v>
-      </c>
-      <c r="L63" t="s">
-        <v>23</v>
-      </c>
-      <c r="M63" t="s">
-        <v>23</v>
-      </c>
-      <c r="N63" t="s">
-        <v>23</v>
-      </c>
-      <c r="O63" t="s">
-        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F7CC35E-0C04-4E53-81EB-BA9AF8EB1140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81D97BA8-E8EB-4519-A854-C85F53FD725B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="4020" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="257">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,156 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/18/2026 6:18:24 PM</t>
+  </si>
+  <si>
+    <t>Truck 6</t>
+  </si>
+  <si>
+    <t>Robert Bailey</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Rolling Stop</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Chemin Du Lac Drive, Shreveport, LA, 71105</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd07-51bc-5d00-aa54-8fd20e3a20de</t>
+  </si>
+  <si>
+    <t>06/17/2026 2:01:08 PM</t>
+  </si>
+  <si>
+    <t>Truck 32</t>
+  </si>
+  <si>
+    <t>Josh Gregory</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Mesquite, TX</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6f5-6cc4-5ec3-8b4d-ccf47f564f0e</t>
+  </si>
+  <si>
+    <t>06/15/2026 4:15:12 PM</t>
+  </si>
+  <si>
+    <t>Daniel Vanwinterswyk</t>
+  </si>
+  <si>
+    <t>Full fleet , Heavy Duty</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Wet Road, Light Traffic, Raining</t>
+  </si>
+  <si>
+    <t>I 49, Harris, LA</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd23-70ad-5f3a-a38c-08272c948c28</t>
+  </si>
+  <si>
+    <t>06/15/2026 8:32:09 AM</t>
+  </si>
+  <si>
+    <t>Truck 12</t>
+  </si>
+  <si>
+    <t>Ben Mcgough</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Purple Heart Recipients Highway, Bossier City, LA, 71111</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb7b-8094-5a3e-8bff-ebb36df00577</t>
+  </si>
+  <si>
+    <t>06/12/2026 10:25:32 PM</t>
+  </si>
+  <si>
+    <t>Truck 3</t>
+  </si>
+  <si>
+    <t>Mark Gwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Passengers, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>307 West Jackson Avenue, Haughton, LA, 71037</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bf03-6a2b-53cb-8961-6d22ce48c6f4</t>
+  </si>
+  <si>
+    <t>06/12/2026 1:46:41 PM</t>
+  </si>
+  <si>
+    <t>Truck 22</t>
+  </si>
+  <si>
+    <t>Powell, Barnes, and Deal Memorial Highway, Bienville Parish, LA</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bd28-62e9-529e-bb7a-8ba519cc45fd</t>
+  </si>
+  <si>
     <t>06/11/2026 3:36:21 PM</t>
   </si>
   <si>
@@ -71,33 +221,9 @@
     <t>Chris Mcconnell</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>I 20, Bossier Parish, LA</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b866-701f-5bfd-aaeb-bd9514759bd3</t>
   </si>
   <si>
@@ -107,9 +233,6 @@
     <t>E-1</t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>Passengers, Light Traffic</t>
   </si>
   <si>
@@ -131,9 +254,6 @@
     <t>Bryan Deshotel</t>
   </si>
   <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
     <t>Crash</t>
   </si>
   <si>
@@ -179,27 +299,18 @@
     <t>06/07/2026 3:36:18 AM</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Very Drowsy, Moderate Traffic, Night</t>
   </si>
   <si>
     <t>Purple Heart Recipients Highway, Bossier City, LA, 71104</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a139-c514-5d92-9a36-cf1a2d178afa</t>
   </si>
   <si>
     <t>06/01/2026 8:11:54 PM</t>
   </si>
   <si>
-    <t>Truck 12</t>
-  </si>
-  <si>
     <t>Josh Caldwell</t>
   </si>
   <si>
@@ -248,9 +359,6 @@
     <t>Harsh Brake</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>5755 Jewella Avenue, Shreveport, LA, 71109</t>
   </si>
   <si>
@@ -266,12 +374,6 @@
     <t>05/26/2026 2:13:56 PM</t>
   </si>
   <si>
-    <t>Truck 22</t>
-  </si>
-  <si>
-    <t>Josh Gregory</t>
-  </si>
-  <si>
     <t>Hollywood Avenue, Shreveport, LA, 71108</t>
   </si>
   <si>
@@ -302,33 +404,18 @@
     <t>05/19/2026 10:16:58 PM</t>
   </si>
   <si>
-    <t>Truck 6</t>
-  </si>
-  <si>
-    <t>Robert Bailey</t>
-  </si>
-  <si>
     <t>Wet Road, Light Traffic, Night</t>
   </si>
   <si>
     <t>142 Captain H M Shreve Boulevard, Shreveport, LA, 71115</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454362-f189-557c-ba35-902c6f5a2ed3</t>
   </si>
   <si>
     <t>05/19/2026 4:22:07 AM</t>
   </si>
   <si>
-    <t>Truck 3</t>
-  </si>
-  <si>
-    <t>Mark Gwin</t>
-  </si>
-  <si>
     <t>I 20, Haughton, LA, 71037</t>
   </si>
   <si>
@@ -389,12 +476,6 @@
     <t>Chico Leone</t>
   </si>
   <si>
-    <t>Full fleet , Heavy Duty</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
     <t>I 20, Minden, LA, 71080</t>
   </si>
   <si>
@@ -425,15 +506,9 @@
     <t>Truck 60</t>
   </si>
   <si>
-    <t>Daniel Vanwinterswyk</t>
-  </si>
-  <si>
     <t>I 20, Shreveport, LA, 71103</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e574-b7a1-5e28-96a1-5bf164776383</t>
   </si>
   <si>
@@ -599,9 +674,6 @@
     <t>03/29/2026 7:41:24 PM</t>
   </si>
   <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
     <t>2804 Dupont Street, Shreveport, LA, 71109</t>
   </si>
   <si>
@@ -714,69 +786,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451be3-0267-5712-b998-32a6b40a984f</t>
-  </si>
-  <si>
-    <t>03/19/2026 2:37:03 PM</t>
-  </si>
-  <si>
-    <t>Forward Collision Warning</t>
-  </si>
-  <si>
-    <t>7101 US 79, River Hill, TX, 75639</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450799-f498-5512-add6-e9823215d7df</t>
-  </si>
-  <si>
-    <t>03/17/2026 3:43:53 PM</t>
-  </si>
-  <si>
-    <t>Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>5221 Jewella Avenue, Shreveport, LA, 71109</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd8a-6c12-52ce-baf3-303addf7bdf3</t>
-  </si>
-  <si>
-    <t>03/17/2026 12:44:39 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fce6-554c-5558-a57e-9e8a5b08a13c</t>
-  </si>
-  <si>
-    <t>03/17/2026 8:28:46 AM</t>
-  </si>
-  <si>
-    <t>Congested</t>
-  </si>
-  <si>
-    <t>Inner Loop Expressway, Shreveport, LA, 71118</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbfc-1056-531a-8556-dc31dc98a53f</t>
-  </si>
-  <si>
-    <t>03/17/2026 8:14:03 AM</t>
-  </si>
-  <si>
-    <t>I 20;US 71, Bossier City, LA, 71171</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fbee-9601-5000-bd9a-cc9c81f9757b</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1241,24 +1250,24 @@
         <v>23</v>
       </c>
       <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
         <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -1302,22 +1311,22 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1338,30 +1347,30 @@
         <v>23</v>
       </c>
       <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
         <v>42</v>
-      </c>
-      <c r="O4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>46</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
@@ -1376,42 +1385,42 @@
         <v>47</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N5" t="s">
         <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1420,10 +1429,10 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -1435,30 +1444,30 @@
         <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1467,10 +1476,10 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -1482,18 +1491,18 @@
         <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1502,7 +1511,7 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>
@@ -1514,30 +1523,30 @@
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
         <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N8" t="s">
         <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -1549,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1561,10 +1570,10 @@
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
@@ -1576,30 +1585,30 @@
         <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -1608,10 +1617,10 @@
         <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
         <v>23</v>
@@ -1620,33 +1629,33 @@
         <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="O10" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -1655,10 +1664,10 @@
         <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="L11" t="s">
         <v>23</v>
@@ -1667,21 +1676,21 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -1690,10 +1699,10 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -1702,10 +1711,10 @@
         <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s">
         <v>23</v>
@@ -1714,33 +1723,33 @@
         <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="O12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1749,10 +1758,10 @@
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="L13" t="s">
         <v>23</v>
@@ -1764,18 +1773,18 @@
         <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -1784,10 +1793,10 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -1796,45 +1805,45 @@
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s">
         <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N14" t="s">
         <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
         <v>103</v>
       </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1843,10 +1852,10 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K15" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s">
         <v>23</v>
@@ -1858,30 +1867,30 @@
         <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -1890,10 +1899,10 @@
         <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s">
         <v>23</v>
@@ -1902,33 +1911,33 @@
         <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -1937,10 +1946,10 @@
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="L17" t="s">
         <v>23</v>
@@ -1949,21 +1958,21 @@
         <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -1972,10 +1981,10 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
@@ -1987,7 +1996,7 @@
         <v>119</v>
       </c>
       <c r="K18" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="L18" t="s">
         <v>23</v>
@@ -1996,68 +2005,68 @@
         <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
         <v>124</v>
       </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
         <v>125</v>
       </c>
-      <c r="G19" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>126</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
         <v>127</v>
-      </c>
-      <c r="L19" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" t="s">
-        <v>23</v>
-      </c>
-      <c r="O19" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2066,10 +2075,10 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -2078,7 +2087,7 @@
         <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -2093,77 +2102,77 @@
         <v>23</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" t="s">
         <v>134</v>
-      </c>
-      <c r="B21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D21" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" t="s">
-        <v>137</v>
-      </c>
-      <c r="K21" t="s">
-        <v>138</v>
-      </c>
-      <c r="L21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="G22" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
@@ -2172,139 +2181,139 @@
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K22" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="O22" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" t="s">
+        <v>142</v>
+      </c>
+      <c r="K23" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" t="s">
+        <v>143</v>
+      </c>
+      <c r="O23" t="s">
         <v>144</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" t="s">
-        <v>23</v>
-      </c>
-      <c r="J23" t="s">
-        <v>146</v>
-      </c>
-      <c r="K23" t="s">
-        <v>147</v>
-      </c>
-      <c r="L23" t="s">
-        <v>23</v>
-      </c>
-      <c r="M23" t="s">
-        <v>23</v>
-      </c>
-      <c r="N23" t="s">
-        <v>23</v>
-      </c>
-      <c r="O23" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" t="s">
         <v>149</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" t="s">
-        <v>23</v>
-      </c>
-      <c r="J24" t="s">
-        <v>151</v>
-      </c>
-      <c r="K24" t="s">
-        <v>152</v>
-      </c>
-      <c r="L24" t="s">
-        <v>23</v>
-      </c>
-      <c r="M24" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" t="s">
-        <v>23</v>
-      </c>
-      <c r="O24" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C25" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
@@ -2313,10 +2322,10 @@
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K25" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s">
         <v>23</v>
@@ -2328,124 +2337,124 @@
         <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K26" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" t="s">
         <v>160</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K26" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" t="s">
-        <v>23</v>
-      </c>
-      <c r="M26" t="s">
-        <v>23</v>
-      </c>
-      <c r="N26" t="s">
-        <v>23</v>
-      </c>
-      <c r="O26" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" t="s">
+        <v>163</v>
+      </c>
+      <c r="K27" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" t="s">
+        <v>49</v>
+      </c>
+      <c r="N27" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" t="s">
         <v>164</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>125</v>
-      </c>
-      <c r="G27" t="s">
-        <v>67</v>
-      </c>
-      <c r="H27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" t="s">
-        <v>151</v>
-      </c>
-      <c r="K27" t="s">
-        <v>63</v>
-      </c>
-      <c r="L27" t="s">
-        <v>23</v>
-      </c>
-      <c r="M27" t="s">
-        <v>23</v>
-      </c>
-      <c r="N27" t="s">
-        <v>23</v>
-      </c>
-      <c r="O27" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" t="s">
         <v>166</v>
-      </c>
-      <c r="B28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" t="s">
-        <v>21</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -2457,42 +2466,42 @@
         <v>167</v>
       </c>
       <c r="K28" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s">
         <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" t="s">
         <v>168</v>
-      </c>
-      <c r="O28" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" t="s">
         <v>170</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>77</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
@@ -2510,7 +2519,7 @@
         <v>23</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N29" t="s">
         <v>23</v>
@@ -2524,22 +2533,22 @@
         <v>174</v>
       </c>
       <c r="B30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" t="s">
         <v>175</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" t="s">
-        <v>77</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -2571,22 +2580,22 @@
         <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G31" t="s">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
@@ -2595,10 +2604,10 @@
         <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s">
         <v>23</v>
@@ -2610,30 +2619,30 @@
         <v>23</v>
       </c>
       <c r="O31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
@@ -2642,45 +2651,45 @@
         <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="K32" t="s">
-        <v>186</v>
+        <v>41</v>
       </c>
       <c r="L32" t="s">
         <v>23</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N32" t="s">
         <v>23</v>
       </c>
       <c r="O32" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
@@ -2689,42 +2698,42 @@
         <v>23</v>
       </c>
       <c r="J33" t="s">
+        <v>176</v>
+      </c>
+      <c r="K33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L33" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" t="s">
         <v>190</v>
-      </c>
-      <c r="K33" t="s">
-        <v>191</v>
-      </c>
-      <c r="L33" t="s">
-        <v>23</v>
-      </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>23</v>
-      </c>
-      <c r="O33" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>194</v>
+        <v>113</v>
       </c>
       <c r="G34" t="s">
         <v>21</v>
@@ -2736,10 +2745,10 @@
         <v>23</v>
       </c>
       <c r="J34" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K34" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="L34" t="s">
         <v>23</v>
@@ -2748,30 +2757,30 @@
         <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="O34" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G35" t="s">
         <v>31</v>
@@ -2783,104 +2792,104 @@
         <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K35" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="L35" t="s">
         <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N35" t="s">
         <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" t="s">
+        <v>200</v>
+      </c>
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
+        <v>201</v>
+      </c>
+      <c r="K36" t="s">
         <v>202</v>
       </c>
-      <c r="B36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" t="s">
-        <v>67</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="L36" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" t="s">
         <v>203</v>
-      </c>
-      <c r="I36" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" t="s">
-        <v>204</v>
-      </c>
-      <c r="K36" t="s">
-        <v>99</v>
-      </c>
-      <c r="L36" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" t="s">
+        <v>205</v>
+      </c>
+      <c r="H37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" t="s">
         <v>206</v>
       </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>194</v>
-      </c>
-      <c r="G37" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>207</v>
-      </c>
-      <c r="K37" t="s">
-        <v>73</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -2900,19 +2909,19 @@
         <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="G38" t="s">
         <v>21</v>
@@ -2924,42 +2933,42 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
+        <v>210</v>
+      </c>
+      <c r="K38" t="s">
         <v>211</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>49</v>
+      </c>
+      <c r="N38" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" t="s">
         <v>212</v>
-      </c>
-      <c r="L38" t="s">
-        <v>23</v>
-      </c>
-      <c r="M38" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" t="s">
-        <v>23</v>
-      </c>
-      <c r="O38" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" t="s">
         <v>214</v>
       </c>
-      <c r="B39" t="s">
-        <v>122</v>
-      </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G39" t="s">
         <v>21</v>
@@ -2980,7 +2989,7 @@
         <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N39" t="s">
         <v>23</v>
@@ -2994,22 +3003,22 @@
         <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
@@ -3021,7 +3030,7 @@
         <v>219</v>
       </c>
       <c r="K40" t="s">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="L40" t="s">
         <v>23</v>
@@ -3033,30 +3042,30 @@
         <v>23</v>
       </c>
       <c r="O40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="F41" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="G41" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
@@ -3065,57 +3074,57 @@
         <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L41" t="s">
         <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N41" t="s">
         <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="G42" t="s">
-        <v>226</v>
+        <v>104</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="I42" t="s">
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K42" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L42" t="s">
         <v>23</v>
@@ -3127,21 +3136,21 @@
         <v>23</v>
       </c>
       <c r="O42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -3150,7 +3159,7 @@
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -3159,16 +3168,16 @@
         <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K43" t="s">
-        <v>231</v>
+        <v>110</v>
       </c>
       <c r="L43" t="s">
         <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N43" t="s">
         <v>23</v>
@@ -3182,19 +3191,19 @@
         <v>233</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F44" t="s">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="G44" t="s">
         <v>21</v>
@@ -3209,7 +3218,7 @@
         <v>235</v>
       </c>
       <c r="K44" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="L44" t="s">
         <v>23</v>
@@ -3221,30 +3230,30 @@
         <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="G45" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
@@ -3262,48 +3271,48 @@
         <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N45" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" t="s">
         <v>241</v>
-      </c>
-      <c r="O45" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
         <v>243</v>
       </c>
-      <c r="B46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
-        <v>125</v>
-      </c>
-      <c r="G46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" t="s">
-        <v>230</v>
-      </c>
       <c r="K46" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="L46" t="s">
         <v>23</v>
@@ -3323,35 +3332,35 @@
         <v>245</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" t="s">
         <v>246</v>
       </c>
-      <c r="H47" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>247</v>
       </c>
-      <c r="K47" t="s">
-        <v>79</v>
-      </c>
       <c r="L47" t="s">
         <v>23</v>
       </c>
@@ -3359,33 +3368,33 @@
         <v>23</v>
       </c>
       <c r="N47" t="s">
+        <v>23</v>
+      </c>
+      <c r="O47" t="s">
         <v>248</v>
-      </c>
-      <c r="O47" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>249</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
         <v>250</v>
-      </c>
-      <c r="B48" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" t="s">
-        <v>161</v>
-      </c>
-      <c r="D48" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" t="s">
-        <v>76</v>
-      </c>
-      <c r="G48" t="s">
-        <v>246</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
@@ -3397,19 +3406,66 @@
         <v>251</v>
       </c>
       <c r="K48" t="s">
+        <v>115</v>
+      </c>
+      <c r="L48" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" t="s">
         <v>252</v>
       </c>
-      <c r="L48" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" t="s">
-        <v>241</v>
-      </c>
-      <c r="O48" t="s">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>253</v>
+      </c>
+      <c r="B49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>46</v>
+      </c>
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
+        <v>254</v>
+      </c>
+      <c r="K49" t="s">
+        <v>255</v>
+      </c>
+      <c r="L49" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" t="s">
+        <v>49</v>
+      </c>
+      <c r="N49" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81D97BA8-E8EB-4519-A854-C85F53FD725B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4462C7E-9387-4EF5-B0FF-D75EA8FB1F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="4020" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="243">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,135 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/25/2026 9:42:46 AM</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>Peyton Birchfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>I 20, Shreveport, LA, 71119</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff3b-c105-506b-8a52-fd8e2d148db4</t>
+  </si>
+  <si>
+    <t>06/24/2026 4:25:18 PM</t>
+  </si>
+  <si>
+    <t>Truck 45</t>
+  </si>
+  <si>
+    <t>Will Ordoyne</t>
+  </si>
+  <si>
+    <t>Full fleet , Heavy Duty</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Light Traffic</t>
+  </si>
+  <si>
+    <t>Joseph D. Waggonner Jr. Memorial Highway, Honore, LA, 71137</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fb85-eb4b-5ac7-9e55-4ace505e38a0</t>
+  </si>
+  <si>
+    <t>06/23/2026 3:35:05 PM</t>
+  </si>
+  <si>
+    <t>Truck 26</t>
+  </si>
+  <si>
+    <t>Nick Whitaker</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Jewella Avenue, Shreveport, LA, 71109</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f631-94ac-5caf-a06b-2b142c46f861</t>
+  </si>
+  <si>
+    <t>06/23/2026 6:54:31 AM</t>
+  </si>
+  <si>
+    <t>Truck 12</t>
+  </si>
+  <si>
+    <t>Ben Mcgough</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t>Slightly Drowsy, Light Traffic</t>
+  </si>
+  <si>
+    <t>Purple Heart Recipients Highway, Bossier City, LA, 71111</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f455-0038-5986-ac17-8d1b414db998</t>
+  </si>
+  <si>
+    <t>06/22/2026 9:11:54 PM</t>
+  </si>
+  <si>
+    <t>Harsh Turn</t>
+  </si>
+  <si>
+    <t>3655 Hollywood Avenue, Shreveport, LA, 71109</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f23f-9637-5131-8abb-1a5ba41a2722</t>
+  </si>
+  <si>
     <t>06/18/2026 6:18:24 PM</t>
   </si>
   <si>
@@ -71,24 +200,12 @@
     <t>Robert Bailey</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Rolling Stop</t>
   </si>
   <si>
     <t>Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Chemin Du Lac Drive, Shreveport, LA, 71105</t>
   </si>
   <si>
@@ -110,9 +227,6 @@
     <t>Following Distance</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>I 20, Mesquite, TX</t>
   </si>
   <si>
@@ -128,39 +242,21 @@
     <t>Daniel Vanwinterswyk</t>
   </si>
   <si>
-    <t>Full fleet , Heavy Duty</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Very Drowsy, Wet Road, Light Traffic, Raining</t>
   </si>
   <si>
     <t>I 49, Harris, LA</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd23-70ad-5f3a-a38c-08272c948c28</t>
   </si>
   <si>
     <t>06/15/2026 8:32:09 AM</t>
   </si>
   <si>
-    <t>Truck 12</t>
-  </si>
-  <si>
-    <t>Ben Mcgough</t>
-  </si>
-  <si>
     <t>Inattentive Driving</t>
   </si>
   <si>
-    <t>Purple Heart Recipients Highway, Bossier City, LA, 71111</t>
-  </si>
-  <si>
     <t>60</t>
   </si>
   <si>
@@ -179,9 +275,6 @@
     <t>Mark Gwin</t>
   </si>
   <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
@@ -272,12 +365,6 @@
     <t>06/10/2026 6:19:44 AM</t>
   </si>
   <si>
-    <t>SV1</t>
-  </si>
-  <si>
-    <t>Peyton Birchfield</t>
-  </si>
-  <si>
     <t>Purple Heart Recipients Highway, Shreveport, LA, 71103</t>
   </si>
   <si>
@@ -290,9 +377,6 @@
     <t>Highway 3, Plain Dealing, LA, 71064</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a8d4-88d6-5d24-82f9-fc6af04ff336</t>
   </si>
   <si>
@@ -356,9 +440,6 @@
     <t>05/26/2026 2:44:39 PM</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>5755 Jewella Avenue, Shreveport, LA, 71109</t>
   </si>
   <si>
@@ -440,9 +521,6 @@
     <t>05/08/2026 6:49:37 AM</t>
   </si>
   <si>
-    <t>Harsh Turn</t>
-  </si>
-  <si>
     <t>7682 West 70th Street, Shreveport, LA, 71129</t>
   </si>
   <si>
@@ -470,9 +548,6 @@
     <t>05/06/2026 8:26:47 AM</t>
   </si>
   <si>
-    <t>Truck 26</t>
-  </si>
-  <si>
     <t>Chico Leone</t>
   </si>
   <si>
@@ -669,123 +744,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453ec8-0786-56e8-801b-52fe84aa5748</t>
-  </si>
-  <si>
-    <t>03/29/2026 7:41:24 PM</t>
-  </si>
-  <si>
-    <t>2804 Dupont Street, Shreveport, LA, 71109</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453c30-32dc-52ca-b7da-4e104f8cd8f5</t>
-  </si>
-  <si>
-    <t>03/28/2026 2:45:32 PM</t>
-  </si>
-  <si>
-    <t>321 Greenacres Boulevard, Bossier City, LA, 71111</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544535fa-f512-51ff-b7ad-9e0dc2547809</t>
-  </si>
-  <si>
-    <t>03/26/2026 4:42:38 PM</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>2796 East 70th Street, Shreveport, LA, 71105</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c19-7101-52ac-b4c8-e817acb3fbc7</t>
-  </si>
-  <si>
-    <t>03/26/2026 10:48:31 AM</t>
-  </si>
-  <si>
-    <t>2116 North Market Street, Shreveport, LA, 71107</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452ad5-4050-5cbe-b8a4-8aff22a8fa37</t>
-  </si>
-  <si>
-    <t>03/25/2026 3:03:49 PM</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>590 Dowling Street, Shreveport, LA, 71101</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452698-a049-538e-b7a2-6711343bda6a</t>
-  </si>
-  <si>
-    <t>03/24/2026 10:00:41 AM</t>
-  </si>
-  <si>
-    <t>I 20, West Monroe, LA, 71225</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445205c-babd-5784-9af6-1aec9227df37</t>
-  </si>
-  <si>
-    <t>03/24/2026 9:24:17 AM</t>
-  </si>
-  <si>
-    <t>5258 I 20, West Monroe, LA, 71292</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445203b-696f-5cf3-bdab-5d778e998dc8</t>
-  </si>
-  <si>
-    <t>03/23/2026 4:13:30 PM</t>
-  </si>
-  <si>
-    <t>Airline Highway, Livonia, LA, 70755</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c8b-b175-5a59-918e-879eb3f9af1e</t>
-  </si>
-  <si>
-    <t>03/23/2026 3:50:01 PM</t>
-  </si>
-  <si>
-    <t>Parking Lot, Light Traffic</t>
-  </si>
-  <si>
-    <t>Shreveport, LA, 71118</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c76-3465-53e9-83e8-4d07fac3caf0</t>
-  </si>
-  <si>
-    <t>03/23/2026 1:09:15 PM</t>
-  </si>
-  <si>
-    <t>I 20, Webster Parish, LA, 71067</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451be3-0267-5712-b998-32a6b40a984f</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1238,39 +1196,39 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -1285,7 +1243,7 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -1294,13 +1252,13 @@
         <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -1311,13 +1269,13 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1332,7 +1290,7 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
         <v>40</v>
@@ -1341,265 +1299,265 @@
         <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>53</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="K6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" t="s">
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="O6" t="s">
         <v>57</v>
-      </c>
-      <c r="K6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
         <v>60</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -1608,747 +1566,747 @@
         <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" t="s">
         <v>80</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" t="s">
         <v>81</v>
       </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" t="s">
-        <v>23</v>
-      </c>
       <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
         <v>82</v>
-      </c>
-      <c r="O10" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
         <v>84</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>86</v>
       </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G15" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="O15" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K16" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K17" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K18" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" t="s">
         <v>132</v>
       </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" t="s">
-        <v>124</v>
-      </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K21" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O22" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K23" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O23" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K25" t="s">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -2360,653 +2318,653 @@
         <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K26" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K27" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="O27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G28" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K28" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="O28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K29" t="s">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C31" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K31" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O31" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="K32" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s">
-        <v>104</v>
+        <v>191</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="K33" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K34" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="O34" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K35" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O35" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
+        <v>206</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
         <v>86</v>
       </c>
-      <c r="D36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>30</v>
-      </c>
       <c r="G36" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="K36" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O36" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="K37" t="s">
-        <v>207</v>
+        <v>33</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="K38" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M38" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K39" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M39" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>218</v>
       </c>
       <c r="O39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -3015,457 +2973,222 @@
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O40" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K41" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M41" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O41" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="G42" t="s">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="H42" t="s">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>232</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O42" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K43" t="s">
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O43" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C44" t="s">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>239</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K44" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O44" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>238</v>
-      </c>
-      <c r="B45" t="s">
-        <v>151</v>
-      </c>
-      <c r="C45" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" t="s">
-        <v>46</v>
-      </c>
-      <c r="G45" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" t="s">
-        <v>23</v>
-      </c>
-      <c r="J45" t="s">
-        <v>239</v>
-      </c>
-      <c r="K45" t="s">
-        <v>240</v>
-      </c>
-      <c r="L45" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" t="s">
-        <v>49</v>
-      </c>
-      <c r="N45" t="s">
-        <v>23</v>
-      </c>
-      <c r="O45" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
         <v>242</v>
-      </c>
-      <c r="B46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
-        <v>30</v>
-      </c>
-      <c r="G46" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" t="s">
-        <v>243</v>
-      </c>
-      <c r="K46" t="s">
-        <v>48</v>
-      </c>
-      <c r="L46" t="s">
-        <v>23</v>
-      </c>
-      <c r="M46" t="s">
-        <v>23</v>
-      </c>
-      <c r="N46" t="s">
-        <v>23</v>
-      </c>
-      <c r="O46" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>245</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" t="s">
-        <v>246</v>
-      </c>
-      <c r="K47" t="s">
-        <v>247</v>
-      </c>
-      <c r="L47" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" t="s">
-        <v>23</v>
-      </c>
-      <c r="O47" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>249</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>250</v>
-      </c>
-      <c r="H48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I48" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" t="s">
-        <v>251</v>
-      </c>
-      <c r="K48" t="s">
-        <v>115</v>
-      </c>
-      <c r="L48" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" t="s">
-        <v>23</v>
-      </c>
-      <c r="O48" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>253</v>
-      </c>
-      <c r="B49" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>46</v>
-      </c>
-      <c r="G49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J49" t="s">
-        <v>254</v>
-      </c>
-      <c r="K49" t="s">
-        <v>255</v>
-      </c>
-      <c r="L49" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" t="s">
-        <v>49</v>
-      </c>
-      <c r="N49" t="s">
-        <v>23</v>
-      </c>
-      <c r="O49" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4462C7E-9387-4EF5-B0FF-D75EA8FB1F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F09C940-75DB-4705-9F3B-61ED1FD9174F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="244">
   <si>
     <t>Time</t>
   </si>
@@ -62,30 +62,96 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/02/2026 7:36:53 AM</t>
+  </si>
+  <si>
+    <t>SV1</t>
+  </si>
+  <si>
+    <t>Peyton Birchfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Forward Collision Warning</t>
+  </si>
+  <si>
+    <t>Congested</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Purple Heart Recipients Highway, Bossier City, LA, 71101</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544522d5-0638-5881-8686-8d5a61b2ad40</t>
+  </si>
+  <si>
+    <t>07/01/2026 11:21:32 AM</t>
+  </si>
+  <si>
+    <t>Truck 26</t>
+  </si>
+  <si>
+    <t>Daniel Vanwinterswyk</t>
+  </si>
+  <si>
+    <t>Full fleet , Heavy Duty</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 49, Caddo Parish, LA</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e7c-53c1-515f-982c-e4cabab70a67</t>
+  </si>
+  <si>
+    <t>06/30/2026 10:56:28 AM</t>
+  </si>
+  <si>
+    <t>Nick Whitaker</t>
+  </si>
+  <si>
+    <t>Rolling Stop</t>
+  </si>
+  <si>
+    <t>Parking Lot, Light Traffic</t>
+  </si>
+  <si>
+    <t>Coleman Avenue, Bossier City, LA, 71101</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445193f-07a4-5431-af32-31c6554e59b4</t>
+  </si>
+  <si>
     <t>06/25/2026 9:42:46 AM</t>
   </si>
   <si>
-    <t>SV1</t>
-  </si>
-  <si>
-    <t>Peyton Birchfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Obstructed Camera</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>I 20, Shreveport, LA, 71119</t>
   </si>
   <si>
@@ -104,12 +170,6 @@
     <t>Will Ordoyne</t>
   </si>
   <si>
-    <t>Full fleet , Heavy Duty</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Moderately Drowsy, Light Traffic</t>
   </si>
   <si>
@@ -125,12 +185,6 @@
     <t>06/23/2026 3:35:05 PM</t>
   </si>
   <si>
-    <t>Truck 26</t>
-  </si>
-  <si>
-    <t>Nick Whitaker</t>
-  </si>
-  <si>
     <t>Harsh Brake</t>
   </si>
   <si>
@@ -200,9 +254,6 @@
     <t>Robert Bailey</t>
   </si>
   <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
     <t>Light Traffic</t>
   </si>
   <si>
@@ -239,9 +290,6 @@
     <t>06/15/2026 4:15:12 PM</t>
   </si>
   <si>
-    <t>Daniel Vanwinterswyk</t>
-  </si>
-  <si>
     <t>Very Drowsy, Wet Road, Light Traffic, Raining</t>
   </si>
   <si>
@@ -419,9 +467,6 @@
     <t>Prospect Street, Shreveport, LA, 71104</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544570bd-a470-5d58-a9be-cd64e7aae7a4</t>
   </si>
   <si>
@@ -702,48 +747,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445641c-c872-5013-8cfe-321d5dbc917e</t>
-  </si>
-  <si>
-    <t>04/05/2026 11:42:36 AM</t>
-  </si>
-  <si>
-    <t>Pedestrians, Light Traffic</t>
-  </si>
-  <si>
-    <t>226 Captain H M Shreve Boulevard, Shreveport, LA, 71115</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455e86-59ac-5113-965f-956c021ba3f1</t>
-  </si>
-  <si>
-    <t>04/02/2026 11:35:15 AM</t>
-  </si>
-  <si>
-    <t>US 82, Crossett, AR, 71635</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454f0c-8b48-5778-9894-6f4e6ae3b3a7</t>
-  </si>
-  <si>
-    <t>03/30/2026 7:46:29 AM</t>
-  </si>
-  <si>
-    <t>Evan</t>
-  </si>
-  <si>
-    <t>121 Lakewood Point Drive, Bossier Parish, LA, 71111</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453ec8-0786-56e8-801b-52fe84aa5748</t>
   </si>
 </sst>
 </file>
@@ -1121,9 +1124,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1196,86 +1199,86 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1290,7 +1293,7 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
         <v>40</v>
@@ -1299,301 +1302,301 @@
         <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
         <v>42</v>
       </c>
-      <c r="O4" t="s">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
+      <c r="K5" t="s">
         <v>46</v>
       </c>
-      <c r="D5" t="s">
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
         <v>79</v>
       </c>
-      <c r="G10" t="s">
-        <v>62</v>
-      </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -1604,7 +1607,7 @@
         <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -1613,145 +1616,145 @@
         <v>86</v>
       </c>
       <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>87</v>
       </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>88</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" t="s">
         <v>89</v>
       </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" t="s">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
         <v>91</v>
       </c>
-      <c r="B12" t="s">
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
         <v>92</v>
       </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" t="s">
         <v>93</v>
       </c>
-      <c r="K12" t="s">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>94</v>
       </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="G13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" t="s">
         <v>96</v>
       </c>
-      <c r="B13" t="s">
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" t="s">
         <v>97</v>
       </c>
-      <c r="C13" t="s">
+      <c r="N13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" t="s">
         <v>98</v>
       </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" t="s">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>99</v>
       </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>81</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="B14" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C14" t="s">
         <v>101</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
         <v>102</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>86</v>
       </c>
       <c r="G14" t="s">
         <v>103</v>
@@ -1760,7 +1763,7 @@
         <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
         <v>104</v>
@@ -1769,19 +1772,19 @@
         <v>105</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -1789,148 +1792,148 @@
         <v>108</v>
       </c>
       <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
         <v>109</v>
       </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="K15" t="s">
         <v>110</v>
       </c>
-      <c r="G15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" t="s">
         <v>111</v>
       </c>
-      <c r="K15" t="s">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>112</v>
       </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="B16" t="s">
         <v>113</v>
       </c>
-      <c r="O15" t="s">
+      <c r="C16" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
         <v>115</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" t="s">
+        <v>97</v>
+      </c>
+      <c r="N16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" t="s">
         <v>116</v>
       </c>
-      <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>118</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
         <v>102</v>
       </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>86</v>
-      </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K17" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1939,298 +1942,298 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K18" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="O18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>132</v>
+      </c>
+      <c r="K19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>139</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" t="s">
+        <v>143</v>
+      </c>
+      <c r="K22" t="s">
+        <v>144</v>
+      </c>
+      <c r="L22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" t="s">
+        <v>97</v>
+      </c>
+      <c r="N22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" t="s">
+        <v>148</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" t="s">
-        <v>127</v>
-      </c>
-      <c r="K19" t="s">
-        <v>128</v>
-      </c>
-      <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>81</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s">
-        <v>133</v>
-      </c>
-      <c r="K20" t="s">
-        <v>134</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s">
-        <v>137</v>
-      </c>
-      <c r="K21" t="s">
-        <v>138</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>140</v>
-      </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s">
-        <v>141</v>
-      </c>
-      <c r="K22" t="s">
-        <v>142</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" t="s">
-        <v>143</v>
-      </c>
-      <c r="O22" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" t="s">
-        <v>146</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
         <v>147</v>
       </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" t="s">
+      <c r="G24" t="s">
         <v>148</v>
       </c>
-      <c r="O23" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" t="s">
-        <v>151</v>
-      </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" t="s">
         <v>152</v>
@@ -2239,630 +2242,630 @@
         <v>153</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O24" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" t="s">
         <v>156</v>
       </c>
-      <c r="H25" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>157</v>
       </c>
-      <c r="K25" t="s">
-        <v>64</v>
-      </c>
       <c r="L25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="O25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
         <v>85</v>
       </c>
       <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
+        <v>161</v>
+      </c>
+      <c r="K26" t="s">
+        <v>162</v>
+      </c>
+      <c r="L26" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" t="s">
+        <v>163</v>
+      </c>
+      <c r="O26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
         <v>18</v>
       </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" t="s">
-        <v>160</v>
-      </c>
-      <c r="K26" t="s">
-        <v>94</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>162</v>
-      </c>
-      <c r="B27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>47</v>
-      </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K27" t="s">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="O27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" t="s">
+        <v>172</v>
+      </c>
+      <c r="K28" t="s">
+        <v>81</v>
+      </c>
+      <c r="L28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>167</v>
-      </c>
-      <c r="B28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" t="s">
-        <v>62</v>
-      </c>
-      <c r="H28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s">
-        <v>168</v>
-      </c>
-      <c r="K28" t="s">
-        <v>134</v>
-      </c>
-      <c r="L28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" t="s">
-        <v>169</v>
-      </c>
-      <c r="O28" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>171</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="s">
-        <v>172</v>
-      </c>
-      <c r="D29" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>131</v>
-      </c>
-      <c r="G29" t="s">
-        <v>173</v>
-      </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K29" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>178</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K30" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="L30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="O30" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
         <v>183</v>
       </c>
-      <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
+        <v>41</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" t="s">
         <v>184</v>
-      </c>
-      <c r="K31" t="s">
-        <v>33</v>
-      </c>
-      <c r="L31" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" t="s">
-        <v>21</v>
       </c>
       <c r="O31" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>186</v>
       </c>
       <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
         <v>187</v>
       </c>
-      <c r="C32" t="s">
-        <v>74</v>
-      </c>
       <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" t="s">
+        <v>188</v>
+      </c>
+      <c r="H32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" t="s">
+        <v>189</v>
+      </c>
+      <c r="K32" t="s">
+        <v>81</v>
+      </c>
+      <c r="L32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>86</v>
+      </c>
+      <c r="G33" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
+        <v>193</v>
+      </c>
+      <c r="K33" t="s">
+        <v>194</v>
+      </c>
+      <c r="L33" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
+        <v>199</v>
+      </c>
+      <c r="K34" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" t="s">
         <v>29</v>
       </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>79</v>
-      </c>
-      <c r="G32" t="s">
-        <v>39</v>
-      </c>
-      <c r="H32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s">
-        <v>188</v>
-      </c>
-      <c r="K32" t="s">
-        <v>80</v>
-      </c>
-      <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>190</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" t="s">
-        <v>191</v>
-      </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" t="s">
-        <v>192</v>
-      </c>
-      <c r="K33" t="s">
-        <v>138</v>
-      </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>81</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G34" t="s">
-        <v>195</v>
-      </c>
-      <c r="H34" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" t="s">
-        <v>197</v>
-      </c>
-      <c r="L34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>199</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K35" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="N35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s">
-        <v>205</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>95</v>
+      </c>
+      <c r="G36" t="s">
         <v>206</v>
       </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" t="s">
-        <v>62</v>
-      </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" t="s">
         <v>207</v>
       </c>
       <c r="K36" t="s">
+        <v>153</v>
+      </c>
+      <c r="L36" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" t="s">
+        <v>97</v>
+      </c>
+      <c r="N36" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" t="s">
         <v>208</v>
       </c>
-      <c r="L36" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" t="s">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" t="s">
         <v>210</v>
       </c>
-      <c r="B37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="H37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" t="s">
         <v>211</v>
       </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>30</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="K37" t="s">
         <v>212</v>
       </c>
-      <c r="H37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s">
-        <v>160</v>
-      </c>
-      <c r="K37" t="s">
-        <v>33</v>
-      </c>
       <c r="L37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O37" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>214</v>
       </c>
@@ -2879,136 +2882,136 @@
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="K38" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O38" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="G39" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J39" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K39" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N39" t="s">
-        <v>218</v>
+        <v>23</v>
       </c>
       <c r="O39" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>226</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>39</v>
+        <v>227</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J40" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="K40" t="s">
-        <v>222</v>
+        <v>53</v>
       </c>
       <c r="L40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O40" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -3020,175 +3023,175 @@
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="K41" t="s">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="G42" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K42" t="s">
-        <v>232</v>
+        <v>97</v>
       </c>
       <c r="L42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N42" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="O42" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>177</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G43" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="N43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O43" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>239</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F09C940-75DB-4705-9F3B-61ED1FD9174F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7038BF33-0AE6-4B92-B6EC-493C908192E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="248">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>07/02/2026 7:36:53 AM</t>
+    <t>07/09/2026 4:35:48 PM</t>
   </si>
   <si>
     <t>SV1</t>
@@ -77,18 +77,99 @@
     <t xml:space="preserve">Current Trucks, Full fleet </t>
   </si>
   <si>
+    <t>Harsh Turn</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Bellevue Road, Adner, LA, 71037</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454905-db89-5f91-a7cb-0eef526b783b</t>
+  </si>
+  <si>
+    <t>07/07/2026 3:24:46 PM</t>
+  </si>
+  <si>
+    <t>Truck 8</t>
+  </si>
+  <si>
+    <t>Robert Bailey</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 20, Greenwood, LA, 71033</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453e78-1b49-5c70-a175-cd193f50a755</t>
+  </si>
+  <si>
+    <t>07/06/2026 12:15:36 AM</t>
+  </si>
+  <si>
+    <t>Donald White</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Construction, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Traffic Street, Bossier City, LA, 71101</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453611-609b-567a-afa4-7037bcc860ec</t>
+  </si>
+  <si>
+    <t>07/03/2026 12:27:36 AM</t>
+  </si>
+  <si>
+    <t>Winfield Road, Happy Meadows, LA, 71037</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544526a9-4873-5cab-b68b-570385916e4e</t>
+  </si>
+  <si>
+    <t>07/02/2026 6:36:53 AM</t>
+  </si>
+  <si>
     <t>Forward Collision Warning</t>
   </si>
   <si>
     <t>Congested</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Purple Heart Recipients Highway, Bossier City, LA, 71101</t>
   </si>
   <si>
@@ -98,7 +179,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544522d5-0638-5881-8686-8d5a61b2ad40</t>
   </si>
   <si>
-    <t>07/01/2026 11:21:32 AM</t>
+    <t>07/01/2026 10:21:32 AM</t>
   </si>
   <si>
     <t>Truck 26</t>
@@ -110,9 +191,6 @@
     <t>Full fleet , Heavy Duty</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Very Drowsy, Light Traffic</t>
   </si>
   <si>
@@ -125,7 +203,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e7c-53c1-515f-982c-e4cabab70a67</t>
   </si>
   <si>
-    <t>06/30/2026 10:56:28 AM</t>
+    <t>06/30/2026 9:56:28 AM</t>
   </si>
   <si>
     <t>Nick Whitaker</t>
@@ -146,7 +224,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445193f-07a4-5431-af32-31c6554e59b4</t>
   </si>
   <si>
-    <t>06/25/2026 9:42:46 AM</t>
+    <t>06/25/2026 8:42:46 AM</t>
   </si>
   <si>
     <t>Obstructed Camera</t>
@@ -161,7 +239,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff3b-c105-506b-8a52-fd8e2d148db4</t>
   </si>
   <si>
-    <t>06/24/2026 4:25:18 PM</t>
+    <t>06/24/2026 3:25:18 PM</t>
   </si>
   <si>
     <t>Truck 45</t>
@@ -182,15 +260,12 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fb85-eb4b-5ac7-9e55-4ace505e38a0</t>
   </si>
   <si>
-    <t>06/23/2026 3:35:05 PM</t>
+    <t>06/23/2026 2:35:05 PM</t>
   </si>
   <si>
     <t>Harsh Brake</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>Jewella Avenue, Shreveport, LA, 71109</t>
   </si>
   <si>
@@ -203,7 +278,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f631-94ac-5caf-a06b-2b142c46f861</t>
   </si>
   <si>
-    <t>06/23/2026 6:54:31 AM</t>
+    <t>06/23/2026 5:54:31 AM</t>
   </si>
   <si>
     <t>Truck 12</t>
@@ -212,9 +287,6 @@
     <t>Ben Mcgough</t>
   </si>
   <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
     <t>Slightly Drowsy, Light Traffic</t>
   </si>
   <si>
@@ -227,10 +299,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f455-0038-5986-ac17-8d1b414db998</t>
   </si>
   <si>
-    <t>06/22/2026 9:11:54 PM</t>
-  </si>
-  <si>
-    <t>Harsh Turn</t>
+    <t>06/22/2026 8:11:54 PM</t>
   </si>
   <si>
     <t>3655 Hollywood Avenue, Shreveport, LA, 71109</t>
@@ -245,18 +314,12 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f23f-9637-5131-8abb-1a5ba41a2722</t>
   </si>
   <si>
-    <t>06/18/2026 6:18:24 PM</t>
+    <t>06/18/2026 5:18:24 PM</t>
   </si>
   <si>
     <t>Truck 6</t>
   </si>
   <si>
-    <t>Robert Bailey</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>Chemin Du Lac Drive, Shreveport, LA, 71105</t>
   </si>
   <si>
@@ -266,7 +329,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd07-51bc-5d00-aa54-8fd20e3a20de</t>
   </si>
   <si>
-    <t>06/17/2026 2:01:08 PM</t>
+    <t>06/17/2026 1:01:08 PM</t>
   </si>
   <si>
     <t>Truck 32</t>
@@ -287,19 +350,22 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d6f5-6cc4-5ec3-8b4d-ccf47f564f0e</t>
   </si>
   <si>
-    <t>06/15/2026 4:15:12 PM</t>
+    <t>06/15/2026 3:15:12 PM</t>
   </si>
   <si>
     <t>Very Drowsy, Wet Road, Light Traffic, Raining</t>
   </si>
   <si>
+    <t>Coached</t>
+  </si>
+  <si>
     <t>I 49, Harris, LA</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd23-70ad-5f3a-a38c-08272c948c28</t>
   </si>
   <si>
-    <t>06/15/2026 8:32:09 AM</t>
+    <t>06/15/2026 7:32:09 AM</t>
   </si>
   <si>
     <t>Inattentive Driving</t>
@@ -314,7 +380,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb7b-8094-5a3e-8bff-ebb36df00577</t>
   </si>
   <si>
-    <t>06/12/2026 10:25:32 PM</t>
+    <t>06/12/2026 9:25:32 PM</t>
   </si>
   <si>
     <t>Truck 3</t>
@@ -323,9 +389,6 @@
     <t>Mark Gwin</t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>Passengers, Light Traffic, Night</t>
   </si>
   <si>
@@ -338,7 +401,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bf03-6a2b-53cb-8961-6d22ce48c6f4</t>
   </si>
   <si>
-    <t>06/12/2026 1:46:41 PM</t>
+    <t>06/12/2026 12:46:41 PM</t>
   </si>
   <si>
     <t>Truck 22</t>
@@ -353,10 +416,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bd28-62e9-529e-bb7a-8ba519cc45fd</t>
   </si>
   <si>
-    <t>06/11/2026 3:36:21 PM</t>
-  </si>
-  <si>
-    <t>Truck 8</t>
+    <t>06/11/2026 2:36:21 PM</t>
   </si>
   <si>
     <t>Chris Mcconnell</t>
@@ -368,7 +428,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b866-701f-5bfd-aaeb-bd9514759bd3</t>
   </si>
   <si>
-    <t>06/11/2026 11:14:55 AM</t>
+    <t>06/11/2026 10:14:55 AM</t>
   </si>
   <si>
     <t>E-1</t>
@@ -386,7 +446,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b777-1704-59bf-8138-59a3233314aa</t>
   </si>
   <si>
-    <t>06/10/2026 3:29:55 PM</t>
+    <t>06/10/2026 2:29:55 PM</t>
   </si>
   <si>
     <t>Truck 7</t>
@@ -410,7 +470,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b33a-3101-5bc3-88c8-47598da83d43</t>
   </si>
   <si>
-    <t>06/10/2026 6:19:44 AM</t>
+    <t>06/10/2026 5:19:44 AM</t>
   </si>
   <si>
     <t>Purple Heart Recipients Highway, Shreveport, LA, 71103</t>
@@ -419,7 +479,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b142-7a3d-5433-916e-4148d9a03d45</t>
   </si>
   <si>
-    <t>06/08/2026 3:02:41 PM</t>
+    <t>06/08/2026 2:02:41 PM</t>
   </si>
   <si>
     <t>Highway 3, Plain Dealing, LA, 71064</t>
@@ -428,7 +488,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a8d4-88d6-5d24-82f9-fc6af04ff336</t>
   </si>
   <si>
-    <t>06/07/2026 3:36:18 AM</t>
+    <t>06/07/2026 2:36:18 AM</t>
   </si>
   <si>
     <t>Very Drowsy, Moderate Traffic, Night</t>
@@ -440,7 +500,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a139-c514-5d92-9a36-cf1a2d178afa</t>
   </si>
   <si>
-    <t>06/01/2026 8:11:54 PM</t>
+    <t>06/01/2026 7:11:54 PM</t>
   </si>
   <si>
     <t>Josh Caldwell</t>
@@ -455,7 +515,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544585e3-1f4f-51dd-afb2-a3d08b4215a1</t>
   </si>
   <si>
-    <t>05/28/2026 5:38:57 PM</t>
+    <t>05/28/2026 4:38:57 PM</t>
   </si>
   <si>
     <t>No Seat Belt</t>
@@ -470,7 +530,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544570bd-a470-5d58-a9be-cd64e7aae7a4</t>
   </si>
   <si>
-    <t>05/28/2026 1:42:30 PM</t>
+    <t>05/28/2026 12:42:30 PM</t>
   </si>
   <si>
     <t>Patrick Lane, Shreveport, LA, 71129</t>
@@ -482,7 +542,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456fe5-2bb4-53c8-bffc-9a38de3f7a5f</t>
   </si>
   <si>
-    <t>05/26/2026 2:44:39 PM</t>
+    <t>05/26/2026 1:44:39 PM</t>
   </si>
   <si>
     <t>5755 Jewella Avenue, Shreveport, LA, 71109</t>
@@ -497,7 +557,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565d1-58a6-5441-9f56-abe9c092ae09</t>
   </si>
   <si>
-    <t>05/26/2026 2:13:56 PM</t>
+    <t>05/26/2026 1:13:56 PM</t>
   </si>
   <si>
     <t>Hollywood Avenue, Shreveport, LA, 71108</t>
@@ -512,7 +572,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544565b5-39a1-53cd-977f-90fcacd41014</t>
   </si>
   <si>
-    <t>05/23/2026 1:29:29 AM</t>
+    <t>05/23/2026 12:29:29 AM</t>
   </si>
   <si>
     <t>Moderately Drowsy, Light Traffic, Night</t>
@@ -527,7 +587,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455386-4909-57f2-8d14-451a07e58316</t>
   </si>
   <si>
-    <t>05/19/2026 10:16:58 PM</t>
+    <t>05/19/2026 9:16:58 PM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic, Night</t>
@@ -539,7 +599,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454362-f189-557c-ba35-902c6f5a2ed3</t>
   </si>
   <si>
-    <t>05/19/2026 4:22:07 AM</t>
+    <t>05/19/2026 3:22:07 AM</t>
   </si>
   <si>
     <t>I 20, Haughton, LA, 71037</t>
@@ -548,7 +608,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f8a-e21f-55c1-85e2-c9d26ee5074d</t>
   </si>
   <si>
-    <t>05/10/2026 11:46:38 PM</t>
+    <t>05/10/2026 10:46:38 PM</t>
   </si>
   <si>
     <t>Cyclist/Motorcyclist, Light Traffic, Night</t>
@@ -563,7 +623,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445155b-ccf6-5abf-82bd-50e48d633720</t>
   </si>
   <si>
-    <t>05/08/2026 6:49:37 AM</t>
+    <t>05/08/2026 5:49:37 AM</t>
   </si>
   <si>
     <t>7682 West 70th Street, Shreveport, LA, 71129</t>
@@ -575,10 +635,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445076b-fa15-5277-a1eb-c46d844f1914</t>
   </si>
   <si>
-    <t>05/06/2026 10:32:16 AM</t>
-  </si>
-  <si>
-    <t>Donald White</t>
+    <t>05/06/2026 9:32:16 AM</t>
   </si>
   <si>
     <t>Parking Lot, Congested</t>
@@ -590,7 +647,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdeb-1af8-5128-a674-bf7cc3b04f19</t>
   </si>
   <si>
-    <t>05/06/2026 8:26:47 AM</t>
+    <t>05/06/2026 7:26:47 AM</t>
   </si>
   <si>
     <t>Chico Leone</t>
@@ -605,7 +662,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fd78-370b-53d4-86fa-85c570133c70</t>
   </si>
   <si>
-    <t>05/02/2026 12:19:44 PM</t>
+    <t>05/02/2026 11:19:44 AM</t>
   </si>
   <si>
     <t>Truck 1</t>
@@ -620,7 +677,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e9b4-0f61-5508-ac64-ec6a03919a24</t>
   </si>
   <si>
-    <t>05/01/2026 4:32:04 PM</t>
+    <t>05/01/2026 3:32:04 PM</t>
   </si>
   <si>
     <t>Truck 60</t>
@@ -632,7 +689,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e574-b7a1-5e28-96a1-5bf164776383</t>
   </si>
   <si>
-    <t>04/28/2026 5:47:36 PM</t>
+    <t>04/28/2026 4:47:36 PM</t>
   </si>
   <si>
     <t>Construction, Passengers, Moderate Traffic</t>
@@ -644,7 +701,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d646-c988-5cd9-a47e-8bafc996366e</t>
   </si>
   <si>
-    <t>04/27/2026 5:32:25 AM</t>
+    <t>04/27/2026 4:32:25 AM</t>
   </si>
   <si>
     <t>Light Traffic, Night</t>
@@ -659,7 +716,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ce7f-5702-59fe-b50c-fbf25865a2dc</t>
   </si>
   <si>
-    <t>04/24/2026 5:24:06 PM</t>
+    <t>04/24/2026 4:24:06 PM</t>
   </si>
   <si>
     <t>Construction, Moderate Traffic</t>
@@ -674,7 +731,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c197-d662-5f98-875f-828cba2d84a2</t>
   </si>
   <si>
-    <t>04/24/2026 5:02:20 PM</t>
+    <t>04/24/2026 4:02:20 PM</t>
   </si>
   <si>
     <t>S1</t>
@@ -692,7 +749,7 @@
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c183-e715-5584-8f77-10fa858fef63</t>
   </si>
   <si>
-    <t>04/18/2026 1:57:17 AM</t>
+    <t>04/18/2026 12:57:17 AM</t>
   </si>
   <si>
     <t>Kendall Mckerley</t>
@@ -702,51 +759,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459f61-26fd-5c26-9f57-0f4d1a54e66b</t>
-  </si>
-  <si>
-    <t>04/10/2026 5:23:41 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445797e-6cd0-58ca-8001-1881473ac909</t>
-  </si>
-  <si>
-    <t>04/10/2026 10:36:38 AM</t>
-  </si>
-  <si>
-    <t>Naples, TX, 75568</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457809-c12a-5a86-8703-a98b57a013e8</t>
-  </si>
-  <si>
-    <t>04/07/2026 5:09:08 PM</t>
-  </si>
-  <si>
-    <t>Mansfield Road, Shreveport, LA, 71118</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544569fe-0661-5c57-9082-90a02dddf9ad</t>
-  </si>
-  <si>
-    <t>04/06/2026 1:45:01 PM</t>
-  </si>
-  <si>
-    <t>SV2</t>
-  </si>
-  <si>
-    <t>I 49, De Soto Parish, LA</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445641c-c872-5013-8cfe-321d5dbc917e</t>
   </si>
 </sst>
 </file>
@@ -1214,33 +1226,33 @@
         <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -1249,10 +1261,10 @@
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
         <v>23</v>
@@ -1264,30 +1276,30 @@
         <v>23</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1296,10 +1308,10 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -1311,12 +1323,12 @@
         <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -1331,10 +1343,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1366,69 +1378,69 @@
         <v>48</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
         <v>51</v>
       </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>52</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
         <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1437,10 +1449,10 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -1449,7 +1461,7 @@
         <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
         <v>61</v>
@@ -1460,222 +1472,222 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
         <v>63</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
         <v>64</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>65</v>
       </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
         <v>66</v>
       </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>67</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
         <v>68</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
         <v>70</v>
       </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
         <v>71</v>
       </c>
-      <c r="G9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>72</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" t="s">
         <v>73</v>
-      </c>
-      <c r="L9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" t="s">
-        <v>74</v>
-      </c>
-      <c r="O9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
         <v>76</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
         <v>77</v>
       </c>
-      <c r="C10" t="s">
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="K10" t="s">
         <v>79</v>
       </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" t="s">
         <v>80</v>
-      </c>
-      <c r="K10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>83</v>
       </c>
-      <c r="B11" t="s">
+      <c r="K11" t="s">
         <v>84</v>
       </c>
-      <c r="C11" t="s">
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
         <v>85</v>
       </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="O11" t="s">
         <v>86</v>
-      </c>
-      <c r="G11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" t="s">
         <v>90</v>
       </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
         <v>91</v>
       </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>92</v>
-      </c>
-      <c r="K12" t="s">
-        <v>53</v>
       </c>
       <c r="L12" t="s">
         <v>23</v>
@@ -1695,31 +1707,31 @@
         <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
         <v>95</v>
-      </c>
-      <c r="G13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" t="s">
-        <v>67</v>
       </c>
       <c r="K13" t="s">
         <v>96</v>
@@ -1728,10 +1740,10 @@
         <v>23</v>
       </c>
       <c r="M13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" t="s">
         <v>97</v>
-      </c>
-      <c r="N13" t="s">
-        <v>23</v>
       </c>
       <c r="O13" t="s">
         <v>98</v>
@@ -1745,195 +1757,195 @@
         <v>100</v>
       </c>
       <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
         <v>101</v>
       </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="K14" t="s">
         <v>102</v>
       </c>
-      <c r="G14" t="s">
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" t="s">
         <v>103</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>104</v>
-      </c>
-      <c r="K14" t="s">
-        <v>105</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
         <v>107</v>
       </c>
-      <c r="B15" t="s">
+      <c r="G15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
         <v>108</v>
       </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>109</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" t="s">
-        <v>23</v>
-      </c>
-      <c r="O15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
         <v>112</v>
       </c>
-      <c r="B16" t="s">
+      <c r="H16" t="s">
         <v>113</v>
       </c>
-      <c r="C16" t="s">
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
         <v>114</v>
       </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="K16" t="s">
         <v>79</v>
       </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" t="s">
         <v>115</v>
-      </c>
-      <c r="K16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" t="s">
-        <v>97</v>
-      </c>
-      <c r="N16" t="s">
-        <v>23</v>
-      </c>
-      <c r="O16" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
         <v>117</v>
       </c>
-      <c r="B17" t="s">
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" t="s">
         <v>118</v>
       </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" t="s">
         <v>119</v>
       </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="N17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" t="s">
         <v>120</v>
-      </c>
-      <c r="K17" t="s">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
         <v>123</v>
-      </c>
-      <c r="B18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" t="s">
-        <v>125</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1942,104 +1954,104 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" t="s">
         <v>126</v>
       </c>
-      <c r="G18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" t="s">
         <v>127</v>
-      </c>
-      <c r="K18" t="s">
-        <v>128</v>
-      </c>
-      <c r="L18" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" t="s">
-        <v>129</v>
-      </c>
-      <c r="O18" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>130</v>
+      </c>
+      <c r="K19" t="s">
         <v>131</v>
       </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
         <v>132</v>
-      </c>
-      <c r="K19" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" t="s">
-        <v>23</v>
-      </c>
-      <c r="O19" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
         <v>134</v>
       </c>
-      <c r="B20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G20" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -2051,13 +2063,13 @@
         <v>135</v>
       </c>
       <c r="K20" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s">
         <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="N20" t="s">
         <v>23</v>
@@ -2071,22 +2083,22 @@
         <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -2095,10 +2107,10 @@
         <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K21" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="L21" t="s">
         <v>23</v>
@@ -2110,30 +2122,30 @@
         <v>23</v>
       </c>
       <c r="O21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
@@ -2142,45 +2154,45 @@
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K22" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>149</v>
       </c>
       <c r="O22" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
@@ -2189,10 +2201,10 @@
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="L23" t="s">
         <v>23</v>
@@ -2204,15 +2216,15 @@
         <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -2224,10 +2236,10 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
@@ -2236,10 +2248,10 @@
         <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
         <v>23</v>
@@ -2251,30 +2263,30 @@
         <v>23</v>
       </c>
       <c r="O24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
@@ -2283,10 +2295,10 @@
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K25" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s">
         <v>23</v>
@@ -2295,33 +2307,33 @@
         <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="G26" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
@@ -2330,45 +2342,45 @@
         <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s">
         <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="N26" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="G27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
@@ -2377,10 +2389,10 @@
         <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K27" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="L27" t="s">
         <v>23</v>
@@ -2392,30 +2404,30 @@
         <v>23</v>
       </c>
       <c r="O27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="G28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -2427,7 +2439,7 @@
         <v>172</v>
       </c>
       <c r="K28" t="s">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s">
         <v>23</v>
@@ -2439,30 +2451,30 @@
         <v>23</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
@@ -2471,10 +2483,10 @@
         <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K29" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="L29" t="s">
         <v>23</v>
@@ -2483,33 +2495,33 @@
         <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="O29" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -2518,10 +2530,10 @@
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K30" t="s">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="L30" t="s">
         <v>23</v>
@@ -2530,33 +2542,33 @@
         <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O30" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
@@ -2565,10 +2577,10 @@
         <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K31" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="L31" t="s">
         <v>23</v>
@@ -2577,33 +2589,33 @@
         <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="O31" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>187</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="G32" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
@@ -2612,10 +2624,10 @@
         <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K32" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="L32" t="s">
         <v>23</v>
@@ -2627,30 +2639,30 @@
         <v>23</v>
       </c>
       <c r="O32" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>57</v>
+        <v>186</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
@@ -2659,10 +2671,10 @@
         <v>23</v>
       </c>
       <c r="J33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K33" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="L33" t="s">
         <v>23</v>
@@ -2674,30 +2686,30 @@
         <v>23</v>
       </c>
       <c r="O33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" t="s">
         <v>198</v>
-      </c>
-      <c r="D34" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>86</v>
-      </c>
-      <c r="G34" t="s">
-        <v>79</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -2709,7 +2721,7 @@
         <v>199</v>
       </c>
       <c r="K34" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="L34" t="s">
         <v>23</v>
@@ -2718,33 +2730,33 @@
         <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="O34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
@@ -2756,30 +2768,30 @@
         <v>203</v>
       </c>
       <c r="K35" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L35" t="s">
         <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="O35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -2788,10 +2800,10 @@
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="G36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
@@ -2800,45 +2812,45 @@
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K36" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s">
         <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N36" t="s">
         <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>211</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="G37" t="s">
-        <v>210</v>
+        <v>33</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -2847,10 +2859,10 @@
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -2862,30 +2874,30 @@
         <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="G38" t="s">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -2894,10 +2906,10 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K38" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="L38" t="s">
         <v>23</v>
@@ -2909,30 +2921,30 @@
         <v>23</v>
       </c>
       <c r="O38" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>56</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G39" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
@@ -2944,90 +2956,90 @@
         <v>222</v>
       </c>
       <c r="K39" t="s">
+        <v>118</v>
+      </c>
+      <c r="L39" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>119</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" t="s">
         <v>223</v>
-      </c>
-      <c r="L39" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" t="s">
         <v>225</v>
       </c>
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
         <v>226</v>
       </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="K40" t="s">
+        <v>173</v>
+      </c>
+      <c r="L40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" t="s">
+        <v>119</v>
+      </c>
+      <c r="N40" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" t="s">
         <v>227</v>
-      </c>
-      <c r="H40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" t="s">
-        <v>175</v>
-      </c>
-      <c r="K40" t="s">
-        <v>53</v>
-      </c>
-      <c r="L40" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N40" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>228</v>
+      </c>
+      <c r="B41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>167</v>
+      </c>
+      <c r="G41" t="s">
         <v>229</v>
       </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" t="s">
-        <v>86</v>
-      </c>
-      <c r="G41" t="s">
-        <v>148</v>
-      </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
@@ -3035,10 +3047,10 @@
         <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="K41" t="s">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="L41" t="s">
         <v>23</v>
@@ -3050,30 +3062,30 @@
         <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="G42" t="s">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -3082,10 +3094,10 @@
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K42" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="L42" t="s">
         <v>23</v>
@@ -3094,33 +3106,33 @@
         <v>23</v>
       </c>
       <c r="N42" t="s">
-        <v>233</v>
+        <v>23</v>
       </c>
       <c r="O42" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -3129,45 +3141,45 @@
         <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K43" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="L43" t="s">
         <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N43" t="s">
         <v>23</v>
       </c>
       <c r="O43" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B44" t="s">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>245</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>57</v>
+        <v>246</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
@@ -3176,10 +3188,10 @@
         <v>23</v>
       </c>
       <c r="J44" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="K44" t="s">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="L44" t="s">
         <v>23</v>
@@ -3191,7 +3203,7 @@
         <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7038BF33-0AE6-4B92-B6EC-493C908192E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C876DF0C-AAFA-4D2B-904E-A4ADA62BF800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="270">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,150 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/16/2026 8:32:10 PM</t>
+  </si>
+  <si>
+    <t>Truck 6</t>
+  </si>
+  <si>
+    <t>Robert Bailey</t>
+  </si>
+  <si>
+    <t>Full fleet , Light Duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Trucks, Full fleet </t>
+  </si>
+  <si>
+    <t>Crash</t>
+  </si>
+  <si>
+    <t>Night</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Shreveport, LA, 71137</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456dea-c51b-57ba-8f39-0daa5c07374f</t>
+  </si>
+  <si>
+    <t>07/16/2026 7:50:56 AM</t>
+  </si>
+  <si>
+    <t>Truck 12</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Greenwood Road, Shreveport, LA, 71033</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b31-d83d-5f70-a029-6478708a3838</t>
+  </si>
+  <si>
+    <t>07/16/2026 12:50:44 AM</t>
+  </si>
+  <si>
+    <t>Truck 22</t>
+  </si>
+  <si>
+    <t>Josh Gregory</t>
+  </si>
+  <si>
+    <t>West Main Street, Grand Cane, LA, 71032</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544569b1-2387-5f94-a0a0-d91ed81913cd</t>
+  </si>
+  <si>
+    <t>07/15/2026 11:09:06 AM</t>
+  </si>
+  <si>
+    <t>Truck 3</t>
+  </si>
+  <si>
+    <t>Bryan Deshotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full fleet </t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Woolworth Road, Shreveport, LA, 71047</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544566c0-e9ed-5a9b-a414-429e0aec1e1d</t>
+  </si>
+  <si>
+    <t>07/14/2026 4:06:31 PM</t>
+  </si>
+  <si>
+    <t>Truck 26</t>
+  </si>
+  <si>
+    <t>Kendall Mckerley</t>
+  </si>
+  <si>
+    <t>Severe Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>Purple Heart Recipients Highway, Shreveport, LA, 71103</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544562aa-d669-5f62-a899-52fabb8cbcce</t>
+  </si>
+  <si>
+    <t>07/14/2026 8:10:53 AM</t>
+  </si>
+  <si>
+    <t>Ben Mcgough</t>
+  </si>
+  <si>
+    <t>Slightly Drowsy</t>
+  </si>
+  <si>
+    <t>Louisiana Korean War Veterans Memorial Highway, Lakewood Village Mobile Home Park, LA, 71106</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544560f7-65a9-5a03-ba9d-9c5ef73803e7</t>
+  </si>
+  <si>
     <t>07/09/2026 4:35:48 PM</t>
   </si>
   <si>
@@ -71,24 +215,12 @@
     <t>Peyton Birchfield</t>
   </si>
   <si>
-    <t xml:space="preserve">Full fleet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Trucks, Full fleet </t>
-  </si>
-  <si>
     <t>Harsh Turn</t>
   </si>
   <si>
     <t>Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Bellevue Road, Adner, LA, 71037</t>
   </si>
   <si>
@@ -107,12 +239,6 @@
     <t>Truck 8</t>
   </si>
   <si>
-    <t>Robert Bailey</t>
-  </si>
-  <si>
-    <t>Full fleet , Light Duty</t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
@@ -182,9 +308,6 @@
     <t>07/01/2026 10:21:32 AM</t>
   </si>
   <si>
-    <t>Truck 26</t>
-  </si>
-  <si>
     <t>Daniel Vanwinterswyk</t>
   </si>
   <si>
@@ -281,21 +404,12 @@
     <t>06/23/2026 5:54:31 AM</t>
   </si>
   <si>
-    <t>Truck 12</t>
-  </si>
-  <si>
-    <t>Ben Mcgough</t>
-  </si>
-  <si>
     <t>Slightly Drowsy, Light Traffic</t>
   </si>
   <si>
     <t>Purple Heart Recipients Highway, Bossier City, LA, 71111</t>
   </si>
   <si>
-    <t>66</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f455-0038-5986-ac17-8d1b414db998</t>
   </si>
   <si>
@@ -317,9 +431,6 @@
     <t>06/18/2026 5:18:24 PM</t>
   </si>
   <si>
-    <t>Truck 6</t>
-  </si>
-  <si>
     <t>Chemin Du Lac Drive, Shreveport, LA, 71105</t>
   </si>
   <si>
@@ -335,9 +446,6 @@
     <t>Truck 32</t>
   </si>
   <si>
-    <t>Josh Gregory</t>
-  </si>
-  <si>
     <t>Following Distance</t>
   </si>
   <si>
@@ -368,24 +476,15 @@
     <t>06/15/2026 7:32:09 AM</t>
   </si>
   <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
     <t>60</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb7b-8094-5a3e-8bff-ebb36df00577</t>
   </si>
   <si>
     <t>06/12/2026 9:25:32 PM</t>
   </si>
   <si>
-    <t>Truck 3</t>
-  </si>
-  <si>
     <t>Mark Gwin</t>
   </si>
   <si>
@@ -404,9 +503,6 @@
     <t>06/12/2026 12:46:41 PM</t>
   </si>
   <si>
-    <t>Truck 22</t>
-  </si>
-  <si>
     <t>Powell, Barnes, and Deal Memorial Highway, Bienville Parish, LA</t>
   </si>
   <si>
@@ -440,9 +536,6 @@
     <t>Benton Road, Bossier City, LA, 71111</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b777-1704-59bf-8138-59a3233314aa</t>
   </si>
   <si>
@@ -452,18 +545,9 @@
     <t>Truck 7</t>
   </si>
   <si>
-    <t>Bryan Deshotel</t>
-  </si>
-  <si>
-    <t>Crash</t>
-  </si>
-  <si>
     <t>Pete Harris Drive, Shreveport, LA, 71103</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>5.50</t>
   </si>
   <si>
@@ -473,9 +557,6 @@
     <t>06/10/2026 5:19:44 AM</t>
   </si>
   <si>
-    <t>Purple Heart Recipients Highway, Shreveport, LA, 71103</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b142-7a3d-5433-916e-4148d9a03d45</t>
   </si>
   <si>
@@ -518,9 +599,6 @@
     <t>05/28/2026 4:38:57 PM</t>
   </si>
   <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
     <t>Construction, Light Traffic</t>
   </si>
   <si>
@@ -747,18 +825,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c183-e715-5584-8f77-10fa858fef63</t>
-  </si>
-  <si>
-    <t>04/18/2026 12:57:17 AM</t>
-  </si>
-  <si>
-    <t>Kendall Mckerley</t>
-  </si>
-  <si>
-    <t>Slightly Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/8005169/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459f61-26fd-5c26-9f57-0f4d1a54e66b</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1240,113 +1306,113 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
         <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="K4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
         <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1364,36 +1430,36 @@
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N5" t="s">
         <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1402,45 +1468,45 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N6" t="s">
         <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1449,10 +1515,10 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -1464,30 +1530,30 @@
         <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -1496,10 +1562,10 @@
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s">
         <v>23</v>
@@ -1508,18 +1574,18 @@
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="O8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -1531,10 +1597,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -1543,10 +1609,10 @@
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
@@ -1558,30 +1624,30 @@
         <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -1590,10 +1656,10 @@
         <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L10" t="s">
         <v>23</v>
@@ -1605,31 +1671,31 @@
         <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>82</v>
       </c>
-      <c r="G11" t="s">
-        <v>33</v>
-      </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
@@ -1637,10 +1703,10 @@
         <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
         <v>23</v>
@@ -1649,33 +1715,33 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -1684,10 +1750,10 @@
         <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L12" t="s">
         <v>23</v>
@@ -1699,30 +1765,30 @@
         <v>23</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -1731,10 +1797,10 @@
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K13" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s">
         <v>23</v>
@@ -1743,33 +1809,33 @@
         <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -1778,10 +1844,10 @@
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K14" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s">
         <v>23</v>
@@ -1793,30 +1859,30 @@
         <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -1825,10 +1891,10 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s">
         <v>23</v>
@@ -1840,42 +1906,42 @@
         <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
         <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="L16" t="s">
         <v>23</v>
@@ -1887,30 +1953,30 @@
         <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -1919,33 +1985,33 @@
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="K17" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="L17" t="s">
         <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="O17" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1954,10 +2020,10 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
@@ -1966,10 +2032,10 @@
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K18" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="L18" t="s">
         <v>23</v>
@@ -1981,30 +2047,30 @@
         <v>23</v>
       </c>
       <c r="O18" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
@@ -2013,10 +2079,10 @@
         <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s">
         <v>23</v>
@@ -2025,33 +2091,33 @@
         <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="O19" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -2060,33 +2126,33 @@
         <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="L20" t="s">
         <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
         <v>23</v>
       </c>
       <c r="O20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
@@ -2095,10 +2161,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -2107,10 +2173,10 @@
         <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K21" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s">
         <v>23</v>
@@ -2122,42 +2188,42 @@
         <v>23</v>
       </c>
       <c r="O21" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="I22" t="s">
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K22" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
@@ -2166,21 +2232,21 @@
         <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="O22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -2189,10 +2255,10 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
@@ -2201,45 +2267,45 @@
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="K23" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s">
         <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N23" t="s">
         <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
@@ -2248,10 +2314,10 @@
         <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="L24" t="s">
         <v>23</v>
@@ -2263,30 +2329,30 @@
         <v>23</v>
       </c>
       <c r="O24" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
@@ -2295,10 +2361,10 @@
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K25" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s">
         <v>23</v>
@@ -2310,30 +2376,30 @@
         <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
@@ -2342,30 +2408,30 @@
         <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K26" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="L26" t="s">
         <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="N26" t="s">
         <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2377,10 +2443,10 @@
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
@@ -2389,10 +2455,10 @@
         <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="L27" t="s">
         <v>23</v>
@@ -2404,30 +2470,30 @@
         <v>23</v>
       </c>
       <c r="O27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -2436,10 +2502,10 @@
         <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="L28" t="s">
         <v>23</v>
@@ -2448,33 +2514,33 @@
         <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="O28" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
@@ -2483,10 +2549,10 @@
         <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="L29" t="s">
         <v>23</v>
@@ -2495,21 +2561,21 @@
         <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
@@ -2518,10 +2584,10 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -2530,10 +2596,10 @@
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K30" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s">
         <v>23</v>
@@ -2542,127 +2608,127 @@
         <v>23</v>
       </c>
       <c r="N30" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30" t="s">
         <v>183</v>
-      </c>
-      <c r="O30" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" t="s">
         <v>185</v>
       </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
         <v>186</v>
       </c>
-      <c r="H31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
+        <v>163</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" t="s">
         <v>187</v>
-      </c>
-      <c r="K31" t="s">
-        <v>188</v>
-      </c>
-      <c r="L31" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" t="s">
-        <v>23</v>
-      </c>
-      <c r="N31" t="s">
-        <v>23</v>
-      </c>
-      <c r="O31" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" t="s">
         <v>190</v>
       </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>167</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="K32" t="s">
         <v>191</v>
       </c>
-      <c r="H32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="L32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" t="s">
+        <v>47</v>
+      </c>
+      <c r="N32" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" t="s">
         <v>192</v>
-      </c>
-      <c r="K32" t="s">
-        <v>102</v>
-      </c>
-      <c r="L32" t="s">
-        <v>23</v>
-      </c>
-      <c r="M32" t="s">
-        <v>23</v>
-      </c>
-      <c r="N32" t="s">
-        <v>23</v>
-      </c>
-      <c r="O32" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" t="s">
         <v>194</v>
-      </c>
-      <c r="B33" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
-        <v>39</v>
-      </c>
-      <c r="G33" t="s">
-        <v>186</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
@@ -2674,7 +2740,7 @@
         <v>195</v>
       </c>
       <c r="K33" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s">
         <v>23</v>
@@ -2694,35 +2760,35 @@
         <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="G34" t="s">
+        <v>194</v>
+      </c>
+      <c r="H34" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
         <v>198</v>
       </c>
-      <c r="H34" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>199</v>
       </c>
-      <c r="K34" t="s">
-        <v>102</v>
-      </c>
       <c r="L34" t="s">
         <v>23</v>
       </c>
@@ -2730,45 +2796,45 @@
         <v>23</v>
       </c>
       <c r="N34" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" t="s">
         <v>200</v>
-      </c>
-      <c r="O34" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" t="s">
         <v>202</v>
       </c>
-      <c r="B35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" t="s">
-        <v>23</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>203</v>
-      </c>
-      <c r="K35" t="s">
-        <v>67</v>
       </c>
       <c r="L35" t="s">
         <v>23</v>
@@ -2788,10 +2854,10 @@
         <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -2800,23 +2866,23 @@
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="G36" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
         <v>207</v>
       </c>
-      <c r="H36" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>208</v>
       </c>
-      <c r="K36" t="s">
-        <v>102</v>
-      </c>
       <c r="L36" t="s">
         <v>23</v>
       </c>
@@ -2824,33 +2890,33 @@
         <v>23</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="O36" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
-        <v>211</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -2859,10 +2925,10 @@
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K37" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -2874,30 +2940,30 @@
         <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
         <v>217</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>107</v>
-      </c>
-      <c r="G38" t="s">
-        <v>21</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -2909,7 +2975,7 @@
         <v>218</v>
       </c>
       <c r="K38" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s">
         <v>23</v>
@@ -2929,90 +2995,90 @@
         <v>220</v>
       </c>
       <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>81</v>
+      </c>
+      <c r="G39" t="s">
+        <v>212</v>
+      </c>
+      <c r="H39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
         <v>221</v>
       </c>
-      <c r="C39" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>117</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
-      </c>
-      <c r="H39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
+        <v>163</v>
+      </c>
+      <c r="L39" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" t="s">
         <v>222</v>
-      </c>
-      <c r="K39" t="s">
-        <v>118</v>
-      </c>
-      <c r="L39" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" t="s">
-        <v>119</v>
-      </c>
-      <c r="N39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>123</v>
+      </c>
+      <c r="G40" t="s">
         <v>224</v>
       </c>
-      <c r="B40" t="s">
-        <v>129</v>
-      </c>
-      <c r="C40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>117</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
         <v>225</v>
       </c>
-      <c r="H40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
+        <v>139</v>
+      </c>
+      <c r="L40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" t="s">
         <v>226</v>
-      </c>
-      <c r="K40" t="s">
-        <v>173</v>
-      </c>
-      <c r="L40" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" t="s">
-        <v>119</v>
-      </c>
-      <c r="N40" t="s">
-        <v>23</v>
       </c>
       <c r="O40" t="s">
         <v>227</v>
@@ -3023,7 +3089,7 @@
         <v>228</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -3035,175 +3101,410 @@
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G41" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" t="s">
         <v>229</v>
       </c>
-      <c r="H41" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
+        <v>108</v>
+      </c>
+      <c r="L41" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" t="s">
         <v>230</v>
       </c>
-      <c r="K41" t="s">
+      <c r="O41" t="s">
         <v>231</v>
-      </c>
-      <c r="L41" t="s">
-        <v>23</v>
-      </c>
-      <c r="M41" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" t="s">
         <v>233</v>
       </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" t="s">
-        <v>107</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" t="s">
         <v>234</v>
       </c>
-      <c r="H42" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
+        <v>139</v>
+      </c>
+      <c r="L42" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42" t="s">
         <v>235</v>
-      </c>
-      <c r="K42" t="s">
-        <v>236</v>
-      </c>
-      <c r="L42" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" t="s">
-        <v>23</v>
-      </c>
-      <c r="N42" t="s">
-        <v>23</v>
-      </c>
-      <c r="O42" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G43" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" t="s">
         <v>238</v>
       </c>
-      <c r="B43" t="s">
+      <c r="K43" t="s">
         <v>239</v>
       </c>
-      <c r="C43" t="s">
+      <c r="L43" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" t="s">
         <v>240</v>
-      </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" t="s">
-        <v>241</v>
-      </c>
-      <c r="K43" t="s">
-        <v>242</v>
-      </c>
-      <c r="L43" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>241</v>
+      </c>
+      <c r="B44" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" t="s">
+        <v>243</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
         <v>244</v>
       </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="K44" t="s">
+        <v>120</v>
+      </c>
+      <c r="L44" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" t="s">
         <v>245</v>
       </c>
-      <c r="D44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G44" t="s">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>246</v>
       </c>
-      <c r="H44" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" t="s">
-        <v>195</v>
-      </c>
-      <c r="K44" t="s">
-        <v>79</v>
-      </c>
-      <c r="L44" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" t="s">
-        <v>23</v>
-      </c>
-      <c r="N44" t="s">
-        <v>23</v>
-      </c>
-      <c r="O44" t="s">
+      <c r="B45" t="s">
         <v>247</v>
+      </c>
+      <c r="C45" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>248</v>
+      </c>
+      <c r="K45" t="s">
+        <v>153</v>
+      </c>
+      <c r="L45" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" t="s">
+        <v>47</v>
+      </c>
+      <c r="N45" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>250</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" t="s">
+        <v>251</v>
+      </c>
+      <c r="H46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
+        <v>252</v>
+      </c>
+      <c r="K46" t="s">
+        <v>199</v>
+      </c>
+      <c r="L46" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" t="s">
+        <v>47</v>
+      </c>
+      <c r="N46" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>254</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>255</v>
+      </c>
+      <c r="H47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" t="s">
+        <v>256</v>
+      </c>
+      <c r="K47" t="s">
+        <v>257</v>
+      </c>
+      <c r="L47" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" t="s">
+        <v>23</v>
+      </c>
+      <c r="O47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>259</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48" t="s">
+        <v>260</v>
+      </c>
+      <c r="H48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" t="s">
+        <v>261</v>
+      </c>
+      <c r="K48" t="s">
+        <v>262</v>
+      </c>
+      <c r="L48" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>264</v>
+      </c>
+      <c r="B49" t="s">
+        <v>265</v>
+      </c>
+      <c r="C49" t="s">
+        <v>266</v>
+      </c>
+      <c r="D49" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
+        <v>267</v>
+      </c>
+      <c r="K49" t="s">
+        <v>268</v>
+      </c>
+      <c r="L49" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -496,24 +496,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/31/2026 12:01:49 PM</t>
+          <t>08/06/2026 6:47:11 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -521,7 +517,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -535,32 +531,30 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0.535</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/30/2026 3:53:18 PM</t>
+          <t>08/06/2026 10:52:41 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -568,7 +562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -592,22 +586,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/27/2026 5:28:21 PM</t>
+          <t>08/04/2026 4:21:54 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -617,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -631,25 +625,27 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>0.736</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27/2026 7:08:38 AM</t>
+          <t>08/03/2026 7:28:46 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>John Arnold</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -688,17 +684,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/26/2026 10:40:27 AM</t>
+          <t>07/31/2026 12:01:49 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -713,7 +709,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -727,32 +723,30 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N6" t="n">
+        <v>0.535</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/26/2026 8:12:01 AM</t>
+          <t>07/30/2026 3:53:18 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -762,7 +756,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -776,28 +770,34 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>0.585</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23/2026 9:24:45 AM</t>
+          <t>07/27/2026 5:28:21 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -805,7 +805,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -819,22 +819,20 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" t="n">
+        <v>0.736</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22/2026 2:46:36 PM</t>
+          <t>07/27/2026 7:08:38 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -878,22 +876,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:05 AM</t>
+          <t>07/26/2026 10:40:27 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -903,7 +901,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -927,17 +925,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22/2026 1:42:12 AM</t>
+          <t>07/26/2026 8:12:01 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +950,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -966,34 +964,28 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N11" t="n">
+        <v>0.585</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/21/2026 10:34:37 AM</t>
+          <t>07/23/2026 9:24:45 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1001,7 +993,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1025,20 +1017,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/20/2026 4:24:06 PM</t>
+          <t>07/22/2026 2:46:36 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1046,7 +1042,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1060,30 +1056,32 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>0.798</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/20/2026 2:59:26 PM</t>
+          <t>07/22/2026 8:57:05 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1093,7 +1091,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1107,25 +1105,27 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>0.538</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/19/2026 5:07:21 PM</t>
+          <t>07/22/2026 1:42:12 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1154,25 +1154,27 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0.47</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/16/2026 9:32:10 PM</t>
+          <t>07/21/2026 10:34:37 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1187,7 +1189,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1201,23 +1203,29 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>3.691</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/16/2026 8:50:56 AM</t>
+          <t>07/20/2026 4:24:06 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Truck 32</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -1226,7 +1234,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1240,30 +1248,32 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" t="n">
+        <v>0.798</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/16/2026 1:50:44 AM</t>
+          <t>07/20/2026 2:59:26 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1271,7 +1281,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1285,32 +1295,30 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N18" t="n">
+        <v>0.538</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15/2026 12:09:06 PM</t>
+          <t>07/19/2026 5:07:21 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1320,7 +1328,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1334,27 +1342,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N19" t="n">
+        <v>0.47</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/14/2026 9:10:53 AM</t>
+          <t>07/16/2026 9:32:10 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1369,7 +1375,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1383,34 +1389,24 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" t="n">
+        <v>3.691</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09/2026 5:35:48 PM</t>
+          <t>07/16/2026 8:50:56 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SV1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1418,7 +1414,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1432,32 +1428,30 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0.586</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/07/2026 4:24:46 PM</t>
+          <t>07/16/2026 1:50:44 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1465,7 +1459,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1489,20 +1483,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/06/2026 1:15:36 AM</t>
+          <t>07/15/2026 12:09:06 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Bryan Deshotel</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1510,7 +1508,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1534,22 +1532,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/03/2026 1:27:36 AM</t>
+          <t>07/14/2026 9:10:53 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1559,7 +1557,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1583,7 +1581,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02/2026 7:36:53 AM</t>
+          <t>07/09/2026 5:35:48 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1608,7 +1606,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1622,32 +1620,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N25" t="n">
+        <v>0.586</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01/2026 11:21:32 AM</t>
+          <t>07/07/2026 4:24:46 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1657,7 +1653,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1681,24 +1677,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30/2026 10:56:28 AM</t>
+          <t>07/06/2026 1:15:36 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Donald White</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1706,7 +1698,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1730,7 +1722,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/25/2026 9:42:46 AM</t>
+          <t>07/03/2026 1:27:36 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1755,7 +1747,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1779,22 +1771,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/24/2026 4:25:18 PM</t>
+          <t>07/02/2026 7:36:53 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truck 45</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1804,7 +1796,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1828,7 +1820,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/23/2026 3:35:05 PM</t>
+          <t>07/01/2026 11:21:32 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1838,7 +1830,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1853,7 +1845,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1867,30 +1859,32 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>0.528</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/23/2026 6:54:31 AM</t>
+          <t>06/30/2026 10:56:28 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1900,7 +1894,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1924,22 +1918,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/22/2026 9:11:54 PM</t>
+          <t>06/25/2026 9:42:46 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1949,7 +1943,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1963,30 +1957,32 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>0.541</v>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/18/2026 6:18:24 PM</t>
+          <t>06/24/2026 4:25:18 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1996,7 +1992,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2020,20 +2016,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/17/2026 2:01:08 PM</t>
+          <t>06/23/2026 3:35:05 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Nick Whitaker</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2055,32 +2055,30 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N34" t="n">
+        <v>0.528</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/15/2026 4:15:12 PM</t>
+          <t>06/23/2026 6:54:31 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2096,7 +2094,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2114,7 +2112,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/15/2026 8:32:09 AM</t>
+          <t>06/22/2026 9:11:54 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2124,12 +2122,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2139,7 +2137,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2153,32 +2151,30 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.541</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/12/2026 10:25:32 PM</t>
+          <t>06/18/2026 6:18:24 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2188,7 +2184,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2212,12 +2208,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/12/2026 1:46:41 PM</t>
+          <t>06/17/2026 2:01:08 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2233,7 +2229,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2257,22 +2253,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/11/2026 3:36:21 PM</t>
+          <t>06/15/2026 4:15:12 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2282,13 +2278,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2306,16 +2302,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/11/2026 11:14:55 AM</t>
+          <t>06/15/2026 8:32:09 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2347,17 +2351,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/10/2026 3:29:55 PM</t>
+          <t>06/12/2026 10:25:32 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2372,7 +2376,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2386,32 +2390,30 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
-        <v>5.497</v>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/10/2026 6:19:44 AM</t>
+          <t>06/12/2026 1:46:41 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2443,16 +2445,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/08/2026 3:02:41 PM</t>
+          <t>06/11/2026 3:36:21 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+          <t>Truck 8</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2460,7 +2470,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2484,24 +2494,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/07/2026 3:36:18 AM</t>
+          <t>06/11/2026 11:14:55 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SV1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2509,7 +2511,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2533,22 +2535,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/01/2026 8:11:54 PM</t>
+          <t>06/10/2026 3:29:55 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2558,7 +2560,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2572,26 +2574,32 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N45" t="n">
+        <v>5.497</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05/28/2026 5:38:57 PM</t>
+          <t>06/10/2026 6:19:44 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>SV1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2599,7 +2607,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2623,12 +2631,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>05/28/2026 1:42:30 PM</t>
+          <t>06/08/2026 3:02:41 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>E-1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2640,7 +2648,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2664,22 +2672,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>05/26/2026 2:44:39 PM</t>
+          <t>06/07/2026 3:36:18 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2689,7 +2697,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2703,28 +2711,34 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>0.484</v>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>05/26/2026 2:13:56 PM</t>
+          <t>06/01/2026 8:11:54 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Josh Caldwell</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2732,7 +2746,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2746,32 +2760,26 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>0.502</v>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>05/23/2026 1:29:29 AM</t>
+          <t>05/28/2026 5:38:57 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SV1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2779,7 +2787,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2803,24 +2811,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>05/19/2026 10:16:58 PM</t>
+          <t>05/28/2026 1:42:30 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 6</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Robert Bailey</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Truck 7</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2852,22 +2852,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>05/19/2026 4:22:07 AM</t>
+          <t>05/26/2026 2:44:39 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2891,34 +2891,28 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N52" t="n">
+        <v>0.484</v>
       </c>
       <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>05/10/2026 11:46:38 PM</t>
+          <t>05/26/2026 2:13:56 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2941,23 +2935,31 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.502</v>
       </c>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>05/08/2026 6:49:37 AM</t>
+          <t>05/23/2026 1:29:29 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 7</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>SV1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2965,7 +2967,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2979,28 +2981,34 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>0.486</v>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>05/06/2026 10:32:16 AM</t>
+          <t>05/19/2026 10:16:58 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3032,22 +3040,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05/06/2026 8:26:47 AM</t>
+          <t>05/19/2026 4:22:07 AM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chico Leone</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3057,7 +3065,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,20 +496,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/06/2026 6:47:11 PM</t>
+          <t>08/14/2026 12:42:32 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Nick Whitaker</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -541,20 +545,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/06/2026 10:52:41 AM</t>
+          <t>08/12/2026 11:53:33 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -562,13 +570,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -586,7 +594,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/04/2026 4:21:54 PM</t>
+          <t>08/12/2026 9:28:11 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -611,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -635,32 +643,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/03/2026 7:28:46 PM</t>
+          <t>08/12/2026 8:49:07 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>John Arnold</t>
+          <t>Jason Scott</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -684,22 +692,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/31/2026 12:01:49 PM</t>
+          <t>08/11/2026 2:19:50 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -709,7 +717,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -723,30 +731,32 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>0.535</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/30/2026 3:53:18 PM</t>
+          <t>08/11/2026 10:53:25 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -756,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -780,17 +790,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/27/2026 5:28:21 PM</t>
+          <t>08/07/2026 3:29:42 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -820,31 +830,27 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.736</v>
+        <v>0.625</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/27/2026 7:08:38 AM</t>
+          <t>08/07/2026 7:34:14 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -876,24 +882,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/26/2026 10:40:27 AM</t>
+          <t>08/06/2026 6:47:11 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -901,7 +903,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -925,24 +927,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/26/2026 8:12:01 AM</t>
+          <t>08/06/2026 10:52:41 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -950,7 +948,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -964,28 +962,34 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>0.585</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/23/2026 9:24:45 AM</t>
+          <t>08/04/2026 4:21:54 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1017,7 +1021,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22/2026 2:46:36 PM</t>
+          <t>08/03/2026 7:28:46 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1027,7 +1031,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>John Arnold</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1066,22 +1070,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:05 AM</t>
+          <t>07/31/2026 12:01:49 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1105,32 +1109,30 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N14" t="n">
+        <v>0.535</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22/2026 1:42:12 AM</t>
+          <t>07/30/2026 3:53:18 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1140,7 +1142,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1164,22 +1166,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/21/2026 10:34:37 AM</t>
+          <t>07/27/2026 5:28:21 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1189,7 +1191,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1203,30 +1205,32 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" t="n">
+        <v>0.736</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/20/2026 4:24:06 PM</t>
+          <t>07/27/2026 7:08:38 AM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1248,15 +1252,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.798</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/20/2026 2:59:26 PM</t>
+          <t>07/26/2026 10:40:27 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1281,7 +1287,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1295,25 +1301,27 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>0.538</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/19/2026 5:07:21 PM</t>
+          <t>07/26/2026 8:12:01 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1343,31 +1351,27 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>0.47</v>
+        <v>0.585</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/16/2026 9:32:10 PM</t>
+          <t>07/23/2026 9:24:45 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1389,24 +1393,34 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>3.691</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/16/2026 8:50:56 AM</t>
+          <t>07/22/2026 2:46:36 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>Truck 1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1414,7 +1428,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1438,20 +1452,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/16/2026 1:50:44 AM</t>
+          <t>07/22/2026 8:57:05 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Nick Whitaker</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1459,7 +1477,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1483,22 +1501,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15/2026 12:09:06 PM</t>
+          <t>07/22/2026 1:42:12 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1508,7 +1526,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1532,17 +1550,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/14/2026 9:10:53 AM</t>
+          <t>07/21/2026 10:34:37 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1581,24 +1599,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09/2026 5:35:48 PM</t>
+          <t>07/20/2026 4:24:06 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1606,7 +1620,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1621,29 +1635,29 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>0.586</v>
+        <v>0.798</v>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07/2026 4:24:46 PM</t>
+          <t>07/20/2026 4:20:33 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1653,13 +1667,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1677,20 +1691,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/06/2026 1:15:36 AM</t>
+          <t>07/20/2026 2:59:26 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1698,7 +1716,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1712,32 +1730,30 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" t="n">
+        <v>0.538</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/03/2026 1:27:36 AM</t>
+          <t>07/19/2026 5:07:21 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1747,7 +1763,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1761,32 +1777,30 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N28" t="n">
+        <v>0.47</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02/2026 7:36:53 AM</t>
+          <t>07/16/2026 9:32:10 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1796,7 +1810,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1810,34 +1824,24 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N29" t="n">
+        <v>3.691</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01/2026 11:21:32 AM</t>
+          <t>07/16/2026 8:50:56 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 26</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Daniel Vanwinterswyk</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1869,24 +1873,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30/2026 10:56:28 AM</t>
+          <t>07/16/2026 1:50:44 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1918,17 +1918,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/25/2026 9:42:46 AM</t>
+          <t>07/15/2026 12:09:06 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1967,22 +1967,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/24/2026 4:25:18 PM</t>
+          <t>07/14/2026 9:10:53 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 45</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2016,22 +2016,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/23/2026 3:35:05 PM</t>
+          <t>07/09/2026 5:35:48 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2056,24 +2056,24 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>0.528</v>
+        <v>0.586</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/23/2026 6:54:31 AM</t>
+          <t>07/07/2026 4:24:46 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2112,24 +2112,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/22/2026 9:11:54 PM</t>
+          <t>07/06/2026 1:15:36 AM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Donald White</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2137,7 +2133,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2151,30 +2147,32 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>0.541</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/18/2026 6:18:24 PM</t>
+          <t>07/03/2026 1:27:36 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2184,7 +2182,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2208,20 +2206,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/17/2026 2:01:08 PM</t>
+          <t>07/02/2026 7:36:53 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2229,7 +2231,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2253,12 +2255,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/15/2026 4:15:12 PM</t>
+          <t>07/01/2026 11:21:32 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2284,7 +2286,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2302,22 +2304,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/15/2026 8:32:09 AM</t>
+          <t>06/30/2026 10:56:28 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2327,7 +2329,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2351,17 +2353,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/12/2026 10:25:32 PM</t>
+          <t>06/25/2026 9:42:46 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2376,7 +2378,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2400,20 +2402,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/12/2026 1:46:41 PM</t>
+          <t>06/24/2026 4:25:18 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Will Ordoyne</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2421,7 +2427,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2445,22 +2451,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/11/2026 3:36:21 PM</t>
+          <t>06/23/2026 3:35:05 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2470,7 +2476,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2484,26 +2490,32 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N43" t="n">
+        <v>0.528</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/11/2026 11:14:55 AM</t>
+          <t>06/23/2026 6:54:31 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2511,7 +2523,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2535,22 +2547,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/10/2026 3:29:55 PM</t>
+          <t>06/22/2026 9:11:54 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2560,7 +2572,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2575,29 +2587,29 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>5.497</v>
+        <v>0.541</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/10/2026 6:19:44 AM</t>
+          <t>06/18/2026 6:18:24 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2607,7 +2619,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2631,15 +2643,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/08/2026 3:02:41 PM</t>
+          <t>06/17/2026 2:01:08 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Truck 32</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
@@ -2648,7 +2664,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2672,22 +2688,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/07/2026 3:36:18 AM</t>
+          <t>06/15/2026 4:15:12 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2703,7 +2719,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2721,7 +2737,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/01/2026 8:11:54 PM</t>
+          <t>06/15/2026 8:32:09 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2731,7 +2747,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2770,16 +2786,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>05/28/2026 5:38:57 PM</t>
+          <t>06/12/2026 10:25:32 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>Truck 3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2787,7 +2811,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2811,15 +2835,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>05/28/2026 1:42:30 PM</t>
+          <t>06/12/2026 1:46:41 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 7</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Truck 22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
@@ -2828,7 +2856,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2852,7 +2880,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>05/26/2026 2:44:39 PM</t>
+          <t>06/11/2026 3:36:21 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2877,7 +2905,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2891,27 +2919,25 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>0.484</v>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>05/26/2026 2:13:56 PM</t>
+          <t>06/11/2026 11:14:55 AM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 22</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
@@ -2920,7 +2946,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2934,25 +2960,27 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>0.502</v>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>05/23/2026 1:29:29 AM</t>
+          <t>06/10/2026 3:29:55 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2967,7 +2995,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2981,32 +3009,30 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N54" t="n">
+        <v>5.497</v>
       </c>
       <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>05/19/2026 10:16:58 PM</t>
+          <t>06/10/2026 6:19:44 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3016,7 +3042,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3040,24 +3066,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05/19/2026 4:22:07 AM</t>
+          <t>06/08/2026 3:02:41 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 3</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Mark Gwin</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3065,7 +3083,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3086,6 +3104,374 @@
       </c>
       <c r="O56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>06/07/2026 3:36:18 AM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SV1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Drowsy</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>06/01/2026 8:11:54 PM</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Josh Caldwell</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>05/28/2026 5:38:57 PM</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>05/28/2026 1:42:30 PM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Truck 7</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>05/26/2026 2:44:39 PM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Truck 8</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>05/26/2026 2:13:56 PM</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Truck 22</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>05/23/2026 1:29:29 AM</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SV1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Drowsy</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>05/19/2026 10:16:58 PM</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Truck 6</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,24 +496,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/14/2026 12:42:32 PM</t>
+          <t>08/19/2026 5:03:58 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 23</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -545,22 +541,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/12/2026 11:53:33 AM</t>
+          <t>08/17/2026 7:10:05 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,13 +566,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -594,7 +590,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/12/2026 9:28:11 AM</t>
+          <t>08/12/2026 11:53:33 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -619,13 +615,13 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -643,32 +639,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/12/2026 8:49:07 AM</t>
+          <t>08/12/2026 9:28:11 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jason Scott</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -692,17 +688,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/11/2026 2:19:50 PM</t>
+          <t>08/12/2026 8:49:07 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Jason Scott</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,12 +708,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -741,22 +737,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/11/2026 10:53:25 AM</t>
+          <t>08/11/2026 2:19:50 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,7 +762,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -790,22 +786,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/07/2026 3:29:42 PM</t>
+          <t>08/11/2026 10:53:25 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -815,7 +811,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -829,28 +825,34 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0.625</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/07/2026 7:34:14 AM</t>
+          <t>08/07/2026 3:29:42 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -858,7 +860,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -872,27 +874,25 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" t="n">
+        <v>0.625</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/06/2026 6:47:11 PM</t>
+          <t>08/07/2026 7:34:14 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
+          <t>Josh Gregory</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -927,17 +927,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/06/2026 10:52:41 AM</t>
+          <t>08/06/2026 6:47:11 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
+          <t>Kendall Mckerley</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -972,24 +972,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/04/2026 4:21:54 PM</t>
+          <t>08/06/2026 10:52:41 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1021,17 +1017,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/03/2026 7:28:46 PM</t>
+          <t>08/04/2026 4:21:54 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>John Arnold</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1046,7 +1042,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1070,17 +1066,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/31/2026 12:01:49 PM</t>
+          <t>08/03/2026 7:28:46 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>John Arnold</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1095,7 +1091,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1109,30 +1105,32 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>0.535</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/30/2026 3:53:18 PM</t>
+          <t>07/31/2026 12:01:49 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1142,7 +1140,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1156,27 +1154,25 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N15" t="n">
+        <v>0.535</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27/2026 5:28:21 PM</t>
+          <t>07/30/2026 3:53:18 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1191,7 +1187,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1205,30 +1201,32 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0.736</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27/2026 7:08:38 AM</t>
+          <t>07/27/2026 5:28:21 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1238,7 +1236,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1252,17 +1250,15 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" t="n">
+        <v>0.736</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/26/2026 10:40:27 AM</t>
+          <t>07/27/2026 7:08:38 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1311,17 +1307,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/26/2026 8:12:01 AM</t>
+          <t>07/26/2026 10:40:27 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1332,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1350,28 +1346,34 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0.585</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/23/2026 9:24:45 AM</t>
+          <t>07/26/2026 8:12:01 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1379,7 +1381,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1393,34 +1395,28 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" t="n">
+        <v>0.585</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/22/2026 2:46:36 PM</t>
+          <t>07/23/2026 9:24:45 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1452,22 +1448,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:05 AM</t>
+          <t>07/22/2026 2:46:36 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1477,7 +1473,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1501,22 +1497,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22/2026 1:42:12 AM</t>
+          <t>07/22/2026 8:57:05 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1526,7 +1522,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1550,7 +1546,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/21/2026 10:34:37 AM</t>
+          <t>07/22/2026 1:42:12 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1575,7 +1571,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1599,20 +1595,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/20/2026 4:24:06 PM</t>
+          <t>07/21/2026 10:34:37 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1634,32 +1634,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>0.798</v>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/20/2026 4:20:33 PM</t>
+          <t>07/20/2026 4:24:06 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1667,13 +1665,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1681,32 +1679,30 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N26" t="n">
+        <v>0.798</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20/2026 2:59:26 PM</t>
+          <t>07/20/2026 4:20:33 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1716,13 +1712,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1730,25 +1726,27 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>0.538</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/19/2026 5:07:21 PM</t>
+          <t>07/20/2026 2:59:26 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1763,7 +1761,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1778,24 +1776,24 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>0.47</v>
+        <v>0.538</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/16/2026 9:32:10 PM</t>
+          <t>07/19/2026 5:07:21 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1810,7 +1808,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1825,23 +1823,31 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>3.691</v>
+        <v>0.47</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/16/2026 8:50:56 AM</t>
+          <t>07/16/2026 9:32:10 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>Truck 6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1849,7 +1855,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1863,29 +1869,23 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N30" t="n">
+        <v>3.691</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/16/2026 1:50:44 AM</t>
+          <t>07/16/2026 8:50:56 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 22</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -1918,24 +1918,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15/2026 12:09:06 PM</t>
+          <t>07/16/2026 1:50:44 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1943,7 +1939,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1967,22 +1963,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/14/2026 9:10:53 AM</t>
+          <t>07/15/2026 12:09:06 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2016,22 +2012,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09/2026 5:35:48 PM</t>
+          <t>07/14/2026 9:10:53 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2041,7 +2037,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2055,30 +2051,32 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>0.586</v>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/07/2026 4:24:46 PM</t>
+          <t>07/09/2026 5:35:48 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2088,7 +2086,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2102,30 +2100,32 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N35" t="n">
+        <v>0.586</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/06/2026 1:15:36 AM</t>
+          <t>07/07/2026 4:24:46 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/03/2026 1:27:36 AM</t>
+          <t>07/06/2026 1:15:36 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2167,14 +2167,10 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Donald White</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2206,7 +2202,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02/2026 7:36:53 AM</t>
+          <t>07/03/2026 1:27:36 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2231,7 +2227,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2255,22 +2251,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/01/2026 11:21:32 AM</t>
+          <t>07/02/2026 7:36:53 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2280,7 +2276,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2304,7 +2300,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30/2026 10:56:28 AM</t>
+          <t>07/01/2026 11:21:32 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2314,7 +2310,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2329,7 +2325,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2353,22 +2349,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/25/2026 9:42:46 AM</t>
+          <t>06/30/2026 10:56:28 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2378,7 +2374,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2402,22 +2398,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/24/2026 4:25:18 PM</t>
+          <t>06/25/2026 9:42:46 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 45</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2427,7 +2423,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2451,17 +2447,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/23/2026 3:35:05 PM</t>
+          <t>06/24/2026 4:25:18 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2476,7 +2472,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2490,30 +2486,32 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
-        <v>0.528</v>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/23/2026 6:54:31 AM</t>
+          <t>06/23/2026 3:35:05 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2523,7 +2521,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2537,17 +2535,15 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N44" t="n">
+        <v>0.528</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/22/2026 9:11:54 PM</t>
+          <t>06/23/2026 6:54:31 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2557,12 +2553,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2572,7 +2568,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2586,30 +2582,32 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
-        <v>0.541</v>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/18/2026 6:18:24 PM</t>
+          <t>06/22/2026 9:11:54 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2619,7 +2617,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2633,30 +2631,32 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N46" t="n">
+        <v>0.541</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/17/2026 2:01:08 PM</t>
+          <t>06/18/2026 6:18:24 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2688,7 +2688,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/15/2026 4:15:12 PM</t>
+          <t>06/17/2026 2:01:08 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2698,14 +2698,10 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2713,13 +2709,13 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2737,22 +2733,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/15/2026 8:32:09 AM</t>
+          <t>06/15/2026 4:15:12 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2762,13 +2758,13 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2786,22 +2782,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/12/2026 10:25:32 PM</t>
+          <t>06/15/2026 8:32:09 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2811,7 +2807,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2835,20 +2831,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/12/2026 1:46:41 PM</t>
+          <t>06/12/2026 10:25:32 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2880,24 +2880,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/11/2026 3:36:21 PM</t>
+          <t>06/12/2026 1:46:41 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2905,7 +2901,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2929,16 +2925,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/11/2026 11:14:55 AM</t>
+          <t>06/11/2026 3:36:21 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>Truck 8</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2946,7 +2950,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2970,24 +2974,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/10/2026 3:29:55 PM</t>
+          <t>06/11/2026 11:14:55 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 7</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2995,7 +2991,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3009,25 +3005,27 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>5.497</v>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/10/2026 6:19:44 AM</t>
+          <t>06/10/2026 3:29:55 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3042,7 +3040,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3056,26 +3054,32 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N55" t="n">
+        <v>5.497</v>
       </c>
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/08/2026 3:02:41 PM</t>
+          <t>06/10/2026 6:19:44 AM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>SV1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3107,24 +3111,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/07/2026 3:36:18 AM</t>
+          <t>06/08/2026 3:02:41 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SV1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3132,7 +3128,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3156,22 +3152,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/01/2026 8:11:54 PM</t>
+          <t>06/07/2026 3:36:18 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3181,7 +3177,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3205,7 +3201,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>05/28/2026 5:38:57 PM</t>
+          <t>06/01/2026 8:11:54 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3213,8 +3209,16 @@
           <t>Truck 12</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Josh Caldwell</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3222,7 +3226,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3246,12 +3250,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>05/28/2026 1:42:30 PM</t>
+          <t>05/28/2026 5:38:57 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3287,24 +3291,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>05/26/2026 2:44:39 PM</t>
+          <t>05/28/2026 1:42:30 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truck 8</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Truck 7</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3312,7 +3308,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3326,28 +3322,34 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>0.484</v>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>05/26/2026 2:13:56 PM</t>
+          <t>05/26/2026 2:44:39 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3370,31 +3372,27 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>0.502</v>
+        <v>0.484</v>
       </c>
       <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05/23/2026 1:29:29 AM</t>
+          <t>05/26/2026 2:13:56 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3402,7 +3400,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3416,61 +3414,10 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N63" t="n">
+        <v>0.502</v>
       </c>
       <c r="O63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>05/19/2026 10:16:58 PM</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Truck 6</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Robert Bailey</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>No Seat Belt</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,19 +496,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/19/2026 5:03:58 PM</t>
+          <t>08/23/2026 1:42:43 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Truck 22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
+          <t>SV2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -541,24 +537,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/17/2026 7:10:05 AM</t>
+          <t>08/19/2026 5:03:58 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -590,22 +582,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/12/2026 11:53:33 AM</t>
+          <t>08/17/2026 7:10:05 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,13 +607,13 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -639,7 +631,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/12/2026 9:28:11 AM</t>
+          <t>08/12/2026 11:53:33 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,13 +656,13 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -688,32 +680,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/12/2026 8:49:07 AM</t>
+          <t>08/12/2026 9:28:11 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jason Scott</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -737,17 +729,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/11/2026 2:19:50 PM</t>
+          <t>08/12/2026 8:49:07 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Jason Scott</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -757,12 +749,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -786,22 +778,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/11/2026 10:53:25 AM</t>
+          <t>08/11/2026 2:19:50 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -811,7 +803,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -835,22 +827,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/07/2026 3:29:42 PM</t>
+          <t>08/11/2026 10:53:25 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -860,7 +852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -874,28 +866,34 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0.625</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/07/2026 7:34:14 AM</t>
+          <t>08/07/2026 3:29:42 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -903,7 +901,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -917,27 +915,25 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N10" t="n">
+        <v>0.625</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/06/2026 6:47:11 PM</t>
+          <t>08/07/2026 7:34:14 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
+          <t>Josh Gregory</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -972,17 +968,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/06/2026 10:52:41 AM</t>
+          <t>08/06/2026 6:47:11 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
+          <t>Kendall Mckerley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1017,24 +1013,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/04/2026 4:21:54 PM</t>
+          <t>08/06/2026 10:52:41 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1066,17 +1058,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/03/2026 7:28:46 PM</t>
+          <t>08/04/2026 4:21:54 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>John Arnold</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1091,7 +1083,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1115,17 +1107,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/31/2026 12:01:49 PM</t>
+          <t>08/03/2026 7:28:46 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>John Arnold</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1140,7 +1132,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1154,30 +1146,32 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>0.535</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/30/2026 3:53:18 PM</t>
+          <t>07/31/2026 12:01:49 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1187,7 +1181,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1201,27 +1195,25 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" t="n">
+        <v>0.535</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/27/2026 5:28:21 PM</t>
+          <t>07/30/2026 3:53:18 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1236,7 +1228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1250,30 +1242,32 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.736</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27/2026 7:08:38 AM</t>
+          <t>07/27/2026 5:28:21 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1283,7 +1277,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1297,17 +1291,15 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N18" t="n">
+        <v>0.736</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/26/2026 10:40:27 AM</t>
+          <t>07/27/2026 7:08:38 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1332,7 +1324,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1356,17 +1348,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/26/2026 8:12:01 AM</t>
+          <t>07/26/2026 10:40:27 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1381,7 +1373,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1395,28 +1387,34 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>0.585</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/23/2026 9:24:45 AM</t>
+          <t>07/26/2026 8:12:01 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1424,7 +1422,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1438,34 +1436,28 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" t="n">
+        <v>0.585</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22/2026 2:46:36 PM</t>
+          <t>07/23/2026 9:24:45 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1497,22 +1489,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:05 AM</t>
+          <t>07/22/2026 2:46:36 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1522,7 +1514,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1546,22 +1538,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22/2026 1:42:12 AM</t>
+          <t>07/22/2026 8:57:05 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1571,7 +1563,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1595,7 +1587,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/21/2026 10:34:37 AM</t>
+          <t>07/22/2026 1:42:12 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1620,7 +1612,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1644,20 +1636,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/20/2026 4:24:06 PM</t>
+          <t>07/21/2026 10:34:37 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1665,7 +1661,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1679,32 +1675,30 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>0.798</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20/2026 4:20:33 PM</t>
+          <t>07/20/2026 4:24:06 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1712,13 +1706,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1726,32 +1720,30 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" t="n">
+        <v>0.798</v>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/20/2026 2:59:26 PM</t>
+          <t>07/20/2026 4:20:33 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1761,13 +1753,13 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1775,25 +1767,27 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>0.538</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/19/2026 5:07:21 PM</t>
+          <t>07/20/2026 2:59:26 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1808,7 +1802,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1823,24 +1817,24 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>0.47</v>
+        <v>0.538</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/16/2026 9:32:10 PM</t>
+          <t>07/19/2026 5:07:21 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1855,7 +1849,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1870,23 +1864,31 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>3.691</v>
+        <v>0.47</v>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/16/2026 8:50:56 AM</t>
+          <t>07/16/2026 9:32:10 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>Truck 6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1894,7 +1896,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1908,29 +1910,23 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N31" t="n">
+        <v>3.691</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/16/2026 1:50:44 AM</t>
+          <t>07/16/2026 8:50:56 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 22</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
@@ -1963,24 +1959,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15/2026 12:09:06 PM</t>
+          <t>07/16/2026 1:50:44 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1988,7 +1980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2012,22 +2004,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/14/2026 9:10:53 AM</t>
+          <t>07/15/2026 12:09:06 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2061,22 +2053,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09/2026 5:35:48 PM</t>
+          <t>07/14/2026 9:10:53 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2086,7 +2078,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2100,30 +2092,32 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>0.586</v>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/07/2026 4:24:46 PM</t>
+          <t>07/09/2026 5:35:48 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2133,7 +2127,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2147,30 +2141,32 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.586</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/06/2026 1:15:36 AM</t>
+          <t>07/07/2026 4:24:46 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2178,7 +2174,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2202,7 +2198,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/03/2026 1:27:36 AM</t>
+          <t>07/06/2026 1:15:36 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2212,14 +2208,10 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Donald White</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2251,7 +2243,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02/2026 7:36:53 AM</t>
+          <t>07/03/2026 1:27:36 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2276,7 +2268,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2300,22 +2292,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/01/2026 11:21:32 AM</t>
+          <t>07/02/2026 7:36:53 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2325,7 +2317,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2349,7 +2341,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30/2026 10:56:28 AM</t>
+          <t>07/01/2026 11:21:32 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2374,7 +2366,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2398,22 +2390,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/25/2026 9:42:46 AM</t>
+          <t>06/30/2026 10:56:28 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2423,7 +2415,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2447,22 +2439,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/24/2026 4:25:18 PM</t>
+          <t>06/25/2026 9:42:46 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truck 45</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2472,7 +2464,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2496,17 +2488,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/23/2026 3:35:05 PM</t>
+          <t>06/24/2026 4:25:18 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2521,7 +2513,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2535,30 +2527,32 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>0.528</v>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/23/2026 6:54:31 AM</t>
+          <t>06/23/2026 3:35:05 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2568,7 +2562,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2582,17 +2576,15 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N45" t="n">
+        <v>0.528</v>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/22/2026 9:11:54 PM</t>
+          <t>06/23/2026 6:54:31 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2602,12 +2594,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2617,7 +2609,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2631,30 +2623,32 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>0.541</v>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/18/2026 6:18:24 PM</t>
+          <t>06/22/2026 9:11:54 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2664,7 +2658,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2678,30 +2672,32 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N47" t="n">
+        <v>0.541</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/17/2026 2:01:08 PM</t>
+          <t>06/18/2026 6:18:24 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2709,7 +2705,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2733,7 +2729,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/15/2026 4:15:12 PM</t>
+          <t>06/17/2026 2:01:08 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2743,14 +2739,10 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2758,13 +2750,13 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2782,22 +2774,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/15/2026 8:32:09 AM</t>
+          <t>06/15/2026 4:15:12 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2807,13 +2799,13 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2831,22 +2823,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/12/2026 10:25:32 PM</t>
+          <t>06/15/2026 8:32:09 AM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2856,7 +2848,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2880,20 +2872,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/12/2026 1:46:41 PM</t>
+          <t>06/12/2026 10:25:32 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2925,24 +2921,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/11/2026 3:36:21 PM</t>
+          <t>06/12/2026 1:46:41 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2950,7 +2942,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2974,16 +2966,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/11/2026 11:14:55 AM</t>
+          <t>06/11/2026 3:36:21 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>Truck 8</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3015,24 +3015,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/10/2026 3:29:55 PM</t>
+          <t>06/11/2026 11:14:55 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Truck 7</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3040,7 +3032,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3054,25 +3046,27 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>5.497</v>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/10/2026 6:19:44 AM</t>
+          <t>06/10/2026 3:29:55 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3087,7 +3081,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3101,26 +3095,32 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N56" t="n">
+        <v>5.497</v>
       </c>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/08/2026 3:02:41 PM</t>
+          <t>06/10/2026 6:19:44 AM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>SV1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3152,24 +3152,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/07/2026 3:36:18 AM</t>
+          <t>06/08/2026 3:02:41 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SV1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3177,7 +3169,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3201,22 +3193,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/01/2026 8:11:54 PM</t>
+          <t>06/07/2026 3:36:18 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3226,7 +3218,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3250,7 +3242,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>05/28/2026 5:38:57 PM</t>
+          <t>06/01/2026 8:11:54 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3258,8 +3250,16 @@
           <t>Truck 12</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Josh Caldwell</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3291,12 +3291,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>05/28/2026 1:42:30 PM</t>
+          <t>05/28/2026 5:38:57 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3332,24 +3332,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>05/26/2026 2:44:39 PM</t>
+          <t>05/28/2026 1:42:30 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truck 8</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Truck 7</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3357,7 +3349,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3371,28 +3363,34 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>0.484</v>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05/26/2026 2:13:56 PM</t>
+          <t>05/26/2026 2:44:39 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3415,9 +3413,52 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>05/26/2026 2:13:56 PM</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Truck 22</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Harsh Brake</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
         <v>0.502</v>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,227 +3239,6 @@
       </c>
       <c r="O59" t="inlineStr"/>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>06/01/2026 8:11:54 PM</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Josh Caldwell</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Inattentive Driving</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>05/28/2026 5:38:57 PM</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>No Seat Belt</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>05/28/2026 1:42:30 PM</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Truck 7</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>No Seat Belt</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>05/26/2026 2:44:39 PM</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Truck 8</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Harsh Brake</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="O63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>05/26/2026 2:13:56 PM</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Truck 22</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Harsh Brake</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Needs Coaching</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="O64" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/23/2026 1:42:43 AM</t>
+          <t>09/03/2026 8:02:45 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,7 +504,11 @@
           <t>SV2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Donald White</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -537,20 +541,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/19/2026 5:03:58 PM</t>
+          <t>09/02/2026 4:11:10 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Chico Leone</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -558,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -582,7 +590,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/17/2026 7:10:05 AM</t>
+          <t>08/23/2026 1:42:43 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -590,16 +598,8 @@
           <t>SV2</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -631,24 +631,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/12/2026 11:53:33 AM</t>
+          <t>08/19/2026 5:03:58 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -656,13 +652,13 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -680,22 +676,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/12/2026 9:28:11 AM</t>
+          <t>08/17/2026 7:10:05 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,7 +701,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -729,38 +725,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/12/2026 8:49:07 AM</t>
+          <t>08/12/2026 11:53:33 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jason Scott</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -778,22 +774,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/11/2026 2:19:50 PM</t>
+          <t>08/12/2026 9:28:11 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -803,7 +799,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -827,32 +823,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/11/2026 10:53:25 AM</t>
+          <t>08/12/2026 8:49:07 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Jason Scott</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -876,17 +872,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/07/2026 3:29:42 PM</t>
+          <t>08/11/2026 2:19:50 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -901,7 +897,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -915,28 +911,34 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>0.625</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/07/2026 7:34:14 AM</t>
+          <t>08/11/2026 10:53:25 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -944,7 +946,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -968,20 +970,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/06/2026 6:47:11 PM</t>
+          <t>08/07/2026 3:29:42 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -989,7 +995,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1003,22 +1009,20 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" t="n">
+        <v>0.625</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/06/2026 10:52:41 AM</t>
+          <t>08/07/2026 7:34:14 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1058,24 +1062,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/04/2026 4:21:54 PM</t>
+          <t>08/06/2026 6:47:11 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1107,24 +1107,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/03/2026 7:28:46 PM</t>
+          <t>08/06/2026 10:52:41 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>John Arnold</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1132,7 +1128,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1156,17 +1152,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/31/2026 12:01:49 PM</t>
+          <t>08/04/2026 4:21:54 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1181,7 +1177,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1195,30 +1191,32 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0.535</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/30/2026 3:53:18 PM</t>
+          <t>08/03/2026 7:28:46 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>John Arnold</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1228,7 +1226,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1252,22 +1250,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27/2026 5:28:21 PM</t>
+          <t>07/31/2026 12:01:49 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1292,29 +1290,29 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0.736</v>
+        <v>0.535</v>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/27/2026 7:08:38 AM</t>
+          <t>07/30/2026 3:53:18 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1324,7 +1322,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1348,22 +1346,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/26/2026 10:40:27 AM</t>
+          <t>07/27/2026 5:28:21 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1373,7 +1371,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1387,27 +1385,25 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" t="n">
+        <v>0.736</v>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/26/2026 8:12:01 AM</t>
+          <t>07/27/2026 7:08:38 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1436,28 +1432,34 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0.585</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/23/2026 9:24:45 AM</t>
+          <t>07/26/2026 10:40:27 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1465,7 +1467,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1489,17 +1491,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22/2026 2:46:36 PM</t>
+          <t>07/26/2026 8:12:01 AM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1514,7 +1516,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1528,34 +1530,28 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" t="n">
+        <v>0.585</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:05 AM</t>
+          <t>07/23/2026 9:24:45 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1563,7 +1559,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1587,7 +1583,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22/2026 1:42:12 AM</t>
+          <t>07/22/2026 2:46:36 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1597,7 +1593,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1612,7 +1608,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1636,22 +1632,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/21/2026 10:34:37 AM</t>
+          <t>07/22/2026 8:57:05 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1661,7 +1657,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1685,20 +1681,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/20/2026 4:24:06 PM</t>
+          <t>07/22/2026 1:42:12 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1720,30 +1720,32 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>0.798</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/20/2026 4:20:33 PM</t>
+          <t>07/21/2026 10:34:37 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1753,13 +1755,13 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1777,24 +1779,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/20/2026 2:59:26 PM</t>
+          <t>07/20/2026 4:24:06 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1802,7 +1800,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1817,14 +1815,14 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>0.538</v>
+        <v>0.798</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/19/2026 5:07:21 PM</t>
+          <t>07/20/2026 4:20:33 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1834,12 +1832,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1849,13 +1847,13 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1863,25 +1861,27 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>0.47</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/16/2026 9:32:10 PM</t>
+          <t>07/20/2026 2:59:26 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1911,23 +1911,31 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>3.691</v>
+        <v>0.538</v>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/16/2026 8:50:56 AM</t>
+          <t>07/19/2026 5:07:21 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>Truck 13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Josh Caldwell</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1935,7 +1943,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1949,30 +1957,32 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N32" t="n">
+        <v>0.47</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/16/2026 1:50:44 AM</t>
+          <t>07/16/2026 9:32:10 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Robert Bailey</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1980,7 +1990,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1994,34 +2004,24 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N33" t="n">
+        <v>3.691</v>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15/2026 12:09:06 PM</t>
+          <t>07/16/2026 8:50:56 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truck 3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Truck 12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2053,24 +2053,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/14/2026 9:10:53 AM</t>
+          <t>07/16/2026 1:50:44 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2078,7 +2074,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2102,17 +2098,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09/2026 5:35:48 PM</t>
+          <t>07/15/2026 12:09:06 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2141,25 +2137,27 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>0.586</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/07/2026 4:24:46 PM</t>
+          <t>07/14/2026 9:10:53 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2174,7 +2172,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2198,7 +2196,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/06/2026 1:15:36 AM</t>
+          <t>07/09/2026 5:35:48 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2208,10 +2206,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Peyton Birchfield</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2219,7 +2221,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2233,32 +2235,30 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N38" t="n">
+        <v>0.586</v>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/03/2026 1:27:36 AM</t>
+          <t>07/07/2026 4:24:46 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02/2026 7:36:53 AM</t>
+          <t>07/06/2026 1:15:36 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2302,14 +2302,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Donald White</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2317,7 +2313,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2341,22 +2337,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/01/2026 11:21:32 AM</t>
+          <t>07/03/2026 1:27:36 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2390,22 +2386,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30/2026 10:56:28 AM</t>
+          <t>07/02/2026 7:36:53 AM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2415,7 +2411,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2439,22 +2435,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/25/2026 9:42:46 AM</t>
+          <t>07/01/2026 11:21:32 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2464,7 +2460,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2488,17 +2484,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/24/2026 4:25:18 PM</t>
+          <t>06/30/2026 10:56:28 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 45</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2513,7 +2509,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2537,22 +2533,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/23/2026 3:35:05 PM</t>
+          <t>06/25/2026 9:42:46 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2562,7 +2558,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2576,30 +2572,32 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
-        <v>0.528</v>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/23/2026 6:54:31 AM</t>
+          <t>06/24/2026 4:25:18 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2633,17 +2631,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/22/2026 9:11:54 PM</t>
+          <t>06/23/2026 3:35:05 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2658,7 +2656,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2673,24 +2671,24 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>0.541</v>
+        <v>0.528</v>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/18/2026 6:18:24 PM</t>
+          <t>06/23/2026 6:54:31 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2705,7 +2703,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2729,20 +2727,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/17/2026 2:01:08 PM</t>
+          <t>06/22/2026 9:11:54 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Will Ordoyne</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2750,7 +2752,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2764,32 +2766,30 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N49" t="n">
+        <v>0.541</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/15/2026 4:15:12 PM</t>
+          <t>06/18/2026 6:18:24 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2799,13 +2799,13 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2823,24 +2823,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/15/2026 8:32:09 AM</t>
+          <t>06/17/2026 2:01:08 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2848,7 +2844,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2872,22 +2868,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/12/2026 10:25:32 PM</t>
+          <t>06/15/2026 4:15:12 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2897,13 +2893,13 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2921,20 +2917,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/12/2026 1:46:41 PM</t>
+          <t>06/15/2026 8:32:09 AM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2966,22 +2966,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/11/2026 3:36:21 PM</t>
+          <t>06/12/2026 10:25:32 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3015,15 +3015,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/11/2026 11:14:55 AM</t>
+          <t>06/12/2026 1:46:41 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Truck 22</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
@@ -3056,22 +3060,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/10/2026 3:29:55 PM</t>
+          <t>06/11/2026 3:36:21 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3081,7 +3085,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3095,32 +3099,26 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>5.497</v>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/10/2026 6:19:44 AM</t>
+          <t>06/11/2026 11:14:55 AM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SV1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3152,16 +3150,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/08/2026 3:02:41 PM</t>
+          <t>06/10/2026 3:29:55 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Truck 7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bryan Deshotel</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3169,7 +3175,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3183,17 +3189,15 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N58" t="n">
+        <v>5.497</v>
       </c>
       <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/07/2026 3:36:18 AM</t>
+          <t>06/10/2026 6:19:44 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,20 +496,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/03/2026 8:02:45 AM</t>
+          <t>09/07/2026 4:43:18 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -517,7 +521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Ran Red Light, Harsh Turn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -531,27 +535,25 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N2" t="n">
+        <v>0.513</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/02/2026 4:11:10 PM</t>
+          <t>09/04/2026 4:54:03 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chico Leone</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -566,7 +568,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -590,19 +592,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/23/2026 1:42:43 AM</t>
+          <t>09/04/2026 3:41:41 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SV2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jason Scott</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -631,17 +641,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/19/2026 5:03:58 PM</t>
+          <t>09/03/2026 8:02:45 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
+          <t>Donald White</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -676,22 +686,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/17/2026 7:10:05 AM</t>
+          <t>09/02/2026 4:11:10 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Chico Leone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -701,7 +711,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -725,24 +735,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/12/2026 11:53:33 AM</t>
+          <t>08/23/2026 1:42:43 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truck 12</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>SV2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -750,13 +752,13 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -774,24 +776,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/12/2026 9:28:11 AM</t>
+          <t>08/19/2026 5:03:58 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -799,7 +797,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -823,17 +821,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/12/2026 8:49:07 AM</t>
+          <t>08/17/2026 7:10:05 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jason Scott</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -843,12 +841,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -872,22 +870,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/11/2026 2:19:50 PM</t>
+          <t>08/12/2026 11:53:33 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -897,13 +895,13 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -921,17 +919,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/11/2026 10:53:25 AM</t>
+          <t>08/12/2026 9:28:11 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -946,7 +944,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -970,17 +968,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/07/2026 3:29:42 PM</t>
+          <t>08/12/2026 8:49:07 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Jason Scott</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -990,12 +988,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Trucks, Full fleet </t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1009,28 +1007,34 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>0.625</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/07/2026 7:34:14 AM</t>
+          <t>08/11/2026 2:19:50 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Bryan Deshotel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1062,7 +1066,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/06/2026 6:47:11 PM</t>
+          <t>08/11/2026 10:53:25 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1072,10 +1076,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Chris Mcconnell</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1083,7 +1091,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1107,20 +1115,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/06/2026 10:52:41 AM</t>
+          <t>08/07/2026 3:29:42 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1128,7 +1140,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1142,34 +1154,28 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N15" t="n">
+        <v>0.625</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/04/2026 4:21:54 PM</t>
+          <t>08/07/2026 7:34:14 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1201,24 +1207,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/03/2026 7:28:46 PM</t>
+          <t>08/06/2026 6:47:11 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>John Arnold</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1226,7 +1228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1250,24 +1252,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/31/2026 12:01:49 PM</t>
+          <t>08/06/2026 10:52:41 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1275,7 +1273,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1289,30 +1287,32 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>0.535</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/30/2026 3:53:18 PM</t>
+          <t>08/04/2026 4:21:54 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ran Red Light</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1346,22 +1346,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/27/2026 5:28:21 PM</t>
+          <t>08/03/2026 7:28:46 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>John Arnold</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1385,25 +1385,27 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>0.736</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/27/2026 7:08:38 AM</t>
+          <t>07/31/2026 12:01:49 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Josh Caldwell</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1418,7 +1420,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1432,32 +1434,30 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" t="n">
+        <v>0.535</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/26/2026 10:40:27 AM</t>
+          <t>07/30/2026 3:53:18 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Mark Gwin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Ran Red Light</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1491,22 +1491,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/26/2026 8:12:01 AM</t>
+          <t>07/27/2026 5:28:21 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1531,27 +1531,31 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>0.585</v>
+        <v>0.736</v>
       </c>
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/23/2026 9:24:45 AM</t>
+          <t>07/27/2026 7:08:38 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kendall Mckerley</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1583,12 +1587,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22/2026 2:46:36 PM</t>
+          <t>07/26/2026 10:40:27 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1608,7 +1612,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1632,22 +1636,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22/2026 8:57:05 AM</t>
+          <t>07/26/2026 8:12:01 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1657,7 +1661,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1671,34 +1675,28 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N26" t="n">
+        <v>0.585</v>
       </c>
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22/2026 1:42:12 AM</t>
+          <t>07/23/2026 9:24:45 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truck 1</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Kendall Mckerley</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1706,7 +1704,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1730,7 +1728,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/21/2026 10:34:37 AM</t>
+          <t>07/22/2026 2:46:36 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1740,7 +1738,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1755,7 +1753,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1779,7 +1777,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/20/2026 4:24:06 PM</t>
+          <t>07/22/2026 8:57:05 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1789,10 +1787,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Nick Whitaker</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1800,7 +1802,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1814,30 +1816,32 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>0.798</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/20/2026 4:20:33 PM</t>
+          <t>07/22/2026 1:42:12 AM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1853,7 +1857,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1871,17 +1875,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/20/2026 2:59:26 PM</t>
+          <t>07/21/2026 10:34:37 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1896,7 +1900,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1910,32 +1914,30 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>0.538</v>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/19/2026 5:07:21 PM</t>
+          <t>07/20/2026 4:24:06 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Truck 13</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Josh Caldwell</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -1943,7 +1945,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1958,29 +1960,29 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>0.47</v>
+        <v>0.798</v>
       </c>
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/16/2026 9:32:10 PM</t>
+          <t>07/20/2026 4:20:33 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1990,13 +1992,13 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2004,15 +2006,17 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>3.691</v>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/16/2026 8:50:56 AM</t>
+          <t>07/20/2026 2:59:26 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2020,8 +2024,16 @@
           <t>Truck 12</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2029,7 +2041,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2043,30 +2055,32 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N34" t="n">
+        <v>0.538</v>
       </c>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/16/2026 1:50:44 AM</t>
+          <t>07/19/2026 5:07:21 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Josh Caldwell</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2074,7 +2088,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2088,32 +2102,30 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N35" t="n">
+        <v>0.47</v>
       </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/15/2026 12:09:06 PM</t>
+          <t>07/16/2026 9:32:10 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2123,7 +2135,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Crash</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2137,17 +2149,15 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>3.691</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/14/2026 9:10:53 AM</t>
+          <t>07/16/2026 8:50:56 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2155,16 +2165,8 @@
           <t>Truck 12</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ben Mcgough</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Full fleet , Light Duty</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2172,7 +2174,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2196,24 +2198,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/09/2026 5:35:48 PM</t>
+          <t>07/16/2026 1:50:44 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2221,7 +2219,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2235,30 +2233,32 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>0.586</v>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/07/2026 4:24:46 PM</t>
+          <t>07/15/2026 12:09:06 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Bryan Deshotel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2292,20 +2292,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/06/2026 1:15:36 AM</t>
+          <t>07/14/2026 9:10:53 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Donald White</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2313,7 +2317,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2337,7 +2341,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/03/2026 1:27:36 AM</t>
+          <t>07/09/2026 5:35:48 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2362,7 +2366,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2376,32 +2380,30 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N41" t="n">
+        <v>0.586</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02/2026 7:36:53 AM</t>
+          <t>07/07/2026 4:24:46 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2411,7 +2413,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Forward Collision Warning</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2435,24 +2437,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/01/2026 11:21:32 AM</t>
+          <t>07/06/2026 1:15:36 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Full fleet , Heavy Duty</t>
-        </is>
-      </c>
+          <t>Donald White</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2484,22 +2482,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30/2026 10:56:28 AM</t>
+          <t>07/03/2026 1:27:36 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Truck 26</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nick Whitaker</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Full fleet , Heavy Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2509,7 +2507,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2533,7 +2531,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/25/2026 9:42:46 AM</t>
+          <t>07/02/2026 7:36:53 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2558,7 +2556,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Forward Collision Warning</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2582,17 +2580,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/24/2026 4:25:18 PM</t>
+          <t>07/01/2026 11:21:32 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Truck 45</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Will Ordoyne</t>
+          <t>Daniel Vanwinterswyk</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2631,7 +2629,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/23/2026 3:35:05 PM</t>
+          <t>06/30/2026 10:56:28 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2656,7 +2654,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2670,30 +2668,32 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
-        <v>0.528</v>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/23/2026 6:54:31 AM</t>
+          <t>06/25/2026 9:42:46 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Peyton Birchfield</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t xml:space="preserve">Full fleet </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2727,12 +2727,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/22/2026 9:11:54 PM</t>
+          <t>06/24/2026 4:25:18 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harsh Turn</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2766,30 +2766,32 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>0.541</v>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/18/2026 6:18:24 PM</t>
+          <t>06/23/2026 3:35:05 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truck 6</t>
+          <t>Truck 26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Robert Bailey</t>
+          <t>Nick Whitaker</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Full fleet , Light Duty</t>
+          <t>Full fleet , Heavy Duty</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2799,7 +2801,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2813,30 +2815,32 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N50" t="n">
+        <v>0.528</v>
       </c>
       <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/17/2026 2:01:08 PM</t>
+          <t>06/23/2026 6:54:31 AM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Ben Mcgough</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Full fleet , Light Duty</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2844,7 +2848,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2868,17 +2872,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/15/2026 4:15:12 PM</t>
+          <t>06/22/2026 9:11:54 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Truck 32</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Daniel Vanwinterswyk</t>
+          <t>Will Ordoyne</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2893,13 +2897,13 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Harsh Turn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2907,27 +2911,25 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N52" t="n">
+        <v>0.541</v>
       </c>
       <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/15/2026 8:32:09 AM</t>
+          <t>06/18/2026 6:18:24 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Truck 12</t>
+          <t>Truck 6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ben Mcgough</t>
+          <t>Robert Bailey</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2942,7 +2944,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2966,24 +2968,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/12/2026 10:25:32 PM</t>
+          <t>06/17/2026 2:01:08 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Truck 3</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mark Gwin</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -2991,7 +2989,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3015,20 +3013,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/12/2026 1:46:41 PM</t>
+          <t>06/15/2026 4:15:12 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Truck 22</t>
+          <t>Truck 32</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Josh Gregory</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Daniel Vanwinterswyk</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Full fleet , Heavy Duty</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3036,13 +3038,13 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3060,17 +3062,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/11/2026 3:36:21 PM</t>
+          <t>06/15/2026 8:32:09 AM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Truck 8</t>
+          <t>Truck 12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chris Mcconnell</t>
+          <t>Ben Mcgough</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3109,16 +3111,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/11/2026 11:14:55 AM</t>
+          <t>06/12/2026 10:25:32 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>Truck 3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mark Gwin</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3150,24 +3160,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/10/2026 3:29:55 PM</t>
+          <t>06/12/2026 1:46:41 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Truck 7</t>
+          <t>Truck 22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bryan Deshotel</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full fleet </t>
-        </is>
-      </c>
+          <t>Josh Gregory</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">Current Trucks, Full fleet </t>
@@ -3175,7 +3181,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Crash</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3189,30 +3195,32 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>5.497</v>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/10/2026 6:19:44 AM</t>
+          <t>06/11/2026 3:36:21 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>Truck 8</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Peyton Birchfield</t>
+          <t>Chris Mcconnell</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full fleet </t>
+          <t>Full fleet , Light Duty</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3222,7 +3230,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3243,6 +3251,94 @@
       </c>
       <c r="O59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>06/11/2026 11:14:55 AM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>06/10/2026 3:29:55 PM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Truck 7</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bryan Deshotel</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full fleet </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Trucks, Full fleet </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Crash</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>5.497</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
